--- a/Question_register.xlsx
+++ b/Question_register.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modules" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$232</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$235</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Constructed variables'!$A$1:$F$140</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Literature'!$A$1:$C$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Literature'!$A$1:$C$151</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Modules'!$A$1:$C$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J232"/>
+  <dimension ref="A1:J235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8762,33 +8762,37 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>trek_dependent</t>
+          <t>ropeway_expect_work</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>Is your main work carrying, transporting or guiding people or goods on foot along the pilgrimage trek?</t>
+          <t>If the ropeway is built, what do you think will happen to your own work? More work for you; less work; about the same; or don't know?</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
+          <t>अगर रोपवे बन गया, तो आपके अपने काम पर क्या असर होगा? मेरे लिए ज़्यादा काम; मेरे लिए कम काम; लगभग वैसा ही; या पता नहीं?</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I183" s="2" t="inlineStr"/>
+          <t>1 More work for me | 2 Less work for me | 3 About the same | 97 Don't know</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if site = 1 (Kedarnath route)</t>
+        </is>
+      </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
+          <t>Pelz et al. 2024, Energy Policy 186:113973 (concept: perceived effect on livelihoods; wording ours)</t>
         </is>
       </c>
     </row>
@@ -8798,17 +8802,17 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Ropeway</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>job_situation</t>
+          <t>ropeway_expect_jobs</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -8818,23 +8822,27 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>During the last month, what were you mainly doing? Ask it open and code the closest one; do not read the list out.</t>
+          <t>Who do you think will get most of the jobs the ropeway creates? People from these villages; people from outside the area; nobody will get jobs; or don't know?</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>पिछले महीने आप मुख्य रूप से क्या कर रहे थे? खुला पूछें और जो सबसे मिलता हो वह कोड करें; पूरी सूची पढ़कर न सुनाएँ।</t>
+          <t>रोपवे में जो नौकरियाँ बनेंगी, वे ज़्यादातर किसे मिलेंगी? इन गाँवों के लोगों को; इलाके के बाहर के लोगों को; किसी को नहीं मिलेंगी; या पता नहीं?</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>1 Works for pay full-time | 2 Works for pay part-time or occasional jobs | 3 Studies and works | 4 Only studies | 5 Being trained for work only | 6 Retired or pensioned | 7 Unpaid household tasks or caring for others | 8 Unemployed, actively seeking work | 9 Sick or disabled, cannot work | 10 Neither studying, working nor seeking work | 97 Does not know</t>
-        </is>
-      </c>
-      <c r="I184" s="2" t="inlineStr"/>
+          <t>1 People from these villages | 2 People from outside the area | 3 Nobody will get jobs | 97 Don't know</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if site = 1 (Kedarnath route)</t>
+        </is>
+      </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
+          <t>Pelz et al. 2024, Energy Policy 186:113973 (concept: local vs outside benefit; wording ours)</t>
         </is>
       </c>
     </row>
@@ -8844,17 +8852,17 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Ropeway</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>job_permanence</t>
+          <t>ropeway_trust</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -8864,27 +8872,27 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
+          <t>Do you think the ropeway will improve the livelihoods of people here? Yes; no; or don't know?</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
+          <t>क्या आपको लगता है कि रोपवे से यहाँ के लोगों की रोज़ी-रोटी सुधरेगी? हाँ; नहीं; या पता नहीं?</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>1 Permanent | 2 Seasonal or temporary | 3 Occasional or casual | 4 On probation | 5 Fixed-term</t>
+          <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+          <t>Ask only if site = 1 (Kedarnath route)</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
+          <t>Pelz et al. 2024, Energy Policy 186:113973 (Fig. 4B, trust in the company; wording ours)</t>
         </is>
       </c>
     </row>
@@ -8894,47 +8902,43 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Ropeway</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>contract_status</t>
+          <t>trek_dependent</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
+          <t>Is your main work carrying, transporting or guiding people or goods on foot along the pilgrimage trek?</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
+          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, signed | 2 Yes, but not yet signed | 3 No contract</t>
-        </is>
-      </c>
-      <c r="I186" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working); and employment_type is 3 or 4 (wage workers) — self-employed skip to the next question</t>
-        </is>
-      </c>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr"/>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
+          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
         </is>
       </c>
     </row>
@@ -8954,37 +8958,33 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>workplace_registered</t>
+          <t>job_situation</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
+          <t>During the last month, what were you mainly doing? Ask it open and code the closest one; do not read the list out.</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
+          <t>पिछले महीने आप मुख्य रूप से क्या कर रहे थे? खुला पूछें और जो सबसे मिलता हो वह कोड करें; पूरी सूची पढ़कर न सुनाएँ।</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I187" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
-        </is>
-      </c>
+          <t>1 Works for pay full-time | 2 Works for pay part-time or occasional jobs | 3 Studies and works | 4 Only studies | 5 Being trained for work only | 6 Retired or pensioned | 7 Unpaid household tasks or caring for others | 8 Unemployed, actively seeking work | 9 Sick or disabled, cannot work | 10 Neither studying, working nor seeking work | 97 Does not know</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr"/>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>pension_contrib</t>
+          <t>job_permanence</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -9014,17 +9014,17 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
+          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
+          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, employer deducts it | 2 Yes, contributes voluntarily | 3 No</t>
+          <t>1 Permanent | 2 Seasonal or temporary | 3 Occasional or casual | 4 On probation | 5 Fixed-term</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
         </is>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>work_health_ins</t>
+          <t>contract_status</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -9064,27 +9064,27 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
+          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
+          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, through work | 2 Only private or other insurance | 3 None | 4 Don't know</t>
+          <t>1 Yes, signed | 2 Yes, but not yet signed | 3 No contract</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working); and employment_type is 3 or 4 (wage workers) — self-employed skip to the next question</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
         </is>
       </c>
     </row>
@@ -9104,27 +9104,27 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>leave_rights</t>
+          <t>workplace_registered</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
+          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
+          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>injured_ever</t>
+          <t>pension_contrib</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -9164,17 +9164,17 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>Have you ever been physically injured at your workplace?</t>
+          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
+          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
+          <t>1 Yes, employer deducts it | 2 Yes, contributes voluntarily | 3 No</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
         </is>
       </c>
     </row>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>workplace_injury_12m</t>
+          <t>work_health_ins</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -9214,17 +9214,17 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, was anyone physically injured at your workplace because of work?</t>
+          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी?</t>
+          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
+          <t>1 Yes, through work | 2 Only private or other insurance | 3 None | 4 Don't know</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q20 (split into injury and death)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
         </is>
       </c>
     </row>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>workplace_death_12m</t>
+          <t>leave_rights</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>And in the last 12 months, did anyone die at your workplace because of work?</t>
+          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>और पिछले 12 महीनों में, क्या आपके काम की जगह पर काम की वजह से किसी की मौत हुई?</t>
+          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q20 (split into injury and death)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
         </is>
       </c>
     </row>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>wants_more_work</t>
+          <t>injured_ever</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>Would you like to work more hours than you do?</t>
+          <t>Have you ever been physically injured at your workplace?</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
+          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>Ask if job_situation is 1 to 7 (Apablaza routes codes 4-7 straight to this question)</t>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
         </is>
       </c>
     </row>
@@ -9354,33 +9354,37 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>more_hours_day</t>
+          <t>workplace_injury_12m</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>On a working day, how many MORE hours would you like to work?</t>
+          <t>In the last 12 months, was anyone physically injured at your workplace because of work?</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
-        </is>
-      </c>
-      <c r="H195" s="2" t="inlineStr"/>
+          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी?</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes | 97 Don't know</t>
+        </is>
+      </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>Ask if wants_more_work = 1, or if job_situation = 8 (Apablaza routes the unemployed-and-seeking category here directly)</t>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q20 (split into injury and death)</t>
         </is>
       </c>
     </row>
@@ -9400,33 +9404,37 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>months_looked_for_work</t>
+          <t>workplace_death_12m</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
+          <t>And in the last 12 months, did anyone die at your workplace because of work?</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
-        </is>
-      </c>
-      <c r="H196" s="2" t="inlineStr"/>
+          <t>और पिछले 12 महीनों में, क्या आपके काम की जगह पर काम की वजह से किसी की मौत हुई?</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes | 97 Don't know</t>
+        </is>
+      </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>Ask if any month in the calendar is 'No paid work', or if job_situation = 8</t>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q20 (split into injury and death)</t>
         </is>
       </c>
     </row>
@@ -9446,7 +9454,7 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>first_job_ever</t>
+          <t>wants_more_work</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -9456,12 +9464,12 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>Was your current work the first paid job you ever had?</t>
+          <t>Would you like to work more hours than you do?</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
+          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -9469,10 +9477,14 @@
           <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
-      <c r="I197" s="2" t="inlineStr"/>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>Ask if job_situation is 1 to 7 (Apablaza routes codes 4-7 straight to this question)</t>
+        </is>
+      </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
         </is>
       </c>
     </row>
@@ -9492,37 +9504,33 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>higher_ed</t>
+          <t>more_hours_day</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>Have you completed any college, diploma or university course?</t>
+          <t>On a working day, how many MORE hours would you like to work?</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>क्या आपने कॉलेज, डिप्लोमा या यूनिवर्सिटी का कोई कोर्स पूरा किया है?</t>
-        </is>
-      </c>
-      <c r="H198" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
-        </is>
-      </c>
+          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr"/>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+          <t>Ask if wants_more_work = 1, or if job_situation = 8 (Apablaza routes the unemployed-and-seeking category here directly)</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 employment table, occupational status (1/8)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
         </is>
       </c>
     </row>
@@ -9542,37 +9550,33 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>social_security_any</t>
+          <t>months_looked_for_work</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>Are you enrolled in any pension, insurance or social-security scheme? For example, EPFO or PM-SYM pension, or Ayushman Bharat health cover.</t>
+          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>क्या आप किसी पेंशन, बीमा या सरकारी सामाजिक सुरक्षा योजना में शामिल हैं? जैसे EPFO या PM-SYM पेंशन, या आयुष्मान भारत स्वास्थ्य कवर।</t>
-        </is>
-      </c>
-      <c r="H199" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
-        </is>
-      </c>
+          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr"/>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+          <t>Ask if any month in the calendar is 'No paid work', or if job_situation = 8</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 employment table, employment security (1/8)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
         </is>
       </c>
     </row>
@@ -9592,7 +9596,7 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>intens_speed</t>
+          <t>first_job_ever</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -9602,12 +9606,12 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you work at very high speed?</t>
+          <t>Was your current work the first paid job you ever had?</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप बहुत तेज़ रफ़्तार से काम करते हैं?</t>
+          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -9615,14 +9619,10 @@
           <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
-      <c r="I200" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
-        </is>
-      </c>
+      <c r="I200" s="2" t="inlineStr"/>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 employment table, work intensity (1/16)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>intens_deadline</t>
+          <t>higher_ed</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you work to tight deadlines?</t>
+          <t>Have you completed any college, diploma or university course?</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आपको कड़ी समय-सीमा में काम करना पड़ता है?</t>
+          <t>क्या आपने कॉलेज, डिप्लोमा या यूनिवर्सिटी का कोई कोर्स पूरा किया है?</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 employment table, work intensity (1/16)</t>
+          <t>Apablaza et al. 2026, Appendix 2 employment table, occupational status (1/8)</t>
         </is>
       </c>
     </row>
@@ -9692,7 +9692,7 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>intens_time</t>
+          <t>social_security_any</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you not have enough time to finish your tasks?</t>
+          <t>Are you enrolled in any pension, insurance or social-security scheme? For example, EPFO or PM-SYM pension, or Ayushman Bharat health cover.</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आपके पास काम पूरा करने के लिए काफ़ी समय नहीं होता?</t>
+          <t>क्या आप किसी पेंशन, बीमा या सरकारी सामाजिक सुरक्षा योजना में शामिल हैं? जैसे EPFO या PM-SYM पेंशन, या आयुष्मान भारत स्वास्थ्य कवर।</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 employment table, work intensity (1/16)</t>
+          <t>Apablaza et al. 2026, Appendix 2 employment table, employment security (1/8)</t>
         </is>
       </c>
     </row>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>posture_position</t>
+          <t>intens_speed</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you work in a tiring or painful position?</t>
+          <t>For more than half of your working day, do you work at very high speed?</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप थकाने वाली या दर्द वाली स्थिति में काम करते हैं?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप बहुत तेज़ रफ़्तार से काम करते हैं?</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 employment table, posture risk (1/16)</t>
+          <t>Apablaza et al. 2026, Appendix 2 employment table, work intensity (1/16)</t>
         </is>
       </c>
     </row>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>posture_loads</t>
+          <t>intens_deadline</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you carry or move heavy loads?</t>
+          <t>For more than half of your working day, do you work to tight deadlines?</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप भारी बोझ उठाते या ढोते हैं?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आपको कड़ी समय-सीमा में काम करना पड़ता है?</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 employment table, posture risk (1/16)</t>
+          <t>Apablaza et al. 2026, Appendix 2 employment table, work intensity (1/16)</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>posture_repetitive</t>
+          <t>intens_time</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -9852,12 +9852,12 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you make the same movements again and again?</t>
+          <t>For more than half of your working day, do you not have enough time to finish your tasks?</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप एक ही तरह की हरकत बार-बार करते हैं?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आपके पास काम पूरा करने के लिए काफ़ी समय नहीं होता?</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 employment table, posture risk (1/16)</t>
+          <t>Apablaza et al. 2026, Appendix 2 employment table, work intensity (1/16)</t>
         </is>
       </c>
     </row>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>phys_noise</t>
+          <t>posture_position</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>For more than half of your working day, are you exposed to loud noise?</t>
+          <t>For more than half of your working day, do you work in a tiring or painful position?</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप तेज़ शोर में रहते हैं?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप थकाने वाली या दर्द वाली स्थिति में काम करते हैं?</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 employment table, physical risk (1/16)</t>
+          <t>Apablaza et al. 2026, Appendix 2 employment table, posture risk (1/16)</t>
         </is>
       </c>
     </row>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>phys_temperature</t>
+          <t>posture_loads</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>For more than half of your working day, are you exposed to extreme heat or cold?</t>
+          <t>For more than half of your working day, do you carry or move heavy loads?</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप बहुत गर्मी या बहुत ठंड में रहते हैं?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप भारी बोझ उठाते या ढोते हैं?</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 employment table, physical risk (1/16)</t>
+          <t>Apablaza et al. 2026, Appendix 2 employment table, posture risk (1/16)</t>
         </is>
       </c>
     </row>
@@ -9982,17 +9982,17 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Tasks and skills (short block)</t>
+          <t>Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>tk_load</t>
+          <t>posture_repetitive</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -10002,23 +10002,27 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you load, unload, stack or count goods? </t>
+          <t>For more than half of your working day, do you make the same movements again and again?</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप एक ही तरह की हरकत बार-बार करते हैं?</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
-        </is>
-      </c>
-      <c r="I208" s="2" t="inlineStr"/>
+          <t>0 No | 1 Yes | 97 Don't know</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+        </is>
+      </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
+          <t>Apablaza et al. 2026, Appendix 2 employment table, posture risk (1/16)</t>
         </is>
       </c>
     </row>
@@ -10028,17 +10032,17 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Tasks and skills (short block)</t>
+          <t>Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>tk_drive</t>
+          <t>phys_noise</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -10048,23 +10052,27 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you drive a motor vehicle? </t>
+          <t>For more than half of your working day, are you exposed to loud noise?</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप तेज़ शोर में रहते हैं?</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
-        </is>
-      </c>
-      <c r="I209" s="2" t="inlineStr"/>
+          <t>0 No | 1 Yes | 97 Don't know</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+        </is>
+      </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
+          <t>Apablaza et al. 2026, Appendix 2 employment table, physical risk (1/16)</t>
         </is>
       </c>
     </row>
@@ -10074,17 +10082,17 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Tasks and skills (short block)</t>
+          <t>Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>tk_engine</t>
+          <t>phys_temperature</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -10094,23 +10102,27 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you operate an engine or machine? </t>
+          <t>For more than half of your working day, are you exposed to extreme heat or cold?</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप बहुत गर्मी या बहुत ठंड में रहते हैं?</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
-        </is>
-      </c>
-      <c r="I210" s="2" t="inlineStr"/>
+          <t>0 No | 1 Yes | 97 Don't know</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+        </is>
+      </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
+          <t>Apablaza et al. 2026, Appendix 2 employment table, physical risk (1/16)</t>
         </is>
       </c>
     </row>
@@ -10130,7 +10142,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>tk_electric</t>
+          <t>tk_load</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -10140,12 +10152,12 @@
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you do electrical or wiring work? </t>
+          <t xml:space="preserve">Do you load, unload, stack or count goods? </t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
@@ -10156,7 +10168,7 @@
       <c r="I211" s="2" t="inlineStr"/>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
+          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
         </is>
       </c>
     </row>
@@ -10176,7 +10188,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>tk_safety</t>
+          <t>tk_drive</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -10186,12 +10198,12 @@
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you check equipment or the route for safety? </t>
+          <t xml:space="preserve">Do you drive a motor vehicle? </t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -10202,7 +10214,7 @@
       <c r="I212" s="2" t="inlineStr"/>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
+          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
         </is>
       </c>
     </row>
@@ -10222,7 +10234,7 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>tk_sell</t>
+          <t>tk_engine</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -10232,12 +10244,12 @@
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you sell goods or services? </t>
+          <t xml:space="preserve">Do you operate an engine or machine? </t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -10248,7 +10260,7 @@
       <c r="I213" s="2" t="inlineStr"/>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
     </row>
@@ -10268,7 +10280,7 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>tk_cash</t>
+          <t>tk_electric</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -10278,12 +10290,12 @@
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you handle cash and payments? </t>
+          <t xml:space="preserve">Do you do electrical or wiring work? </t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
@@ -10294,7 +10306,7 @@
       <c r="I214" s="2" t="inlineStr"/>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>Autor and Handel 2013; NCO 5131.0401</t>
+          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
         </is>
       </c>
     </row>
@@ -10314,7 +10326,7 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>tk_cook</t>
+          <t>tk_safety</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -10324,12 +10336,12 @@
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you cook or prepare food or drink? </t>
+          <t xml:space="preserve">Do you check equipment or the route for safety? </t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
@@ -10340,7 +10352,7 @@
       <c r="I215" s="2" t="inlineStr"/>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>NCO 5120.0300 cook</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
         </is>
       </c>
     </row>
@@ -10360,7 +10372,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>tk_serve</t>
+          <t>tk_sell</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -10370,12 +10382,12 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you serve guests or customers? </t>
+          <t xml:space="preserve">Do you sell goods or services? </t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -10386,7 +10398,7 @@
       <c r="I216" s="2" t="inlineStr"/>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
+          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
         </is>
       </c>
     </row>
@@ -10406,7 +10418,7 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>tk_clean</t>
+          <t>tk_cash</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -10416,12 +10428,12 @@
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you clean rooms or public areas? </t>
+          <t xml:space="preserve">Do you handle cash and payments? </t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -10432,7 +10444,7 @@
       <c r="I217" s="2" t="inlineStr"/>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
+          <t>Autor and Handel 2013; NCO 5131.0401</t>
         </is>
       </c>
     </row>
@@ -10452,7 +10464,7 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>tk_guide</t>
+          <t>tk_cook</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -10462,12 +10474,12 @@
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you guide or explain things to visitors? </t>
+          <t xml:space="preserve">Do you cook or prepare food or drink? </t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -10478,7 +10490,7 @@
       <c r="I218" s="2" t="inlineStr"/>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
+          <t>NCO 5120.0300 cook</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10510,7 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>tk_coord</t>
+          <t>tk_serve</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -10508,12 +10520,12 @@
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you coordinate work by phone, radio or signals? </t>
+          <t xml:space="preserve">Do you serve guests or customers? </t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -10524,7 +10536,7 @@
       <c r="I219" s="2" t="inlineStr"/>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>NCO 8343.1700 ropeway operator</t>
+          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
         </is>
       </c>
     </row>
@@ -10544,37 +10556,33 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>drove_twowheeler</t>
+          <t>tk_clean</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
+          <t xml:space="preserve">Do you clean rooms or public areas? </t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
+          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I220" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if tk_drive is 1 or 2</t>
-        </is>
-      </c>
+          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr"/>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>Level ladder without licences: people drive without holding a licence</t>
+          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
         </is>
       </c>
     </row>
@@ -10594,37 +10602,33 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>drove_car</t>
+          <t>tk_guide</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>... a car or jeep?</t>
+          <t xml:space="preserve">Do you guide or explain things to visitors? </t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>...कार या जीप?</t>
+          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I221" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if tk_drive is 1 or 2</t>
-        </is>
-      </c>
+          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr"/>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>Level ladder without licences</t>
+          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
         </is>
       </c>
     </row>
@@ -10644,37 +10648,33 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>drove_heavy</t>
+          <t>tk_coord</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>... a truck or bus?</t>
+          <t xml:space="preserve">Do you coordinate work by phone, radio or signals? </t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>...ट्रक या बस?</t>
+          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I222" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if tk_drive is 1 or 2</t>
-        </is>
-      </c>
+          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr"/>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>Level ladder without licences</t>
+          <t>NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
     </row>
@@ -10694,7 +10694,7 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>read_at_work</t>
+          <t>drove_twowheeler</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -10704,12 +10704,12 @@
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
+          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
+          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
@@ -10717,10 +10717,14 @@
           <t>0 No | 1 Yes</t>
         </is>
       </c>
-      <c r="I223" s="2" t="inlineStr"/>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if tk_drive is 1 or 2</t>
+        </is>
+      </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>STEP module 6A</t>
+          <t>Level ladder without licences: people drive without holding a licence</t>
         </is>
       </c>
     </row>
@@ -10740,7 +10744,7 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>calc_at_work</t>
+          <t>drove_car</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -10750,12 +10754,12 @@
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>In your work, do you work out prices or costs?</t>
+          <t>... a car or jeep?</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
+          <t>...कार या जीप?</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -10763,10 +10767,14 @@
           <t>0 No | 1 Yes</t>
         </is>
       </c>
-      <c r="I224" s="2" t="inlineStr"/>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if tk_drive is 1 or 2</t>
+        </is>
+      </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>STEP module 6A</t>
+          <t>Level ladder without licences</t>
         </is>
       </c>
     </row>
@@ -10776,43 +10784,47 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Access to common resources (short block)</t>
+          <t>Tasks and skills (short block)</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>cpr_firewood</t>
+          <t>drove_heavy</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did anyone in your household collect firewood or dead wood from common land or forest near here?</t>
+          <t>... a truck or bus?</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने आस-पास की साझा ज़मीन या जंगल से लकड़ी या सूखी टहनियाँ इकट्ठी कीं?</t>
+          <t>...ट्रक या बस?</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
-        </is>
-      </c>
-      <c r="I225" s="2" t="inlineStr"/>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if tk_drive is 1 or 2</t>
+        </is>
+      </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001 (natural capital); Lax &amp; Krug (firewood as the core forest indicator)</t>
+          <t>Level ladder without licences</t>
         </is>
       </c>
     </row>
@@ -10822,43 +10834,43 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Access to common resources (short block)</t>
+          <t>Tasks and skills (short block)</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>cpr_fodder</t>
+          <t>read_at_work</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did anyone in your household cut grass or fodder from common land near here?</t>
+          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने साझा ज़मीन से घास या चारा काटा?</t>
+          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr"/>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001 (natural capital); Lax &amp; Krug</t>
+          <t>STEP module 6A</t>
         </is>
       </c>
     </row>
@@ -10868,43 +10880,43 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Access to common resources (short block)</t>
+          <t>Tasks and skills (short block)</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>cpr_forest_produce</t>
+          <t>calc_at_work</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did anyone in your household collect herbs, mushrooms or wild fruit from the forest?</t>
+          <t>In your work, do you work out prices or costs?</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने जंगल से जड़ी-बूटी, मशरूम या जंगली फल इकट्ठे किए?</t>
+          <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I227" s="2" t="inlineStr"/>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>Lax &amp; Krug (forest produce as food and medicine)</t>
+          <t>STEP module 6A</t>
         </is>
       </c>
     </row>
@@ -10924,7 +10936,7 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>cpr_grazing</t>
+          <t>cpr_firewood</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -10934,12 +10946,12 @@
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did any animal of your household graze on common pasture?</t>
+          <t>In the last 12 months, did anyone in your household collect firewood or dead wood from common land or forest near here?</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर का कोई जानवर साझा चरागाह में चरा?</t>
+          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने आस-पास की साझा ज़मीन या जंगल से लकड़ी या सूखी टहनियाँ इकट्ठी कीं?</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -10950,7 +10962,7 @@
       <c r="I228" s="2" t="inlineStr"/>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001 (natural capital); Lax &amp; Krug</t>
+          <t>Krantz 2001, natural capital: resource stocks from which resource flows are derived (definitions list); item wording is ours</t>
         </is>
       </c>
     </row>
@@ -10970,7 +10982,7 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>cpr_restricted</t>
+          <t>cpr_fodder</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -10980,12 +10992,12 @@
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, has anyone in your household been stopped from using a common forest, pasture or path, or been asked to pay to use it?</t>
+          <t>In the last 12 months, did anyone in your household cut grass or fodder from common land near here?</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी को साझा जंगल, चरागाह या रास्ते के इस्तेमाल से रोका गया, या इसके लिए पैसे देने को कहा गया?</t>
+          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने साझा ज़मीन से घास या चारा काटा?</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -10996,7 +11008,7 @@
       <c r="I229" s="2" t="inlineStr"/>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001 (claims and access)</t>
+          <t>Krantz 2001, natural capital: resource stocks from which resource flows are derived; item wording is ours</t>
         </is>
       </c>
     </row>
@@ -11016,7 +11028,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>cpr_lost_access</t>
+          <t>cpr_forest_produce</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -11026,12 +11038,12 @@
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, has a common place you used to collect from or graze on been closed because of building, road or ropeway work?</t>
+          <t>In the last 12 months, did anyone in your household collect herbs, mushrooms or wild fruit from the forest?</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या कोई साझा जगह, जहाँ आप पहले लकड़ी, घास या चारा लेते थे, निर्माण, सड़क या रोपवे के काम की वजह से बंद हो गई?</t>
+          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने जंगल से जड़ी-बूटी, मशरूम या जंगली फल इकट्ठे किए?</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -11042,7 +11054,7 @@
       <c r="I230" s="2" t="inlineStr"/>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001 (access); Module J context</t>
+          <t>Krantz 2001, natural capital (resource flows from stocks); item wording is ours</t>
         </is>
       </c>
     </row>
@@ -11062,7 +11074,7 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>cpr_water_route</t>
+          <t>cpr_grazing</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -11072,23 +11084,23 @@
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>On your route or near your worksite, can you use a common water source (spring, tap or stream) without paying?</t>
+          <t>In the last 12 months, did any animal of your household graze on common pasture?</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>रास्ते पर या काम की जगह के पास, क्या आप कोई साझा पानी का स्रोत (झरना, नल या नदी-नाला) बिना पैसे दिए इस्तेमाल कर सकते हैं?</t>
+          <t>पिछले 12 महीनों में, क्या आपके घर का कोई जानवर साझा चरागाह में चरा?</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, free to use | 2 A source exists but we must pay | 3 No source nearby | 97 Don't know</t>
+          <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr"/>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001 (natural capital: water); Lax &amp; Krug (water resources)</t>
+          <t>Krantz 2001, natural capital: resource stocks from which resource flows are derived; item wording is ours</t>
         </is>
       </c>
     </row>
@@ -11108,7 +11120,7 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>cpr_governance</t>
+          <t>cpr_restricted</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -11118,28 +11130,166 @@
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>In this area, who decides who may use the common land and forest? Ask and code what they name; do not read the list.</t>
+          <t>In the last 12 months, has anyone in your household been stopped from using a common forest, pasture or path, or been asked to pay to use it?</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>इस इलाके की साझा ज़मीन और जंगल का फ़ैसला कौन करता है, कि कौन उसका इस्तेमाल कर सकता है? जो नाम लें वही लिख लें; सूची न पढ़ें।</t>
+          <t>पिछले 12 महीनों में, क्या आपके घर के किसी को साझा जंगल, चरागाह या रास्ते के इस्तेमाल से रोका गया, या इसके लिए पैसे देने को कहा गया?</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>1 Village head or panchayat | 2 Forest department | 3 Local committee or community group | 4 Nobody decides; it is open to all | 97 Don't know</t>
+          <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr"/>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001 (institutions); Lax &amp; Krug (adherence to rules)</t>
+          <t>Krantz 2001, access ('the opportunity in practice to use a resource') and claims ('demands and appeals'); item wording is ours</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>Access to common resources (short block)</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>cpr_lost_access</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>select one</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>In the last 12 months, has a common place you used to collect from or graze on been closed because of building, road or ropeway work?</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>पिछले 12 महीनों में, क्या कोई साझा जगह, जहाँ आप पहले लकड़ी, घास या चारा लेते थे, निर्माण, सड़क या रोपवे के काम की वजह से बंद हो गई?</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes | 97 Don't know</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr"/>
+      <c r="J233" s="2" t="inlineStr">
+        <is>
+          <t>Krantz 2001, access (as above); the ropeway link is the project's own</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>Access to common resources (short block)</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>cpr_water_route</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>select one</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>On your route or near your worksite, can you use a common water source (spring, tap or stream) without paying?</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>रास्ते पर या काम की जगह के पास, क्या आप कोई साझा पानी का स्रोत (झरना, नल या नदी-नाला) बिना पैसे दिए इस्तेमाल कर सकते हैं?</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>1 Yes, free to use | 2 A source exists but we must pay | 3 No source nearby | 97 Don't know</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr"/>
+      <c r="J234" s="2" t="inlineStr">
+        <is>
+          <t>Krantz 2001, natural capital (water) and access ('the opportunity in practice to use a resource'); item wording is ours</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>Access to common resources (short block)</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>cpr_governance</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>select one</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>In this area, who decides who may use the common land and forest? Ask and code what they name; do not read the list.</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>इस इलाके की साझा ज़मीन और जंगल का फ़ैसला कौन करता है, कि कौन उसका इस्तेमाल कर सकता है? जो नाम लें वही लिख लें; सूची न पढ़ें।</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>1 Village head or panchayat | 2 Forest department | 3 Local committee or community group | 4 Nobody decides; it is open to all | 97 Don't know</t>
+        </is>
+      </c>
+      <c r="I235" s="2" t="inlineStr"/>
+      <c r="J235" s="2" t="inlineStr">
+        <is>
+          <t>NO SOURCE ON DISK YET: Krantz does not address governance of common land. To be sourced from Agrawal 2001 or Ostrom 1990 once read on disk</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J232"/>
+  <autoFilter ref="A1:J235"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15375,7 +15525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C148"/>
+  <dimension ref="A1:C151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -15913,7 +16063,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001 (natural capital); Lax &amp; Krug</t>
+          <t>Krantz 2001, natural capital: resource stocks from which resource flows are derived; item wording is ours</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -17098,7 +17248,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
+          <t>Pelz et al. 2024, Energy Policy 186:113973 (concept: perceived effect on livelihoods; wording ours)</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
@@ -17106,14 +17256,14 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>trek_dependent</t>
+          <t>ropeway_expect_work</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
+          <t>Pelz et al. 2024, Energy Policy 186:113973 (concept: local vs outside benefit; wording ours)</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
@@ -17121,14 +17271,14 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>job_situation</t>
+          <t>ropeway_expect_jobs</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
+          <t>Pelz et al. 2024, Energy Policy 186:113973 (Fig. 4B, trust in the company; wording ours)</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
@@ -17136,14 +17286,14 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>job_permanence</t>
+          <t>ropeway_trust</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
+          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
@@ -17151,14 +17301,14 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>contract_status</t>
+          <t>trek_dependent</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
@@ -17166,14 +17316,14 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>workplace_registered</t>
+          <t>job_situation</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
@@ -17181,14 +17331,14 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>pension_contrib</t>
+          <t>job_permanence</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
@@ -17196,14 +17346,14 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>work_health_ins</t>
+          <t>contract_status</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
@@ -17211,14 +17361,14 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>leave_rights</t>
+          <t>workplace_registered</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
@@ -17226,14 +17376,14 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>injured_ever</t>
+          <t>pension_contrib</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
@@ -17241,14 +17391,14 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>wants_more_work</t>
+          <t>work_health_ins</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
@@ -17256,14 +17406,14 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>more_hours_day</t>
+          <t>leave_rights</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
@@ -17271,14 +17421,14 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>months_looked_for_work</t>
+          <t>injured_ever</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
@@ -17286,14 +17436,14 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>first_job_ever</t>
+          <t>wants_more_work</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 employment table, occupational status (1/8)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
@@ -17301,14 +17451,14 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>higher_ed</t>
+          <t>more_hours_day</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 employment table, employment security (1/8)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
@@ -17316,14 +17466,14 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>social_security_any</t>
+          <t>months_looked_for_work</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
@@ -17331,14 +17481,14 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>tk_load</t>
+          <t>first_job_ever</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
+          <t>Apablaza et al. 2026, Appendix 2 employment table, occupational status (1/8)</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
@@ -17346,14 +17496,14 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>tk_drive</t>
+          <t>higher_ed</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
+          <t>Apablaza et al. 2026, Appendix 2 employment table, employment security (1/8)</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
@@ -17361,14 +17511,14 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>tk_engine</t>
+          <t>social_security_any</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
+          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
         </is>
       </c>
       <c r="B133" s="2" t="n">
@@ -17376,14 +17526,14 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>tk_electric</t>
+          <t>tk_load</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
+          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
         </is>
       </c>
       <c r="B134" s="2" t="n">
@@ -17391,14 +17541,14 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>tk_safety</t>
+          <t>tk_drive</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
       <c r="B135" s="2" t="n">
@@ -17406,14 +17556,14 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>tk_sell</t>
+          <t>tk_engine</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Autor and Handel 2013; NCO 5131.0401</t>
+          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
@@ -17421,14 +17571,14 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>tk_cash</t>
+          <t>tk_electric</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>NCO 5120.0300 cook</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
@@ -17436,14 +17586,14 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>tk_cook</t>
+          <t>tk_safety</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
+          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
@@ -17451,14 +17601,14 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>tk_serve</t>
+          <t>tk_sell</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
+          <t>Autor and Handel 2013; NCO 5131.0401</t>
         </is>
       </c>
       <c r="B139" s="2" t="n">
@@ -17466,14 +17616,14 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>tk_clean</t>
+          <t>tk_cash</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
+          <t>NCO 5120.0300 cook</t>
         </is>
       </c>
       <c r="B140" s="2" t="n">
@@ -17481,14 +17631,14 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>tk_guide</t>
+          <t>tk_cook</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>NCO 8343.1700 ropeway operator</t>
+          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="n">
@@ -17496,14 +17646,14 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>tk_coord</t>
+          <t>tk_serve</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Level ladder without licences: people drive without holding a licence</t>
+          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
@@ -17511,14 +17661,14 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>drove_twowheeler</t>
+          <t>tk_clean</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001 (natural capital); Lax &amp; Krug (firewood as the core forest indicator)</t>
+          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
         </is>
       </c>
       <c r="B143" s="2" t="n">
@@ -17526,14 +17676,14 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>cpr_firewood</t>
+          <t>tk_guide</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Lax &amp; Krug (forest produce as food and medicine)</t>
+          <t>NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
       <c r="B144" s="2" t="n">
@@ -17541,14 +17691,14 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>cpr_forest_produce</t>
+          <t>tk_coord</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001 (claims and access)</t>
+          <t>Level ladder without licences: people drive without holding a licence</t>
         </is>
       </c>
       <c r="B145" s="2" t="n">
@@ -17556,14 +17706,14 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>cpr_restricted</t>
+          <t>drove_twowheeler</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001 (access); Module J context</t>
+          <t>Krantz 2001, natural capital: resource stocks from which resource flows are derived (definitions list); item wording is ours</t>
         </is>
       </c>
       <c r="B146" s="2" t="n">
@@ -17571,14 +17721,14 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>cpr_lost_access</t>
+          <t>cpr_firewood</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001 (natural capital: water); Lax &amp; Krug (water resources)</t>
+          <t>Krantz 2001, natural capital (resource flows from stocks); item wording is ours</t>
         </is>
       </c>
       <c r="B147" s="2" t="n">
@@ -17586,14 +17736,14 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>cpr_water_route</t>
+          <t>cpr_forest_produce</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001 (institutions); Lax &amp; Krug (adherence to rules)</t>
+          <t>Krantz 2001, access ('the opportunity in practice to use a resource') and claims ('demands and appeals'); item wording is ours</t>
         </is>
       </c>
       <c r="B148" s="2" t="n">
@@ -17601,12 +17751,57 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
+          <t>cpr_restricted</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Krantz 2001, access (as above); the ropeway link is the project's own</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>cpr_lost_access</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Krantz 2001, natural capital (water) and access ('the opportunity in practice to use a resource'); item wording is ours</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>cpr_water_route</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>NO SOURCE ON DISK YET: Krantz does not address governance of common land. To be sourced from Agrawal 2001 or Ostrom 1990 once read on disk</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
           <t>cpr_governance</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C148"/>
+  <autoFilter ref="A1:C151"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17804,7 +17999,7 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -17860,7 +18055,7 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/Question_register.xlsx
+++ b/Question_register.xlsx
@@ -8318,7 +8318,7 @@
       <c r="I172" s="2" t="inlineStr"/>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, which is not included in this instrument. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking.</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       <c r="I173" s="2" t="inlineStr"/>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, which is not included in this instrument. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking.</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       <c r="I174" s="2" t="inlineStr"/>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, which is not included in this instrument. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking.</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8444,7 @@
       <c r="I175" s="2" t="inlineStr"/>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, which is not included in this instrument. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking.</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       <c r="I176" s="2" t="inlineStr"/>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, which is not included in this instrument. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking.</t>
         </is>
       </c>
     </row>
@@ -8528,7 +8528,7 @@
       <c r="I177" s="2" t="inlineStr"/>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, which is not included in this instrument. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking.</t>
         </is>
       </c>
     </row>
@@ -8570,7 +8570,7 @@
       <c r="I178" s="2" t="inlineStr"/>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, which is not included in this instrument. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking.</t>
         </is>
       </c>
     </row>
@@ -8612,7 +8612,7 @@
       <c r="I179" s="2" t="inlineStr"/>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, which is not included in this instrument. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking.</t>
         </is>
       </c>
     </row>
@@ -8654,7 +8654,7 @@
       <c r="I180" s="2" t="inlineStr"/>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, which is not included in this instrument. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking.</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       <c r="I181" s="2" t="inlineStr"/>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, which is not included in this instrument. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking.</t>
         </is>
       </c>
     </row>
@@ -15583,7 +15583,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, which is not included in this instrument. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking.</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">

--- a/Question_register.xlsx
+++ b/Question_register.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modules" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$237</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$238</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Constructed variables'!$A$1:$F$140</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Literature'!$A$1:$C$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Literature'!$A$1:$C$154</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Modules'!$A$1:$C$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J237"/>
+  <dimension ref="A1:J238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1428,29 +1428,37 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>n_other_activities</t>
+          <t>wage_employer</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Besides your main work, how many OTHER paid activities or income-generating activities do you have? (0 if none. For example, a shop owner who also rents out a pony and drives in the off-season would say 2.)</t>
+          <t>Who employs you? A private company; a government or public body; a household (domestic work); a contractor or agent; or an individual employer?</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>अपने मुख्य काम के अलावा, आप और कितने काम करते हैं जिनसे पैसा आता है? (अगर कोई नहीं तो 0। जैसे, दुकान वाला जो घोड़ा भी किराये पर देता है और जाड़ों में गाड़ी चलाता है, वह 2 बताएगा।)</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
+          <t>आपको काम पर कौन रखता है? कोई निजी कंपनी; सरकारी या सार्वजनिक विभाग; कोई घर (घरेलू काम); ठेकेदार या एजेंट; या कोई व्यक्ति जो सीधे पैसे देता है?</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1 Private company | 2 Government or public body | 3 A household (domestic work) | 4 A contractor or agent | 5 An individual employer | 97 Don't know</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if employment_type is 3 or 4 (regular or casual wage worker)</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Project design (multiple job-holding, common in the Yatra economy)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q8 (shortened to wage workers); categories ours</t>
         </is>
       </c>
     </row>
@@ -1470,34 +1478,26 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>other_activity_types</t>
+          <t>n_other_activities</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>select multiple</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Which ones are they? Check every one that applies. Ask and code the closest group for each; do not read the list aloud unless needed.</t>
+          <t>Besides your main work, how many OTHER paid activities or income-generating activities do you have? (0 if none. For example, a shop owner who also rents out a pony and drives in the off-season would say 2.)</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>वे कौन-कौन से काम हैं? जो-जो लागू हो, सब बताइए।</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>1 Pony/mule worker (works the animals, does not own them) | 2 Pony/mule owner (owns the animals) | 3 Porter (carries on own back/shoulders - goods, luggage, or a person in a kandi) | 4 Palki / dandi bearer (carries a person on a palanquin, as part of a team) | 5 Dhaba, tea stall or food stall WORKER (prepared food or tea) | 6 Dhaba, tea stall or food stall OWNER (prepared food or tea) | 7 Shop WORKER (goods: prasad, puja items, clothes, general store) | 8 Shop OWNER (goods, not prepared food) | 9 Hotel / lodge WORKER | 10 Hotel / lodge OWNER | 11 Driver (any motor vehicle) | 12 Guide | 13 Wage labourer (construction, loading, odd jobs) | 14 Other</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if n_other_activities &gt; 0</t>
-        </is>
-      </c>
+          <t>अपने मुख्य काम के अलावा, आप और कितने काम करते हैं जिनसे पैसा आता है? (अगर कोई नहीं तो 0। जैसे, दुकान वाला जो घोड़ा भी किराये पर देता है और जाड़ों में गाड़ी चलाता है, वह 2 बताएगा।)</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
           <t>Project design (multiple job-holding, common in the Yatra economy)</t>
@@ -1520,25 +1520,29 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>other_activity_income_pm</t>
+          <t>other_activity_types</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>select multiple</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Taking all of that other work together, about how much do you usually earn from it in a month? (Rs)</t>
+          <t>Which ones are they? Check every one that applies. Ask and code the closest group for each; do not read the list aloud unless needed.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>वह सारा दूसरा काम मिलाकर, महीने में लगभग कितना कमा लेते हैं? (रुपये)</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
+          <t>वे कौन-कौन से काम हैं? जो-जो लागू हो, सब बताइए।</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1 Pony/mule worker (works the animals, does not own them) | 2 Pony/mule owner (owns the animals) | 3 Porter (carries on own back/shoulders - goods, luggage, or a person in a kandi) | 4 Palki / dandi bearer (carries a person on a palanquin, as part of a team) | 5 Dhaba, tea stall or food stall WORKER (prepared food or tea) | 6 Dhaba, tea stall or food stall OWNER (prepared food or tea) | 7 Shop WORKER (goods: prasad, puja items, clothes, general store) | 8 Shop OWNER (goods, not prepared food) | 9 Hotel / lodge WORKER | 10 Hotel / lodge OWNER | 11 Driver (any motor vehicle) | 12 Guide | 13 Wage labourer (construction, loading, odd jobs) | 14 Other</t>
+        </is>
+      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Ask only if n_other_activities &gt; 0</t>
@@ -1546,7 +1550,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Project design (multiple job-holding)</t>
+          <t>Project design (multiple job-holding, common in the Yatra economy)</t>
         </is>
       </c>
     </row>
@@ -1566,33 +1570,33 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>tenure_under_1</t>
+          <t>other_activity_income_pm</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Have you been in this job for less than one year?</t>
+          <t>Taking all of that other work together, about how much do you usually earn from it in a month? (Rs)</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>क्या आप इस काम में एक साल से कम से हैं?</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
+          <t>वह सारा दूसरा काम मिलाकर, महीने में लगभग कितना कमा लेते हैं? (रुपये)</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if n_other_activities &gt; 0</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q10 (screen); Table 3 (stability)</t>
+          <t>Project design (multiple job-holding)</t>
         </is>
       </c>
     </row>
@@ -1612,33 +1616,33 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>years_current_job</t>
+          <t>tenure_under_1</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>If one year or more: how many years have you been in this job? Write it as a decimal if needed, for example 1.5 for one year and six months.</t>
+          <t>Have you been in this job for less than one year?</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>अगर एक साल या ज़्यादा: आप इस काम में कितने साल से हैं? दशमलव में लिखें, जैसे डेढ़ साल के लिए 1.5।</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if tenure_under_1 = 0 (one year or more)</t>
-        </is>
-      </c>
+          <t>क्या आप इस काम में एक साल से कम से हैं?</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q10; Table 3 (stability)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q10 (screen); Table 3 (stability)</t>
         </is>
       </c>
     </row>
@@ -1658,29 +1662,33 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>hours_day_yatra</t>
+          <t>years_current_job</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>number</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>In the Yatra season, on a normal working day, how many hours do you work in total, across all your work?</t>
+          <t>If one year or more: how many years have you been in this job? Write it as a decimal if needed, for example 1.5 for one year and six months.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम में, आम दिन में आप कुल कितने घंटे काम करते हैं, सारे कामों को मिलाकर?</t>
+          <t>अगर एक साल या ज़्यादा: आप इस काम में कितने साल से हैं? दशमलव में लिखें, जैसे डेढ़ साल के लिए 1.5।</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if tenure_under_1 = 0 (one year or more)</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q13 (decomposed into hours/day x days/week rather than asked as one weekly figure, for ease of recall)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q10; Table 3 (stability)</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1708,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>days_week_yatra</t>
+          <t>hours_day_yatra</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1710,12 +1718,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>How many days a week do you usually work in the season?</t>
+          <t>In the Yatra season, on a normal working day, how many hours do you work in total, across all your work?</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>सीज़न में आप हफ़्ते में कितने दिन काम करते हैं?</t>
+          <t>यात्रा के मौसम में, आम दिन में आप कुल कितने घंटे काम करते हैं, सारे कामों को मिलाकर?</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -1742,33 +1750,29 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>prev_occ_change</t>
+          <t>days_week_yatra</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>In the last ten years, did you change your main kind of work?</t>
+          <t>How many days a week do you usually work in the season?</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>पिछले दस साल में, क्या आपने अपना मुख्य काम बदला?</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
+          <t>सीज़न में आप हफ़्ते में कितने दिन काम करते हैं?</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Occupational mobility check; job-history item</t>
+          <t>Apablaza et al. 2026 Q13 (decomposed into hours/day x days/week rather than asked as one weekly figure, for ease of recall)</t>
         </is>
       </c>
     </row>
@@ -1788,33 +1792,33 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>prev_occ</t>
+          <t>prev_occ_change</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>What was your previous main work? Write down exactly what they say, in their words — do not pick from a list.</t>
+          <t>In the last ten years, did you change your main kind of work?</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>इससे पहले आपका मुख्य काम क्या था?</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if prev_occ_change = 1</t>
-        </is>
-      </c>
+          <t>पिछले दस साल में, क्या आपने अपना मुख्य काम बदला?</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010 (observed moves are systematically shorter than random moves — the validation test for a task-distance measure); coded to NCO-2015 in the office</t>
+          <t>Occupational mobility check; job-history item</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1838,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>target_occ</t>
+          <t>prev_occ</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1844,19 +1848,23 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>If you could not continue this work at all, what work would you move to instead? Write down exactly what they say, in their words — do not pick from a list, and do not prompt with examples.</t>
+          <t>What was your previous main work? Write down exactly what they say, in their words — do not pick from a list.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>अगर यह काम बिल्कुल बंद हो जाए, तो आप कौन सा काम करेंगे?</t>
+          <t>इससे पहले आपका मुख्य काम क्या था?</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if prev_occ_change = 1</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Project design (stated destination, for the structural-displacement analysis); coded to NCO-2015 in the office</t>
+          <t>Gathmann and Schonberg 2010 (observed moves are systematically shorter than random moves — the validation test for a task-distance measure); coded to NCO-2015 in the office</t>
         </is>
       </c>
     </row>
@@ -1876,37 +1884,29 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>prev_occ_reason</t>
+          <t>target_occ</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>What was the main reason you changed?</t>
+          <t>If you could not continue this work at all, what work would you move to instead? Write down exactly what they say, in their words — do not pick from a list, and do not prompt with examples.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>काम बदलने की मुख्य वजह क्या थी?</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>1 Better income | 2 Lost the previous work | 3 Work ended with the season | 4 Family reasons | 5 Health or injury | 6 Other</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if prev_occ_change = 1</t>
-        </is>
-      </c>
+          <t>अगर यह काम बिल्कुल बंद हो जाए, तो आप कौन सा काम करेंगे?</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Job-history item</t>
+          <t>Project design (stated destination, for the structural-displacement analysis); coded to NCO-2015 in the office</t>
         </is>
       </c>
     </row>
@@ -1926,33 +1926,37 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>training_received</t>
+          <t>prev_occ_reason</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Apart from school and college, have you ever completed any training course or apprenticeship?</t>
+          <t>What was the main reason you changed?</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>स्कूल और कॉलेज की पढ़ाई छोड़कर, क्या आपने कभी कोई ट्रेनिंग या सीखने का कोर्स पूरा किया है?</t>
+          <t>काम बदलने की मुख्य वजह क्या थी?</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
+          <t>1 Better income | 2 Lost the previous work | 3 Work ended with the season | 4 Family reasons | 5 Health or injury | 6 Other</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if prev_occ_change = 1</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>STEP module 2; Chaudhuri et al. 2002 adaptive-capacity covariate</t>
+          <t>Job-history item</t>
         </is>
       </c>
     </row>
@@ -1962,43 +1966,43 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Monthly calendar of work and income</t>
+          <t>Work and work history</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>status_m5</t>
+          <t>training_received</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>In May, what was your main work or activity?</t>
+          <t>Apart from school and college, have you ever completed any training course or apprenticeship?</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>मई में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>स्कूल और कॉलेज की पढ़ाई छोड़कर, क्या आपने कभी कोई ट्रेनिंग या सीखने का कोर्स पूरा किया है?</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (working the season) | 9 Getting ready for the season (not earning from it yet) | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Monthly work calendar; seasonality of consumption and poverty per Dercon and Krishnan 2000 (their design is a three-round panel, not a monthly recall calendar — the calendar format is project design)</t>
+          <t>STEP module 2; Chaudhuri et al. 2002 adaptive-capacity covariate</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2022,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>status_m6</t>
+          <t>status_m5</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2028,12 +2032,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>In June, what was your main work or activity?</t>
+          <t>In May, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>जून में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>मई में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2064,7 +2068,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>status_m7</t>
+          <t>status_m6</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2074,12 +2078,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>In July, what was your main work or activity?</t>
+          <t>In June, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>जुलाई में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>जून में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2110,7 +2114,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>status_m8</t>
+          <t>status_m7</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2120,12 +2124,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>In August, what was your main work or activity?</t>
+          <t>In July, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>अगस्त में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>जुलाई में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2156,7 +2160,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>status_m9</t>
+          <t>status_m8</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2166,12 +2170,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>In September, what was your main work or activity?</t>
+          <t>In August, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>सितंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>अगस्त में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2202,7 +2206,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>status_m10</t>
+          <t>status_m9</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2212,12 +2216,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>In October, what was your main work or activity?</t>
+          <t>In September, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>अक्टूबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>सितंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2248,7 +2252,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>status_m11</t>
+          <t>status_m10</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2258,12 +2262,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>In November, what was your main work or activity?</t>
+          <t>In October, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>नवंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>अक्टूबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2294,7 +2298,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>status_m12</t>
+          <t>status_m11</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2304,12 +2308,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>In December, what was your main work or activity?</t>
+          <t>In November, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>दिसंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>नवंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2340,7 +2344,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>status_m1</t>
+          <t>status_m12</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2350,12 +2354,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>In January, what was your main work or activity?</t>
+          <t>In December, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>जनवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>दिसंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2386,7 +2390,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>status_m2</t>
+          <t>status_m1</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2396,12 +2400,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>In February, what was your main work or activity?</t>
+          <t>In January, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>फ़रवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>जनवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2432,7 +2436,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>status_m3</t>
+          <t>status_m2</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2442,12 +2446,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>In March, what was your main work or activity?</t>
+          <t>In February, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>मार्च में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>फ़रवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2478,7 +2482,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>status_m4</t>
+          <t>status_m3</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2488,12 +2492,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>In April, what was your main work or activity?</t>
+          <t>In March, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>अप्रैल में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>मार्च में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2524,7 +2528,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>knows_monthly_income</t>
+          <t>status_m4</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2534,27 +2538,23 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Can you tell me roughly what you earned in each month of the past year, or would it be easier to give one total for the whole year?</t>
+          <t>In April, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>क्या आप हर महीने की कमाई अलग-अलग बता सकते हैं, या पूरे साल का एक जोड़ बताना आसान रहेगा?</t>
+          <t>अप्रैल में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1 Month by month | 0 One total for the whole year</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Ask everyone; may be left blank if the respondent declines to discuss earnings, and both earnings routes then stay shut</t>
-        </is>
-      </c>
+          <t>1 Yatra work (working the season) | 9 Getting ready for the season (not earning from it yet) | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q14/Q15 (the 'does not know' route out of monthly earnings)</t>
+          <t>Monthly work calendar; seasonality of consumption and poverty per Dercon and Krishnan 2000 (their design is a three-round panel, not a monthly recall calendar — the calendar format is project design)</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>earnings_range</t>
+          <t>knows_monthly_income</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2584,27 +2584,27 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Which range is closest to what you usually earn in a month from work? Under Rs 5,000; Rs 5,000 to 10,000; Rs 10,000 to 20,000; Rs 20,000 or more; or don't know?</t>
+          <t>Can you tell me roughly what you earned in each month of the past year, or would it be easier to give one total for the whole year?</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>आपकी एक महीने की कमाई लगभग किस दायरे में है? 5,000 रुपये से कम; 5,000 से 10,000; 10,000 से 20,000; 20,000 या उससे ज़्यादा; या पता नहीं?</t>
+          <t>क्या आप हर महीने की कमाई अलग-अलग बता सकते हैं, या पूरे साल का एक जोड़ बताना आसान रहेगा?</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1 Under Rs 5,000 | 2 Rs 5,000 to 10,000 | 3 Rs 10,000 to 20,000 | 4 Rs 20,000 or more | 97 Don't know</t>
+          <t>1 Month by month | 0 One total for the whole year</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 0 (monthly figure not known or declined)</t>
+          <t>Ask everyone; may be left blank if the respondent declines to discuss earnings, and both earnings routes then stay shut</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q15; bands to check</t>
+          <t>Apablaza et al. 2026 Q14/Q15 (the 'does not know' route out of monthly earnings)</t>
         </is>
       </c>
     </row>
@@ -2624,33 +2624,37 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>income_m5</t>
+          <t>earnings_range</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in May, after costs? (Rs)</t>
+          <t>Which range is closest to what you usually earn in a month from work? Under Rs 5,000; Rs 5,000 to 10,000; Rs 10,000 to 20,000; Rs 20,000 or more; or don't know?</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>मई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr"/>
+          <t>आपकी एक महीने की कमाई लगभग किस दायरे में है? 5,000 रुपये से कम; 5,000 से 10,000; 10,000 से 20,000; 20,000 या उससे ज़्यादा; या पता नहीं?</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>1 Under Rs 5,000 | 2 Rs 5,000 to 10,000 | 3 Rs 10,000 to 20,000 | 4 Rs 20,000 or more | 97 Don't know</t>
+        </is>
+      </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m5 = 8 (no paid work); may be left blank</t>
+          <t>Ask only if knows_monthly_income = 0 (monthly figure not known or declined)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q14 (monthly earnings), asked month by month to avoid heaping on one typical figure</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q15; bands to check</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2674,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>income_m6</t>
+          <t>income_m5</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2680,18 +2684,18 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in June, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in May, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>जून में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>मई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m6 = 8 (no paid work); may be left blank</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m5 = 8 (no paid work); may be left blank</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -2716,7 +2720,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>income_m7</t>
+          <t>income_m6</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2726,18 +2730,18 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in July, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in June, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>जुलाई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जून में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m7 = 8 (no paid work); may be left blank</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m6 = 8 (no paid work); may be left blank</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -2762,7 +2766,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>income_m8</t>
+          <t>income_m7</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2772,18 +2776,18 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in August, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in July, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>अगस्त में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जुलाई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m8 = 8 (no paid work); may be left blank</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m7 = 8 (no paid work); may be left blank</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -2808,7 +2812,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>income_m9</t>
+          <t>income_m8</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2818,18 +2822,18 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in September, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in August, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>सितंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अगस्त में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m9 = 8 (no paid work); may be left blank</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m8 = 8 (no paid work); may be left blank</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -2854,7 +2858,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>income_m10</t>
+          <t>income_m9</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2864,18 +2868,18 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in October, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in September, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>अक्टूबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>सितंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m10 = 8 (no paid work); may be left blank</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m9 = 8 (no paid work); may be left blank</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -2900,7 +2904,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>income_m11</t>
+          <t>income_m10</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2910,18 +2914,18 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in November, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in October, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>नवंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अक्टूबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m11 = 8 (no paid work); may be left blank</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m10 = 8 (no paid work); may be left blank</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -2946,7 +2950,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>income_m12</t>
+          <t>income_m11</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2956,18 +2960,18 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in December, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in November, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>दिसंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>नवंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m12 = 8 (no paid work); may be left blank</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m11 = 8 (no paid work); may be left blank</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -2992,7 +2996,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>income_m1</t>
+          <t>income_m12</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3002,18 +3006,18 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in January, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in December, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>जनवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>दिसंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m1 = 8 (no paid work); may be left blank</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m12 = 8 (no paid work); may be left blank</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3038,7 +3042,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>income_m2</t>
+          <t>income_m1</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3048,18 +3052,18 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in February, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in January, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>फ़रवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जनवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m2 = 8 (no paid work); may be left blank</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m1 = 8 (no paid work); may be left blank</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3084,7 +3088,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>income_m3</t>
+          <t>income_m2</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3094,18 +3098,18 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in March, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in February, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>मार्च में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>फ़रवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m3 = 8 (no paid work); may be left blank</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m2 = 8 (no paid work); may be left blank</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -3130,7 +3134,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>income_m4</t>
+          <t>income_m3</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3140,18 +3144,18 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in April, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in March, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>अप्रैल में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>मार्च में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m4 = 8 (no paid work); may be left blank</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m3 = 8 (no paid work); may be left blank</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -3176,7 +3180,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>income_annual_total</t>
+          <t>income_m4</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3186,23 +3190,23 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Thinking of the whole past year, about how much did you earn in total from all your work, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in April, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>पूरे पिछले साल को मिलाकर, सारे काम से ख़र्चा निकालकर आपने कुल कितना कमाया? (रुपये)</t>
+          <t>अप्रैल में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 0; may be left blank</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m4 = 8 (no paid work); may be left blank</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q15 (fallback when monthly earnings are not known), adapted to an annual total for a seasonal workforce</t>
+          <t>Apablaza et al. 2026 Q14 (monthly earnings), asked month by month to avoid heaping on one typical figure</t>
         </is>
       </c>
     </row>
@@ -3222,22 +3226,22 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>pct_income_yatra</t>
+          <t>income_annual_total</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Out of every 100 rupees you earned in the whole year, how many came from your Yatra work? (The rest is counted as coming from your other work.)</t>
+          <t>Thinking of the whole past year, about how much did you earn in total from all your work, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>पूरे साल में आपने जो 100 रुपये कमाए, उनमें से कितने यात्रा के काम से आए? (बाकी दूसरे काम का माना जाएगा।)</t>
+          <t>पूरे पिछले साल को मिलाकर, सारे काम से ख़र्चा निकालकर आपने कुल कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -3248,7 +3252,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Project design (the Yatra / non-Yatra split needed to reweight an annual total onto the work calendar)</t>
+          <t>Apablaza et al. 2026 Q15 (fallback when monthly earnings are not known), adapted to an annual total for a seasonal workforce</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3272,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>hours_day_offseason</t>
+          <t>pct_income_yatra</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3278,23 +3282,23 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>In the months when the Yatra is closed and you are doing other work, on a normal working day, how many hours do you work in total?</t>
+          <t>Out of every 100 rupees you earned in the whole year, how many came from your Yatra work? (The rest is counted as coming from your other work.)</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>जिन महीनों में यात्रा बंद रहती है और आप कोई दूसरा काम करते हैं, उनमें आम दिन में आप कुल कितने घंटे काम करते हैं?</t>
+          <t>पूरे साल में आपने जो 100 रुपये कमाए, उनमें से कितने यात्रा के काम से आए? (बाकी दूसरे काम का माना जाएगा।)</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Ask only if any month in the calendar is other paid work (status 2 to 7)</t>
+          <t>Ask only if knows_monthly_income = 0; may be left blank</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season (decomposed as hours/day x days/week, as in the Yatra-season pair)</t>
+          <t>Project design (the Yatra / non-Yatra split needed to reweight an annual total onto the work calendar)</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3318,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>days_week_offseason</t>
+          <t>hours_day_offseason</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3324,12 +3328,12 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>In those months, how many days a week do you usually work?</t>
+          <t>In the months when the Yatra is closed and you are doing other work, on a normal working day, how many hours do you work in total?</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>उन महीनों में आप हफ़्ते में कितने दिन काम करते हैं?</t>
+          <t>जिन महीनों में यात्रा बंद रहती है और आप कोई दूसरा काम करते हैं, उनमें आम दिन में आप कुल कितने घंटे काम करते हैं?</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -3340,7 +3344,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season</t>
+          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season (decomposed as hours/day x days/week, as in the Yatra-season pair)</t>
         </is>
       </c>
     </row>
@@ -3350,43 +3354,43 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Migration, home place and remittances</t>
+          <t>Monthly calendar of work and income</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>origin</t>
+          <t>days_week_offseason</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Where is your permanent home?</t>
+          <t>In those months, how many days a week do you usually work?</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>आपका पक्का घर कहाँ है?</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>1 Local (same district) | 2 Other Uttarakhand district | 3 Other Indian state | 4 Nepal</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
+          <t>उन महीनों में आप हफ़्ते में कितने दिन काम करते हैं?</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if any month in the calendar is other paid work (status 2 to 7)</t>
+        </is>
+      </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>Project design (distance bucket); NOT an NSS classification — the earlier citation to one was withdrawn 2026-09-28, no NSS schedule is held by this project</t>
+          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3410,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>home_state</t>
+          <t>origin</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3416,27 +3420,23 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Which state is your permanent home in?</t>
+          <t>Where is your permanent home?</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>वह घर किस राज्य में है? (अगर भारत से बाहर है तो वह बताइए।)</t>
+          <t>आपका पक्का घर कहाँ है?</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>1 Andhra Pradesh | 2 Arunachal Pradesh | 3 Assam | 4 Bihar | 5 Chhattisgarh | 6 Goa | 7 Gujarat | 8 Haryana | 9 Himachal Pradesh | 10 Jharkhand | 11 Karnataka | 12 Kerala | 13 Madhya Pradesh | 14 Maharashtra | 15 Manipur | 16 Meghalaya | 17 Mizoram | 18 Nagaland | 19 Odisha | 20 Punjab | 21 Rajasthan | 22 Sikkim | 23 Tamil Nadu | 24 Telangana | 25 Tripura | 26 Uttar Pradesh | 28 West Bengal | 29 Andaman and Nicobar Islands | 30 Chandigarh | 31 Dadra and Nagar Haveli and Daman and Diu | 32 Delhi | 33 Jammu and Kashmir | 34 Ladakh | 35 Lakshadweep | 36 Puducherry</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if origin = 3 (another Indian state)</t>
-        </is>
-      </c>
+          <t>1 Local (same district) | 2 Other Uttarakhand district | 3 Other Indian state | 4 Nepal</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Standard state/UT classification; needed to apply the right poverty line per respondent</t>
+          <t>Project design (distance bucket); NOT an NSS classification — the earlier citation to one was withdrawn 2026-09-28, no NSS schedule is held by this project</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>home_rural_urban</t>
+          <t>home_state</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3466,23 +3466,27 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Is that home in a village, or in a town or city?</t>
+          <t>Which state is your permanent home in?</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>वह घर गाँव में है, या क़स्बे या शहर में?</t>
+          <t>वह घर किस राज्य में है? (अगर भारत से बाहर है तो वह बताइए।)</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>1 Village (rural) | 2 Town or city (urban)</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr"/>
+          <t>1 Andhra Pradesh | 2 Arunachal Pradesh | 3 Assam | 4 Bihar | 5 Chhattisgarh | 6 Goa | 7 Gujarat | 8 Haryana | 9 Himachal Pradesh | 10 Jharkhand | 11 Karnataka | 12 Kerala | 13 Madhya Pradesh | 14 Maharashtra | 15 Manipur | 16 Meghalaya | 17 Mizoram | 18 Nagaland | 19 Odisha | 20 Punjab | 21 Rajasthan | 22 Sikkim | 23 Tamil Nadu | 24 Telangana | 25 Tripura | 26 Uttar Pradesh | 28 West Bengal | 29 Andaman and Nicobar Islands | 30 Chandigarh | 31 Dadra and Nagar Haveli and Daman and Diu | 32 Delhi | 33 Jammu and Kashmir | 34 Ladakh | 35 Lakshadweep | 36 Puducherry</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if origin = 3 (another Indian state)</t>
+        </is>
+      </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Rural and urban poverty lines (Sethu et al. 2024)</t>
+          <t>Standard state/UT classification; needed to apply the right poverty line per respondent</t>
         </is>
       </c>
     </row>
@@ -3502,33 +3506,33 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>resp_returns_at_closure</t>
+          <t>home_rural_urban</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>When the Yatra closes for the season, do YOU go to your home place?</t>
+          <t>Is that home in a village, or in a town or city?</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा का मौसम ख़त्म हो जाता है, तो क्या आप अपने घर चले जाते हैं?</t>
+          <t>वह घर गाँव में है, या क़स्बे या शहर में?</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 Village (rural) | 2 Town or city (urban)</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>Project design; categories from the pilot's own residency_pattern distribution (n=46)</t>
+          <t>Rural and urban poverty lines (Sethu et al. 2024)</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3552,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>hh_at_home_place</t>
+          <t>resp_returns_at_closure</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3558,12 +3562,12 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>For most of the year, do the rest of your household live in your home village or town?</t>
+          <t>When the Yatra closes for the season, do YOU go to your home place?</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>साल के ज़्यादातर समय, क्या आपके घर के बाक़ी लोग आपके गाँव या शहर में ही रहते हैं?</t>
+          <t>जब यात्रा का मौसम ख़त्म हो जाता है, तो क्या आप अपने घर चले जाते हैं?</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3574,7 +3578,7 @@
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>Project design (split-household measurement, underpinning Module E)</t>
+          <t>Project design; categories from the pilot's own residency_pattern distribution (n=46)</t>
         </is>
       </c>
     </row>
@@ -3594,29 +3598,33 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>remit_out_yatra_pm</t>
+          <t>hh_at_home_place</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much money do you usually send to family or others living elsewhere? (Rs, 0 if none)</t>
+          <t>For most of the year, do the rest of your household live in your home village or town?</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप घर या कहीं और रहने वालों को कितना पैसा भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr"/>
+          <t>साल के ज़्यादातर समय, क्या आपके घर के बाक़ी लोग आपके गाँव या शहर में ही रहते हैं?</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>Project design (amount only; frequency dropped for length). A previous citation to NSS 64th Round practice was withdrawn 2026-09-28: no NSS schedule is held by this project and it could not be checked</t>
+          <t>Project design (split-household measurement, underpinning Module E)</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3644,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>remit_out_offseason_pm</t>
+          <t>remit_out_yatra_pm</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3646,20 +3654,16 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much do you usually send? (Rs, 0 if none)</t>
+          <t>In a normal month during the Yatra season, how much money do you usually send to family or others living elsewhere? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप घर या कहीं और रहने वालों को कितना पैसा भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if resp_returns_at_closure = 0 (he stays away when the Yatra closes)</t>
-        </is>
-      </c>
+      <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr">
         <is>
           <t>Project design (amount only; frequency dropped for length). A previous citation to NSS 64th Round practice was withdrawn 2026-09-28: no NSS schedule is held by this project and it could not be checked</t>
@@ -3682,37 +3686,33 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>remit_mode</t>
+          <t>remit_out_offseason_pm</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>How do you usually send it?</t>
+          <t>In a normal month when the Yatra is closed, how much do you usually send? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>आप पैसा आम तौर पर कैसे भेजते हैं?</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>1 From my own phone (UPI or net banking) | 2 In person at a bank branch or bank mitra / CSP | 3 Money order or post office | 4 Sent with someone going home | 5 Carried it myself | 6 Through an agent or middleman | 7 Other</t>
-        </is>
-      </c>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Ask only if remit_out_yatra_pm &gt; 0 or remit_out_offseason_pm &gt; 0</t>
+          <t>Ask only if resp_returns_at_closure = 0 (he stays away when the Yatra closes)</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Project design (remittance channel as a financial-inclusion and cost measure)</t>
+          <t>Project design (amount only; frequency dropped for length). A previous citation to NSS 64th Round practice was withdrawn 2026-09-28: no NSS schedule is held by this project and it could not be checked</t>
         </is>
       </c>
     </row>
@@ -3732,29 +3732,37 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>remit_in_yatra_pm</t>
+          <t>remit_mode</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much money do you usually receive from family or others? (Rs, 0 if none)</t>
+          <t>How do you usually send it?</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, घरवालों या किसी और से आपको कितना पैसा मिलता है? (रुपये, न मिलता हो तो 0)</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr"/>
+          <t>आप पैसा आम तौर पर कैसे भेजते हैं?</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>1 From my own phone (UPI or net banking) | 2 In person at a bank branch or bank mitra / CSP | 3 Money order or post office | 4 Sent with someone going home | 5 Carried it myself | 6 Through an agent or middleman | 7 Other</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if remit_out_yatra_pm &gt; 0 or remit_out_offseason_pm &gt; 0</t>
+        </is>
+      </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>Project design (amount only; frequency dropped for length). A previous citation to NSS 64th Round practice was withdrawn 2026-09-28: no NSS schedule is held by this project and it could not be checked</t>
+          <t>Project design (remittance channel as a financial-inclusion and cost measure)</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3782,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>remit_in_offseason_pm</t>
+          <t>remit_in_yatra_pm</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3784,12 +3792,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much do you usually receive? (Rs, 0 if none)</t>
+          <t>In a normal month during the Yatra season, how much money do you usually receive from family or others? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना मिलता है? (रुपये, न मिलता हो तो 0)</t>
+          <t>यात्रा के मौसम के आम महीने में, घरवालों या किसी और से आपको कितना पैसा मिलता है? (रुपये, न मिलता हो तो 0)</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -3816,33 +3824,29 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>n_here_season</t>
+          <t>remit_in_offseason_pm</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>During the Yatra season, how many people are you feeding and spending on here, counting yourself?</t>
+          <t>In a normal month when the Yatra is closed, how much do you usually receive? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम में आप यहाँ कितने लोगों का खाना-ख़र्चा चलाते हैं, अपने आप को गिनकर?</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना मिलता है? (रुपये, न मिलता हो तो 0)</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if hh_at_home_place = 1</t>
-        </is>
-      </c>
+      <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>Project design (season-specific denominator for per-capita consumption)</t>
+          <t>Project design (amount only; frequency dropped for length). A previous citation to NSS 64th Round practice was withdrawn 2026-09-28: no NSS schedule is held by this project and it could not be checked</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3866,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>years_coming_here</t>
+          <t>n_here_season</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -3872,23 +3876,23 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>How many years have you been coming here for the Yatra season?</t>
+          <t>During the Yatra season, how many people are you feeding and spending on here, counting yourself?</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>आप कितने सालों से यात्रा के मौसम में यहाँ आ रहे हैं?</t>
+          <t>यात्रा के मौसम में आप यहाँ कितने लोगों का खाना-ख़र्चा चलाते हैं, अपने आप को गिनकर?</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Ask only if resp_returns_at_closure = 1</t>
+          <t>Ask only if hh_at_home_place = 1</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>Project design (duration of the seasonal relationship)</t>
+          <t>Project design (season-specific denominator for per-capita consumption)</t>
         </is>
       </c>
     </row>
@@ -3908,37 +3912,33 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>came_here_reason</t>
+          <t>years_coming_here</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>What was the main reason you first came here to work?</t>
+          <t>How many years have you been coming here for the Yatra season?</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>आप सबसे पहले यहाँ काम करने किस मुख्य वजह से आए थे?</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>1 No work at home | 2 Pay is better here | 3 Family or people from my village were already here | 4 Land at home is too little to live on | 5 Debt to repay | 6 A contractor or agent brought me | 7 Married into / moved with family | 8 Some other reason</t>
-        </is>
-      </c>
+          <t>आप कितने सालों से यात्रा के मौसम में यहाँ आ रहे हैं?</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Ask only if origin is not Local (same district)</t>
+          <t>Ask only if resp_returns_at_closure = 1</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Project design (push/pull as a vulnerability covariate)</t>
+          <t>Project design (duration of the seasonal relationship)</t>
         </is>
       </c>
     </row>
@@ -3958,33 +3958,37 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>came_here_reason_other</t>
+          <t>came_here_reason</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>What was that reason? Write down what they say.</t>
+          <t>What was the main reason you first came here to work?</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>वह वजह क्या थी? जो वे कहें वही लिख लें।</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr"/>
+          <t>आप सबसे पहले यहाँ काम करने किस मुख्य वजह से आए थे?</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>1 No work at home | 2 Pay is better here | 3 Family or people from my village were already here | 4 Land at home is too little to live on | 5 Debt to repay | 6 A contractor or agent brought me | 7 Married into / moved with family | 8 Some other reason</t>
+        </is>
+      </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Ask only if came_here_reason = 8 (some other reason). May be left blank.</t>
+          <t>Ask only if origin is not Local (same district)</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>Project design (catch-all codes lose the case they catch)</t>
+          <t>Project design (push/pull as a vulnerability covariate)</t>
         </is>
       </c>
     </row>
@@ -4004,33 +4008,33 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>worked_away_in_closure</t>
+          <t>came_here_reason_other</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Last year, in the months when the Yatra was closed, did you work away from your home place?</t>
+          <t>What was that reason? Write down what they say.</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>पिछले साल, जिन महीनों में यात्रा बंद थी, क्या आपने अपने घर वाली जगह से बाहर जाकर काम किया?</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr"/>
+          <t>वह वजह क्या थी? जो वे कहें वही लिख लें।</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if came_here_reason = 8 (some other reason). May be left blank.</t>
+        </is>
+      </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Project design (off-season labour migration)</t>
+          <t>Project design (catch-all codes lose the case they catch)</t>
         </is>
       </c>
     </row>
@@ -4050,33 +4054,33 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>closure_work_detail</t>
+          <t>worked_away_in_closure</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Where did you go, and what work did you do there? Write what they say.</t>
+          <t>Last year, in the months when the Yatra was closed, did you work away from your home place?</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>कहाँ गए थे, और वहाँ क्या काम किया? जैसा वे बताएँ वैसा लिख लीजिए।</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if worked_away_in_closure = 1; may be left blank</t>
-        </is>
-      </c>
+          <t>पिछले साल, जिन महीनों में यात्रा बंद थी, क्या आपने अपने घर वाली जगह से बाहर जाकर काम किया?</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>Project design; coded to NCO-2015 in the office</t>
+          <t>Project design (off-season labour migration)</t>
         </is>
       </c>
     </row>
@@ -4096,37 +4100,33 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>left_here_month</t>
+          <t>closure_work_detail</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>In the past year, which month did you last leave here and go to your home place?</t>
+          <t>Where did you go, and what work did you do there? Write what they say.</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>पिछले साल आप यहाँ से आख़िरी बार किस महीने अपने घर गए थे?</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>1 January | 2 February | 3 March | 4 April | 5 May | 6 June | 7 July | 8 August | 9 September | 10 October | 11 November | 12 December</t>
-        </is>
-      </c>
+          <t>कहाँ गए थे, और वहाँ क्या काम किया? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Ask only if resp_returns_at_closure = 1</t>
+          <t>Ask only if worked_away_in_closure = 1; may be left blank</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Project design (measured seasonal base, asked as a spell)</t>
+          <t>Project design; coded to NCO-2015 in the office</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>returned_here_month</t>
+          <t>left_here_month</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>And which month did you come back here?</t>
+          <t>In the past year, which month did you last leave here and go to your home place?</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>और किस महीने आप वापस यहाँ आए?</t>
+          <t>पिछले साल आप यहाँ से आख़िरी बार किस महीने अपने घर गए थे?</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>would_move_for_work</t>
+          <t>returned_here_month</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4206,23 +4206,27 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>If this work here ended, would you go away from your home place to look for work in the coming year?</t>
+          <t>And which month did you come back here?</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>अगर यहाँ का यह काम बंद हो जाए, तो क्या आप आने वाले साल में काम ढूँढने अपने घर से बाहर जाएँगे?</t>
+          <t>और किस महीने आप वापस यहाँ आए?</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr"/>
+          <t>1 January | 2 February | 3 March | 4 April | 5 May | 6 June | 7 July | 8 August | 9 September | 10 October | 11 November | 12 December</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if resp_returns_at_closure = 1</t>
+        </is>
+      </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Project design; horizoned intention item after VASyR 2025 (move_accom_yesno, asked over a stated 6-month horizon)</t>
+          <t>Project design (measured seasonal base, asked as a spell)</t>
         </is>
       </c>
     </row>
@@ -4242,7 +4246,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>migration_referral</t>
+          <t>would_move_for_work</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4252,23 +4256,23 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Who mainly helped you get this work, or arranged it for you?</t>
+          <t>If this work here ended, would you go away from your home place to look for work in the coming year?</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>यहाँ आने या यह काम पकड़ने में मुख्य रूप से किसने मदद की या रास्ता दिखाया: यहाँ पहले से रह रहा कोई घरवाला; कोई दोस्त या जान-पहचान वाला; कोई ठेकेदार या एजेंट; कोई नेता या समाज का बड़ा आदमी; कोई नहीं, आपने खुद ढूँढा; मालिक ने सीधे बुलाया; या कोई और?</t>
+          <t>अगर यहाँ का यह काम बंद हो जाए, तो क्या आप आने वाले साल में काम ढूँढने अपने घर से बाहर जाएँगे?</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>1 A family member already working here | 2 A friend or someone from the village | 3 A thekedar or contractor I now work for | 4 An agent or middleman who placed me (usually for a fee) | 5 No one; I found it myself | 6 The employer called me directly | 7 Someone else</t>
+          <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Project design (referral channel as a proxy for social capital and for placement debt)</t>
+          <t>Project design; horizoned intention item after VASyR 2025 (move_accom_yesno, asked over a stated 6-month horizon)</t>
         </is>
       </c>
     </row>
@@ -4288,33 +4292,33 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>migration_referral_other</t>
+          <t>migration_referral</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Who was it? Write what they say.</t>
+          <t>Who mainly helped you get this work, or arranged it for you?</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>वे कौन थे? जैसा वे बताएँ वैसा लिख लीजिए।</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if migration_referral = 7 (Other); may be left blank</t>
-        </is>
-      </c>
+          <t>यहाँ आने या यह काम पकड़ने में मुख्य रूप से किसने मदद की या रास्ता दिखाया: यहाँ पहले से रह रहा कोई घरवाला; कोई दोस्त या जान-पहचान वाला; कोई ठेकेदार या एजेंट; कोई नेता या समाज का बड़ा आदमी; कोई नहीं, आपने खुद ढूँढा; मालिक ने सीधे बुलाया; या कोई और?</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>1 A family member already working here | 2 A friend or someone from the village | 3 A thekedar or contractor I now work for | 4 An agent or middleman who placed me (usually for a fee) | 5 No one; I found it myself | 6 The employer called me directly | 7 Someone else</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Standard household-survey item</t>
+          <t>Project design (referral channel as a proxy for social capital and for placement debt)</t>
         </is>
       </c>
     </row>
@@ -4324,43 +4328,43 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Household consumption</t>
+          <t>Migration, home place and remittances</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>spend_differs_by_season</t>
+          <t>migration_referral_other</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Leaving aside money you send home — is what your household spends in a normal month during the Yatra season different from what it spends when the Yatra is closed?</t>
+          <t>Who was it? Write what they say.</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>घर भेजे जाने वाले पैसे को छोड़कर — यात्रा के मौसम में आपके घर का महीने का ख़र्च, और जब यात्रा बंद रहती है तब का ख़र्च, क्या अलग-अलग होता है?</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr"/>
+          <t>वे कौन थे? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if migration_referral = 7 (Other); may be left blank</t>
+        </is>
+      </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Project design (respondent-gated seasonal recall); the underlying two-season design follows Beegle et al. 2012 and Deaton and Grosh 2000 on usual-period recall</t>
+          <t>Standard household-survey item</t>
         </is>
       </c>
     </row>
@@ -4380,29 +4384,33 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>cons_staples_yatra_pm</t>
+          <t>spend_differs_by_season</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
+          <t>Leaving aside money you send home — is what your household spends in a normal month during the Yatra season different from what it spends when the Yatra is closed?</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करते हैं? (रुपये)</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr"/>
+          <t>घर भेजे जाने वाले पैसे को छोड़कर — यात्रा के मौसम में आपके घर का महीने का ख़र्च, और जब यात्रा बंद रहती है तब का ख़र्च, क्या अलग-अलग होता है?</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
       <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 5.1-5.3 (30-day); IHDS-II Income and Social Capital Questionnaire, Q14 14.1-14.6 (30-day, same items)</t>
+          <t>Project design (respondent-gated seasonal recall); the underlying two-season design follows Beegle et al. 2012 and Deaton and Grosh 2000 on usual-period recall</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4430,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>cons_staples_offseason_pm</t>
+          <t>cons_staples_yatra_pm</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4432,20 +4440,16 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr"/>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if spend_differs_by_season = 1</t>
-        </is>
-      </c>
+      <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="inlineStr">
         <is>
           <t>HCES 2022-23, MoSPI Appendix A, Sections 5.1-5.3 (30-day); IHDS-II Income and Social Capital Questionnaire, Q14 14.1-14.6 (30-day, same items)</t>
@@ -4468,7 +4472,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>cons_perishables_yatra_pm</t>
+          <t>cons_staples_offseason_pm</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4478,19 +4482,23 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if spend_differs_by_season = 1</t>
+        </is>
+      </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 6.1-6.8 (7-day actual recall in HCES; asked here as a usual monthly figure instead, for the reason above)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 5.1-5.3 (30-day); IHDS-II Income and Social Capital Questionnaire, Q14 14.1-14.6 (30-day, same items)</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4518,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>cons_perishables_offseason_pm</t>
+          <t>cons_perishables_yatra_pm</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4520,20 +4528,16 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if spend_differs_by_season = 1</t>
-        </is>
-      </c>
+      <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr">
         <is>
           <t>HCES 2022-23, MoSPI Appendix A, Sections 6.1-6.8 (7-day actual recall in HCES; asked here as a usual monthly figure instead, for the reason above)</t>
@@ -4556,7 +4560,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>cons_food_own_yatra_pm</t>
+          <t>cons_perishables_offseason_pm</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -4566,19 +4570,23 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>If you (and anyone staying with you here) had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month during the Yatra season? (Rs, 0 if you buy everything)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>अगर आप (और जो यहाँ आपके साथ रहते हैं) अपना खाना ख़ुद न उगाते, न पालते और न किसी से मिलता, तो यात्रा के मौसम के आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if spend_differs_by_season = 1</t>
+        </is>
+      </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Calvo and Dercon 2007; Eze and Iheonu 2025 (non-purchased food, aggregate approach)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 6.1-6.8 (7-day actual recall in HCES; asked here as a usual monthly figure instead, for the reason above)</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4606,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>cons_food_own_offseason_pm</t>
+          <t>cons_food_own_yatra_pm</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -4608,20 +4616,16 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>If your household had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month when the Yatra is closed? (Rs, 0 if you buy everything)</t>
+          <t>If you (and anyone staying with you here) had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month during the Yatra season? (Rs, 0 if you buy everything)</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>अगर आपका घर अपना खाना ख़ुद न उगाता, न पालता और न किसी से मिलता, तो जब यात्रा बंद रहती है उस आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
+          <t>अगर आप (और जो यहाँ आपके साथ रहते हैं) अपना खाना ख़ुद न उगाते, न पालते और न किसी से मिलता, तो यात्रा के मौसम के आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr"/>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if spend_differs_by_season = 1</t>
-        </is>
-      </c>
+      <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr">
         <is>
           <t>Calvo and Dercon 2007; Eze and Iheonu 2025 (non-purchased food, aggregate approach)</t>
@@ -4644,7 +4648,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>cons_food_out_yatra_pm</t>
+          <t>cons_food_own_offseason_pm</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -4654,19 +4658,23 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
+          <t>If your household had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month when the Yatra is closed? (Rs, 0 if you buy everything)</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>अगर आपका घर अपना खाना ख़ुद न उगाता, न पालता और न किसी से मिलता, तो जब यात्रा बंद रहती है उस आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if spend_differs_by_season = 1</t>
+        </is>
+      </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 7.1 'served processed food' (7-day in HCES; usual monthly here)</t>
+          <t>Calvo and Dercon 2007; Eze and Iheonu 2025 (non-purchased food, aggregate approach)</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4694,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>cons_food_out_offseason_pm</t>
+          <t>cons_food_out_yatra_pm</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -4696,20 +4704,16 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr"/>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if spend_differs_by_season = 1</t>
-        </is>
-      </c>
+      <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="2" t="inlineStr">
         <is>
           <t>HCES 2022-23, MoSPI Appendix A, Section 7.1 'served processed food' (7-day in HCES; usual monthly here)</t>
@@ -4732,7 +4736,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>cons_fuel_yatra_pm</t>
+          <t>cons_food_out_offseason_pm</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -4742,19 +4746,23 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if spend_differs_by_season = 1</t>
+        </is>
+      </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 8.1 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.21-14.22. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 7.1 'served processed food' (7-day in HCES; usual monthly here)</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4782,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>cons_fuel_offseason_pm</t>
+          <t>cons_fuel_yatra_pm</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -4784,20 +4792,16 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr"/>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if spend_differs_by_season = 1</t>
-        </is>
-      </c>
+      <c r="I95" s="2" t="inlineStr"/>
       <c r="J95" s="2" t="inlineStr">
         <is>
           <t>HCES 2022-23, MoSPI Appendix A, Section 8.1 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.21-14.22. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
@@ -4820,7 +4824,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>cons_routine_misc_yatra_pm</t>
+          <t>cons_fuel_offseason_pm</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -4830,19 +4834,23 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr"/>
-      <c r="I96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if spend_differs_by_season = 1</t>
+        </is>
+      </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 9.1-9.2 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.25-14.27. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 8.1 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.21-14.22. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4870,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>cons_routine_misc_offseason_pm</t>
+          <t>cons_routine_misc_yatra_pm</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -4872,20 +4880,16 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr"/>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if spend_differs_by_season = 1</t>
-        </is>
-      </c>
+      <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="2" t="inlineStr">
         <is>
           <t>HCES 2022-23, MoSPI Appendix A, Sections 9.1-9.2 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.25-14.27. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
@@ -4908,7 +4912,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>cons_transport_comm_yatra_pm</t>
+          <t>cons_routine_misc_offseason_pm</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -4918,19 +4922,23 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr"/>
-      <c r="I98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if spend_differs_by_season = 1</t>
+        </is>
+      </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 11.1-11.2 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.24/14.28. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 9.1-9.2 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.25-14.27. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
         </is>
       </c>
     </row>
@@ -4950,7 +4958,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>cons_transport_comm_offseason_pm</t>
+          <t>cons_transport_comm_yatra_pm</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -4960,20 +4968,16 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if spend_differs_by_season = 1</t>
-        </is>
-      </c>
+      <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr">
         <is>
           <t>HCES 2022-23, MoSPI Appendix A, Sections 11.1-11.2 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.24/14.28. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
@@ -4996,7 +5000,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>cons_rent_yatra_pm</t>
+          <t>cons_transport_comm_offseason_pm</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5006,19 +5010,23 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if spend_differs_by_season = 1</t>
+        </is>
+      </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 11.4 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.30. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 11.1-11.2 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.24/14.28. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5046,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>cons_rent_offseason_pm</t>
+          <t>cons_rent_yatra_pm</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5048,20 +5056,16 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if spend_differs_by_season = 1</t>
-        </is>
-      </c>
+      <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr">
         <is>
           <t>HCES 2022-23, MoSPI Appendix A, Section 11.4 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.30. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
@@ -5084,7 +5088,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>cons_med_nonhosp_yatra_pm</t>
+          <t>cons_rent_offseason_pm</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5094,19 +5098,23 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if spend_differs_by_season = 1</t>
+        </is>
+      </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 10.3 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.33 (30-day, out-patient)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 11.4 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.30. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5134,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>cons_med_nonhosp_offseason_pm</t>
+          <t>cons_med_nonhosp_yatra_pm</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5136,20 +5144,16 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr"/>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if spend_differs_by_season = 1</t>
-        </is>
-      </c>
+      <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr">
         <is>
           <t>HCES 2022-23, MoSPI Appendix A, Section 10.3 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.33 (30-day, out-patient)</t>
@@ -5172,7 +5176,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>cons_packaged_food_yatra_pm</t>
+          <t>cons_med_nonhosp_offseason_pm</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5182,19 +5186,23 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
-      <c r="I104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if spend_differs_by_season = 1</t>
+        </is>
+      </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 7.2 (7-day in HCES; usual monthly here, as for every other seasonal item)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 10.3 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.33 (30-day, out-patient)</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5222,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>cons_packaged_food_offseason_pm</t>
+          <t>cons_packaged_food_yatra_pm</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5224,20 +5232,16 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr"/>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if spend_differs_by_season = 1</t>
-        </is>
-      </c>
+      <c r="I105" s="2" t="inlineStr"/>
       <c r="J105" s="2" t="inlineStr">
         <is>
           <t>HCES 2022-23, MoSPI Appendix A, Section 7.2 (7-day in HCES; usual monthly here, as for every other seasonal item)</t>
@@ -5260,7 +5264,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>cons_pan_tobacco_yatra_pm</t>
+          <t>cons_packaged_food_offseason_pm</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5270,19 +5274,23 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if spend_differs_by_season = 1</t>
+        </is>
+      </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 12.1-12.3 (7-day in HCES; usual monthly here, and combined into one figure)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 7.2 (7-day in HCES; usual monthly here, as for every other seasonal item)</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5310,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>cons_pan_tobacco_offseason_pm</t>
+          <t>cons_pan_tobacco_yatra_pm</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -5312,20 +5320,16 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if spend_differs_by_season = 1</t>
-        </is>
-      </c>
+      <c r="I107" s="2" t="inlineStr"/>
       <c r="J107" s="2" t="inlineStr">
         <is>
           <t>HCES 2022-23, MoSPI Appendix A, Sections 12.1-12.3 (7-day in HCES; usual monthly here, and combined into one figure)</t>
@@ -5348,7 +5352,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>cons_clothing_12m</t>
+          <t>cons_pan_tobacco_offseason_pm</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -5358,19 +5362,23 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much did your household spend on clothes and footwear? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में आपके घर ने कपड़ों और जूते-चप्पल पर कितना ख़र्च किया? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if spend_differs_by_season = 1</t>
+        </is>
+      </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 13.1-13.2 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.38-14.39 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses a 6-month recall for clothing (items 401-441); we follow the two India sources, since one of them (HCES) underlies our poverty line</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 12.1-12.3 (7-day in HCES; usual monthly here, and combined into one figure)</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5398,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>cons_education_12m</t>
+          <t>cons_clothing_12m</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -5400,19 +5408,19 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much on education: fees, books, uniforms, tuition? (Rs)</t>
+          <t>In the last 12 months, how much did your household spend on clothes and footwear? (Rs)</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में पढ़ाई पर कितना ख़र्च हुआ: फ़ीस, किताबें, ड्रेस, ट्यूशन? (रुपये)</t>
+          <t>पिछले 12 महीनों में आपके घर ने कपड़ों और जूते-चप्पल पर कितना ख़र्च किया? (रुपये)</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr"/>
       <c r="I109" s="2" t="inlineStr"/>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 10.1 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.35-14.37 (365-day, same items). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 asks school fees inside its education/roster module, per child, not as a household total, so it is not directly comparable</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 13.1-13.2 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.38-14.39 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses a 6-month recall for clothing (items 401-441); we follow the two India sources, since one of them (HCES) underlies our poverty line</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5440,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>cons_medical_hosp_12m</t>
+          <t>cons_education_12m</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -5442,19 +5450,19 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much did your household pay for any hospital admission or stay? (Rs, 0 if none)</t>
+          <t>In the last 12 months, how much on education: fees, books, uniforms, tuition? (Rs)</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में अस्पताल में भर्ती होने पर आपके घर का कितना ख़र्च हुआ? (रुपये, न हुआ हो तो 0)</t>
+          <t>पिछले 12 महीनों में पढ़ाई पर कितना ख़र्च हुआ: फ़ीस, किताबें, ड्रेस, ट्यूशन? (रुपये)</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr"/>
       <c r="I110" s="2" t="inlineStr"/>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 10.2 (365-day, hospitalisation). IHDS-II Income and Social Capital Questionnaire, Q14 14.34 (365-day, in-patient). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses one combined 6-month medical item (less detail); we follow the matching HCES/IHDS split</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 10.1 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.35-14.37 (365-day, same items). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 asks school fees inside its education/roster module, per child, not as a household total, so it is not directly comparable</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5482,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>cons_durables_12m</t>
+          <t>cons_medical_hosp_12m</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -5484,19 +5492,19 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much on durable goods: furniture, utensils, cooking appliances, phone, jewellery or ornaments, bicycle or vehicle parts? (Rs)</t>
+          <t>In the last 12 months, how much did your household pay for any hospital admission or stay? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में सामान पर कितना ख़र्च हुआ: फ़र्नीचर, बर्तन, चूल्हा-मशीन, फ़ोन, गहने, साइकिल या गाड़ी के पुर्ज़े? (रुपये)</t>
+          <t>पिछले 12 महीनों में अस्पताल में भर्ती होने पर आपके घर का कितना ख़र्च हुआ? (रुपये, न हुआ हो तो 0)</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr"/>
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 14 (365-day, 10 sub-groups). IHDS-II Income and Social Capital Questionnaire, Q14 14.40-14.48 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (12-month tier: durables, appliances, building materials). All three agree on the 12-month recall; insurance premiums, which IHDS (14.50) and the Nigeria survey (items 510-513) count here, are excluded, following HCES and standard national-accounts practice (insurance is a financial item, not consumption) — premiums are covered instead by the insurance items in Module G</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 10.2 (365-day, hospitalisation). IHDS-II Income and Social Capital Questionnaire, Q14 14.34 (365-day, in-patient). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses one combined 6-month medical item (less detail); we follow the matching HCES/IHDS split</t>
         </is>
       </c>
     </row>
@@ -5506,43 +5514,39 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Housing, amenities and assets</t>
+          <t>Household consumption</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>floor_material</t>
+          <t>cons_durables_12m</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>What is the main material of the floor at your usual home?</t>
+          <t>In the last 12 months, how much on durable goods: furniture, utensils, cooking appliances, phone, jewellery or ornaments, bicycle or vehicle parts? (Rs)</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>आपके असली घर में फ़र्श मुख्य रूप से किस चीज़ का है?</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>1 Mud/kaccha | 2 Cement/mud-cement | 3 Tile/mosaic/marble</t>
-        </is>
-      </c>
+          <t>पिछले 12 महीनों में सामान पर कितना ख़र्च हुआ: फ़र्नीचर, बर्तन, चूल्हा-मशीन, फ़ोन, गहने, साइकिल या गाड़ी के पुर्ज़े? (रुपये)</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr"/>
       <c r="I112" s="2" t="inlineStr"/>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI housing indicator</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 14 (365-day, 10 sub-groups). IHDS-II Income and Social Capital Questionnaire, Q14 14.40-14.48 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (12-month tier: durables, appliances, building materials). All three agree on the 12-month recall; insurance premiums, which IHDS (14.50) and the Nigeria survey (items 510-513) count here, are excluded, following HCES and standard national-accounts practice (insurance is a financial item, not consumption) — premiums are covered instead by the insurance items in Module G</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5566,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>roof_material</t>
+          <t>floor_material</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -5572,17 +5576,17 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>What is the main material of the roof at your usual home?</t>
+          <t>What is the main material of the floor at your usual home?</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>आपके असली घर की छत मुख्य रूप से किस चीज़ की है?</t>
+          <t>आपके असली घर में फ़र्श मुख्य रूप से किस चीज़ का है?</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>1 Thatch/wood/mud | 2 Tin/GI sheet | 3 Concrete/RCC</t>
+          <t>1 Mud/kaccha | 2 Cement/mud-cement | 3 Tile/mosaic/marble</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr"/>
@@ -5608,7 +5612,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>wall_material</t>
+          <t>roof_material</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -5618,23 +5622,23 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>What are the walls of your usual home mainly made of?</t>
+          <t>What is the main material of the roof at your usual home?</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>आपके असली घर की दीवारें मुख्य रूप से किस चीज़ की बनी हैं?</t>
+          <t>आपके असली घर की छत मुख्य रूप से किस चीज़ की है?</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>1 Mud, thatch, bamboo or other natural material | 2 Unburnt brick, wood or tin | 3 Burnt brick, cement, concrete or stone</t>
+          <t>1 Thatch/wood/mud | 2 Tin/GI sheet | 3 Concrete/RCC</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI housing indicator (wall limb)</t>
+          <t>NITI Aayog National MPI housing indicator</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5658,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>accom_type_here</t>
+          <t>wall_material</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -5664,23 +5668,23 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>While you are here for the season, where do you sleep?</t>
+          <t>What are the walls of your usual home mainly made of?</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>सीज़न में यहाँ रहते हुए आप कहाँ सोते हैं?</t>
+          <t>आपके असली घर की दीवारें मुख्य रूप से किस चीज़ की बनी हैं?</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>1 At my own usual home (I live here) | 2 Rented room or house | 3 Room or dormitory the employer provides | 4 Sleeps at the shop, dhaba or workplace | 5 Tent or temporary shelter | 6 Lodge, dharamshala or ashram | 7 In the open, or a verandah | 8 Somewhere else</t>
+          <t>1 Mud, thatch, bamboo or other natural material | 2 Unburnt brick, wood or tin | 3 Burnt brick, cement, concrete or stone</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr"/>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>Lyons et al. 2023, Table 2 (area/settlement conditions), adapted to a labour-migrant setting</t>
+          <t>NITI Aayog National MPI housing indicator (wall limb)</t>
         </is>
       </c>
     </row>
@@ -5700,33 +5704,33 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>accom_type_here</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Does your usual home have an electricity connection?</t>
+          <t>While you are here for the season, where do you sleep?</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके असली घर में बिजली का कनेक्शन है?</t>
+          <t>सीज़न में यहाँ रहते हुए आप कहाँ सोते हैं?</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 At my own usual home (I live here) | 2 Rented room or house | 3 Room or dormitory the employer provides | 4 Sleeps at the shop, dhaba or workplace | 5 Tent or temporary shelter | 6 Lodge, dharamshala or ashram | 7 In the open, or a verandah | 8 Somewhere else</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI</t>
+          <t>Lyons et al. 2023, Table 2 (area/settlement conditions), adapted to a labour-migrant setting</t>
         </is>
       </c>
     </row>
@@ -5746,33 +5750,33 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>toilet_type</t>
+          <t>electricity</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>What kind of toilet does your household use at your usual home?</t>
+          <t>Does your usual home have an electricity connection?</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>आपका घर अपने असली घर में किस तरह का शौचालय इस्तेमाल करता है?</t>
+          <t>क्या आपके असली घर में बिजली का कनेक्शन है?</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>1 No toilet / open defecation | 2 Pit latrine without slab or open pit | 3 Improved toilet, but shared with other households | 4 Improved toilet, used only by this household</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr"/>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI sanitation indicator (improved/unimproved and shared/not)</t>
+          <t>NITI Aayog National MPI</t>
         </is>
       </c>
     </row>
@@ -5792,7 +5796,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>drinking_water</t>
+          <t>toilet_type</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -5802,23 +5806,23 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>What is your main source of drinking water at your usual home?</t>
+          <t>What kind of toilet does your household use at your usual home?</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>आपके असली घर में पीने का पानी मुख्य रूप से कहाँ से आता है?</t>
+          <t>आपका घर अपने असली घर में किस तरह का शौचालय इस्तेमाल करता है?</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>1 Piped into the house or yard | 2 Public tap or standpipe | 3 Handpump, tubewell or borewell | 4 Protected well or protected spring | 5 Rainwater collection | 6 Bottled, packaged or community RO | 7 Unprotected well or unprotected spring | 8 River, stream, pond or canal | 9 Tanker truck or cart with drum</t>
+          <t>1 No toilet / open defecation | 2 Pit latrine without slab or open pit | 3 Improved toilet, but shared with other households | 4 Improved toilet, used only by this household</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI drinking-water indicator (JMP improved/unimproved taxonomy)</t>
+          <t>NITI Aayog National MPI sanitation indicator (improved/unimproved and shared/not)</t>
         </is>
       </c>
     </row>
@@ -5838,33 +5842,33 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>water_on_premises</t>
+          <t>drinking_water</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Is the drinking water available at the house itself?</t>
+          <t>What is your main source of drinking water at your usual home?</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>क्या पीने का पानी घर पर ही मिल जाता है?</t>
+          <t>आपके असली घर में पीने का पानी मुख्य रूप से कहाँ से आता है?</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 Piped into the house or yard | 2 Public tap or standpipe | 3 Handpump, tubewell or borewell | 4 Protected well or protected spring | 5 Rainwater collection | 6 Bottled, packaged or community RO | 7 Unprotected well or unprotected spring | 8 River, stream, pond or canal | 9 Tanker truck or cart with drum</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr"/>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI drinking-water indicator (30-minute round-trip rule)</t>
+          <t>NITI Aayog National MPI drinking-water indicator (JMP improved/unimproved taxonomy)</t>
         </is>
       </c>
     </row>
@@ -5884,30 +5888,30 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>water_fetch_minutes</t>
+          <t>water_on_premises</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>How long does it take to go there, get the water and come back? (minutes, round trip)</t>
+          <t>Is the drinking water available at the house itself?</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>वहाँ जाने, पानी भरने और लौटने में कुल कितना समय लगता है? (मिनट)</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr"/>
-      <c r="I120" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if water_on_premises = 0</t>
-        </is>
-      </c>
+          <t>क्या पीने का पानी घर पर ही मिल जाता है?</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr"/>
       <c r="J120" s="2" t="inlineStr">
         <is>
           <t>NITI Aayog National MPI drinking-water indicator (30-minute round-trip rule)</t>
@@ -5930,33 +5934,33 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>cooking_fuel</t>
+          <t>water_fetch_minutes</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>What does your household mainly use to cook at your usual home?</t>
+          <t>How long does it take to go there, get the water and come back? (minutes, round trip)</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>आपके असली घर में खाना मुख्य रूप से किस चीज़ पर बनता है?</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>1 LPG or cylinder gas | 2 Piped natural gas | 3 Electricity | 4 Biogas (gobar gas plant) | 5 Kerosene | 6 Firewood | 7 Dung cakes (gobar) | 8 Crop residue, straw or shrubs | 9 Charcoal | 10 Coal or lignite</t>
-        </is>
-      </c>
-      <c r="I121" s="2" t="inlineStr"/>
+          <t>वहाँ जाने, पानी भरने और लौटने में कुल कितना समय लगता है? (मिनट)</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr"/>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if water_on_premises = 0</t>
+        </is>
+      </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI cooking-fuel indicator (its own list of dirty fuels)</t>
+          <t>NITI Aayog National MPI drinking-water indicator (30-minute round-trip rule)</t>
         </is>
       </c>
     </row>
@@ -5976,33 +5980,33 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>owns_tv</t>
+          <t>cooking_fuel</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Does your household own: a television?</t>
+          <t>What does your household mainly use to cook at your usual home?</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में टीवी है?</t>
+          <t>आपके असली घर में खाना मुख्य रूप से किस चीज़ पर बनता है?</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 LPG or cylinder gas | 2 Piped natural gas | 3 Electricity | 4 Biogas (gobar gas plant) | 5 Kerosene | 6 Firewood | 7 Dung cakes (gobar) | 8 Crop residue, straw or shrubs | 9 Charcoal | 10 Coal or lignite</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr"/>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI assets indicator</t>
+          <t>NITI Aayog National MPI cooking-fuel indicator (its own list of dirty fuels)</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6026,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>owns_radio</t>
+          <t>owns_tv</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6032,12 +6036,12 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>... a radio?</t>
+          <t>Does your household own: a television?</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>...रेडियो?</t>
+          <t>क्या आपके घर में टीवी है?</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -6068,7 +6072,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>owns_bicycle</t>
+          <t>owns_radio</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -6078,12 +6082,12 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>... a bicycle?</t>
+          <t>... a radio?</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>...साइकिल?</t>
+          <t>...रेडियो?</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -6114,7 +6118,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>owns_motorcycle</t>
+          <t>owns_bicycle</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -6124,12 +6128,12 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>... a motorcycle or scooter?</t>
+          <t>... a bicycle?</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>...मोटरसाइकिल या स्कूटर?</t>
+          <t>...साइकिल?</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6160,7 +6164,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>owns_car</t>
+          <t>owns_motorcycle</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -6170,12 +6174,12 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>... a car, jeep or truck?</t>
+          <t>... a motorcycle or scooter?</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>...कार, जीप या ट्रक?</t>
+          <t>...मोटरसाइकिल या स्कूटर?</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -6186,7 +6190,7 @@
       <c r="I126" s="2" t="inlineStr"/>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI assets indicator (car or truck limb)</t>
+          <t>NITI Aayog National MPI assets indicator</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6210,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>owns_phone</t>
+          <t>owns_car</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -6216,12 +6220,12 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>... a telephone of any kind, mobile or landline?</t>
+          <t>... a car, jeep or truck?</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>...कोई फ़ोन, मोबाइल या लैंडलाइन?</t>
+          <t>...कार, जीप या ट्रक?</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -6232,7 +6236,7 @@
       <c r="I127" s="2" t="inlineStr"/>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI assets indicator</t>
+          <t>NITI Aayog National MPI assets indicator (car or truck limb)</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6256,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>owns_computer</t>
+          <t>owns_phone</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -6262,12 +6266,12 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>... a computer or laptop?</t>
+          <t>... a telephone of any kind, mobile or landline?</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>...कंप्यूटर या लैपटॉप?</t>
+          <t>...कोई फ़ोन, मोबाइल या लैंडलाइन?</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -6298,7 +6302,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>owns_animal_cart</t>
+          <t>owns_computer</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -6308,12 +6312,12 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>... a cart pulled by an animal?</t>
+          <t>... a computer or laptop?</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>...जानवर से खींची जाने वाली गाड़ी?</t>
+          <t>...कंप्यूटर या लैपटॉप?</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -6344,7 +6348,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>owns_fridge</t>
+          <t>owns_animal_cart</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -6354,12 +6358,12 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>... a refrigerator?</t>
+          <t>... a cart pulled by an animal?</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>...फ़्रिज?</t>
+          <t>...जानवर से खींची जाने वाली गाड़ी?</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -6390,33 +6394,33 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>land_unit</t>
+          <t>owns_fridge</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>In what unit do you count your land — nali, bigha, acres or hectares?</t>
+          <t>... a refrigerator?</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>आप अपनी ज़मीन किस हिसाब से गिनते हैं — नाली, बीघा, एकड़ या हेक्टेयर?</t>
+          <t>...फ़्रिज?</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>1 Nali | 2 Bigha | 3 Acres | 4 Hectares | 5 No land</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr"/>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>Project design (local land units, Uttarakhand)</t>
+          <t>NITI Aayog National MPI assets indicator</t>
         </is>
       </c>
     </row>
@@ -6436,29 +6440,33 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>land_cultivable_acres</t>
+          <t>land_unit</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>And how much CULTIVABLE land is that? Do not count the land the house stands on.</t>
+          <t>In what unit do you count your land — nali, bigha, acres or hectares?</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>आपके घर के पास कितनी जोतने लायक़ ज़मीन है, अपनी या जोतने की, एकड़ में? जिस ज़मीन पर घर बना है उसे मत गिनिए। (न हो तो 0)</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr"/>
+          <t>आप अपनी ज़मीन किस हिसाब से गिनते हैं — नाली, बीघा, एकड़ या हेक्टेयर?</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>1 Nali | 2 Bigha | 3 Acres | 4 Hectares | 5 No land</t>
+        </is>
+      </c>
       <c r="I132" s="2" t="inlineStr"/>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>Chaudhuri et al. 2002 asset covariate</t>
+          <t>Project design (local land units, Uttarakhand)</t>
         </is>
       </c>
     </row>
@@ -6478,29 +6486,25 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>owns_cow_buffalo</t>
+          <t>land_cultivable_acres</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>number</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Does your household own any cows or buffaloes?</t>
+          <t>And how much CULTIVABLE land is that? Do not count the land the house stands on.</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में गाय या भैंस है?</t>
-        </is>
-      </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
+          <t>आपके घर के पास कितनी जोतने लायक़ ज़मीन है, अपनी या जोतने की, एकड़ में? जिस ज़मीन पर घर बना है उसे मत गिनिए। (न हो तो 0)</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr"/>
       <c r="I133" s="2" t="inlineStr"/>
       <c r="J133" s="2" t="inlineStr">
         <is>
@@ -6524,7 +6528,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>owns_goat_sheep</t>
+          <t>owns_cow_buffalo</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -6534,12 +6538,12 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Does your household own any goats or sheep?</t>
+          <t>Does your household own any cows or buffaloes?</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में बकरी या भेड़ है?</t>
+          <t>क्या आपके घर में गाय या भैंस है?</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -6570,7 +6574,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>owns_pony_mule</t>
+          <t>owns_goat_sheep</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -6580,12 +6584,12 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Does your household own any ponies or mules?</t>
+          <t>Does your household own any goats or sheep?</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में घोड़ा या खच्चर है?</t>
+          <t>क्या आपके घर में बकरी या भेड़ है?</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -6596,7 +6600,7 @@
       <c r="I135" s="2" t="inlineStr"/>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>Project design (pilot livelihood survey)</t>
+          <t>Chaudhuri et al. 2002 asset covariate</t>
         </is>
       </c>
     </row>
@@ -6616,7 +6620,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>owns_shop_stall</t>
+          <t>owns_pony_mule</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -6626,12 +6630,12 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Does your household own a shop or stall that you use to earn?</t>
+          <t>Does your household own any ponies or mules?</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर की अपनी दुकान या खोखा है जिससे आप कमाते हैं?</t>
+          <t>क्या आपके घर में घोड़ा या खच्चर है?</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -6642,7 +6646,7 @@
       <c r="I136" s="2" t="inlineStr"/>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>Chaudhuri et al. 2002 asset covariate</t>
+          <t>Project design (pilot livelihood survey)</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6666,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>owns_work_vehicle</t>
+          <t>owns_shop_stall</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -6672,12 +6676,12 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Does your household own a vehicle you use to earn (for example a jeep, truck or taxi)?</t>
+          <t>Does your household own a shop or stall that you use to earn?</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर की अपनी गाड़ी है जिससे आप कमाते हैं (जैसे जीप, ट्रक या टैक्सी)?</t>
+          <t>क्या आपके घर की अपनी दुकान या खोखा है जिससे आप कमाते हैं?</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -6708,7 +6712,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>owns_work_equipment</t>
+          <t>owns_work_vehicle</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -6718,12 +6722,12 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Does your household own equipment or tools that you use to earn?</t>
+          <t>Does your household own a vehicle you use to earn (for example a jeep, truck or taxi)?</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर के पास काम के औज़ार या मशीन है जिससे आप कमाते हैं?</t>
+          <t>क्या आपके घर की अपनी गाड़ी है जिससे आप कमाते हैं (जैसे जीप, ट्रक या टैक्सी)?</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -6754,33 +6758,33 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>work_equipment_detail</t>
+          <t>owns_work_equipment</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>What are they? Write what they say. Leave blank if they cannot say.</t>
+          <t>Does your household own equipment or tools that you use to earn?</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>वे क्या हैं? जैसा वे बताएँ वैसा लिख लीजिए। न बता पाएँ तो खाली छोड़ दीजिए।</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr"/>
-      <c r="I139" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if owns_work_equipment = 1; may be left blank</t>
-        </is>
-      </c>
+          <t>क्या आपके घर के पास काम के औज़ार या मशीन है जिससे आप कमाते हैं?</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr"/>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>Standard household-survey item</t>
+          <t>Chaudhuri et al. 2002 asset covariate</t>
         </is>
       </c>
     </row>
@@ -6790,43 +6794,43 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Finance, insurance and schemes</t>
+          <t>Housing, amenities and assets</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>has_bank_account</t>
+          <t>work_equipment_detail</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Does anyone in your household have a bank account or a post office account?</t>
+          <t>What are they? Write what they say. Leave blank if they cannot say.</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में किसी का बैंक खाता या डाकघर का खाता है?</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I140" s="2" t="inlineStr"/>
+          <t>वे क्या हैं? जैसा वे बताएँ वैसा लिख लीजिए। न बता पाएँ तो खाली छोड़ दीजिए।</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr"/>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if owns_work_equipment = 1; may be left blank</t>
+        </is>
+      </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI bank-account indicator; VEP adaptive-capacity covariate</t>
+          <t>Standard household-survey item</t>
         </is>
       </c>
     </row>
@@ -6846,7 +6850,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>took_loan_12m</t>
+          <t>has_bank_account</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -6856,12 +6860,12 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did you or anyone in your household borrow money?</t>
+          <t>Does anyone in your household have a bank account or a post office account?</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपने या आपके घर के किसी सदस्य ने पैसा उधार लिया?</t>
+          <t>क्या आपके घर में किसी का बैंक खाता या डाकघर का खाता है?</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -6872,7 +6876,7 @@
       <c r="I141" s="2" t="inlineStr"/>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate</t>
+          <t>NITI Aayog National MPI bank-account indicator; VEP adaptive-capacity covariate</t>
         </is>
       </c>
     </row>
@@ -6892,37 +6896,33 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>credit_source</t>
+          <t>took_loan_12m</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Who was the main lender?</t>
+          <t>In the last 12 months, did you or anyone in your household borrow money?</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>मुख्य रूप से किससे उधार लिया?</t>
+          <t>पिछले 12 महीनों में क्या आपने या आपके घर के किसी सदस्य ने पैसा उधार लिया?</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>1 Nationalised or public-sector bank | 2 Private bank | 3 Cooperative bank or RRB | 4 Microfinance institution or SHG | 5 Moneylender | 6 Relative or friend | 7 Employer or contractor (advance) | 8 Other</t>
-        </is>
-      </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if took_loan_12m = 1</t>
-        </is>
-      </c>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr"/>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate (lender type)</t>
+          <t>VEP adaptive-capacity covariate</t>
         </is>
       </c>
     </row>
@@ -6942,7 +6942,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>loan_purpose</t>
+          <t>credit_source</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -6952,17 +6952,17 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>What did you take it for?</t>
+          <t>Who was the main lender?</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>वह क़र्ज़ आपने किस काम के लिए लिया था?</t>
+          <t>मुख्य रूप से किससे उधार लिया?</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>1 Medical or hospital costs | 2 Buying an animal, vehicle or equipment for work | 3 Shop stock or business | 4 Food or daily household needs | 5 A wedding, funeral or ceremony | 6 House building or repair | 7 Education | 8 Repaying another loan | 9 Something else</t>
+          <t>1 Nationalised or public-sector bank | 2 Private bank | 3 Cooperative bank or RRB | 4 Microfinance institution or SHG | 5 Moneylender | 6 Relative or friend | 7 Employer or contractor (advance) | 8 Other</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>Project design (investment against distress borrowing)</t>
+          <t>VEP adaptive-capacity covariate (lender type)</t>
         </is>
       </c>
     </row>
@@ -6992,25 +6992,29 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>loan_amount_borrowed</t>
+          <t>loan_purpose</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>How much did you borrow in total? (Rs)</t>
+          <t>What did you take it for?</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>आपने कुल कितना क़र्ज़ लिया था? (रुपये)</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr"/>
+          <t>वह क़र्ज़ आपने किस काम के लिए लिया था?</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>1 Medical or hospital costs | 2 Buying an animal, vehicle or equipment for work | 3 Shop stock or business | 4 Food or daily household needs | 5 A wedding, funeral or ceremony | 6 House building or repair | 7 Education | 8 Repaying another loan | 9 Something else</t>
+        </is>
+      </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
           <t>Ask only if took_loan_12m = 1</t>
@@ -7018,7 +7022,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>Project design (loan size, for the debt-burden measures)</t>
+          <t>Project design (investment against distress borrowing)</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7042,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>loan_amount</t>
+          <t>loan_amount_borrowed</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -7048,12 +7052,12 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>How much of that loan is still left to repay? (Rs)</t>
+          <t>How much did you borrow in total? (Rs)</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>उस क़र्ज़ में से अब भी कितना चुकाना बाक़ी है? (रुपये)</t>
+          <t>आपने कुल कितना क़र्ज़ लिया था? (रुपये)</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr"/>
@@ -7064,7 +7068,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>Islam and Chowdhury 2025 (financial distress and household vulnerability to poverty)</t>
+          <t>Project design (loan size, for the debt-burden measures)</t>
         </is>
       </c>
     </row>
@@ -7084,29 +7088,25 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>pays_interest</t>
+          <t>loan_amount</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>Do you pay interest on it?</t>
+          <t>How much of that loan is still left to repay? (Rs)</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>क्या आप उस पर ब्याज देते हैं?</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
+          <t>उस क़र्ज़ में से अब भी कितना चुकाना बाक़ी है? (रुपये)</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr"/>
       <c r="I146" s="2" t="inlineStr">
         <is>
           <t>Ask only if took_loan_12m = 1</t>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>Project design (informal lending is often interest-free)</t>
+          <t>Islam and Chowdhury 2025 (financial distress and household vulnerability to poverty)</t>
         </is>
       </c>
     </row>
@@ -7134,33 +7134,37 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>loan_interest_per100_pm</t>
+          <t>pays_interest</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>On every 100 rupees you borrowed, about how much interest do you pay in a month? (Rs; 0 if none, leave blank if not known)</t>
+          <t>Do you pay interest on it?</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>आपने जो 100 रुपये उधार लिए, उन पर महीने का कितना ब्याज देते हैं? (रुपये; दर पता न हो तो खाली छोड़ दें)</t>
-        </is>
-      </c>
-      <c r="H147" s="2" t="inlineStr"/>
+          <t>क्या आप उस पर ब्याज देते हैं?</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>Ask only if took_loan_12m = 1; may be left blank</t>
+          <t>Ask only if took_loan_12m = 1</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>Project design (informal-credit pricing as locally quoted)</t>
+          <t>Project design (informal lending is often interest-free)</t>
         </is>
       </c>
     </row>
@@ -7180,37 +7184,33 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>loan_against_asset</t>
+          <t>loan_interest_per100_pm</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>number</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Did you have to give something as security for it — an animal, a vehicle, jewellery, land or your business?</t>
+          <t>On every 100 rupees you borrowed, about how much interest do you pay in a month? (Rs; 0 if none, leave blank if not known)</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>क्या उसके बदले कुछ गिरवी रखना पड़ा — जानवर, गाड़ी, गहने, ज़मीन या आपका धंधा?</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
+          <t>आपने जो 100 रुपये उधार लिए, उन पर महीने का कितना ब्याज देते हैं? (रुपये; दर पता न हो तो खाली छोड़ दें)</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr"/>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>Ask only if took_loan_12m = 1</t>
+          <t>Ask only if took_loan_12m = 1; may be left blank</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
+          <t>Project design (informal-credit pricing as locally quoted)</t>
         </is>
       </c>
     </row>
@@ -7230,37 +7230,37 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>loan_collateral</t>
+          <t>loan_against_asset</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>What did you have to give as security?</t>
+          <t>Did you have to give something as security for it — an animal, a vehicle, jewellery, land or your business?</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>आपको क्या गिरवी रखना पड़ा?</t>
+          <t>क्या उसके बदले कुछ गिरवी रखना पड़ा — जानवर, गाड़ी, गहने, ज़मीन या आपका धंधा?</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>1 Jewellery or ornaments | 2 Land | 3 Animals | 4 A vehicle | 5 Shop stock or business goods | 6 House or building | 7 Something else</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>Ask only if loan_against_asset = 1</t>
+          <t>Ask only if took_loan_12m = 1</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003 (asset-based coping)</t>
+          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
         </is>
       </c>
     </row>
@@ -7280,29 +7280,37 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>n_health_insured</t>
+          <t>loan_collateral</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>How many people in your household are covered by any health insurance or health scheme, including government ones? (0 if none)</t>
+          <t>What did you have to give as security?</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोगों का कोई स्वास्थ्य बीमा या स्वास्थ्य योजना है, सरकारी भी मिलाकर? (कोई नहीं तो 0)</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr"/>
-      <c r="I150" s="2" t="inlineStr"/>
+          <t>आपको क्या गिरवी रखना पड़ा?</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>1 Jewellery or ornaments | 2 Land | 3 Animals | 4 A vehicle | 5 Shop stock or business goods | 6 House or building | 7 Something else</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if loan_against_asset = 1</t>
+        </is>
+      </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI health-insurance indicator; Lyons et al. 2023</t>
+          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003 (asset-based coping)</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7330,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>n_life_insured</t>
+          <t>n_health_insured</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -7332,19 +7340,19 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>How many people in your household have life insurance? (0 if none)</t>
+          <t>How many people in your household are covered by any health insurance or health scheme, including government ones? (0 if none)</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोगों का जीवन बीमा है? (कोई नहीं तो 0)</t>
+          <t>आपके घर में कितने लोगों का कोई स्वास्थ्य बीमा या स्वास्थ्य योजना है, सरकारी भी मिलाकर? (कोई नहीं तो 0)</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr"/>
       <c r="I151" s="2" t="inlineStr"/>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>Standard household-survey item</t>
+          <t>NITI Aayog National MPI health-insurance indicator; Lyons et al. 2023</t>
         </is>
       </c>
     </row>
@@ -7364,34 +7372,26 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>has_crop_insurance</t>
+          <t>n_life_insured</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Is your crop insured?</t>
+          <t>How many people in your household have life insurance? (0 if none)</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>क्या आपकी फ़सल का बीमा है?</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I152" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if land_cultivable_acres &gt; 0</t>
-        </is>
-      </c>
+          <t>आपके घर में कितने लोगों का जीवन बीमा है? (कोई नहीं तो 0)</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr"/>
+      <c r="I152" s="2" t="inlineStr"/>
       <c r="J152" s="2" t="inlineStr">
         <is>
           <t>Standard household-survey item</t>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>govt_any_benefit</t>
+          <t>has_crop_insurance</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did your household get anything from any government scheme? Read the list out before you take an answer.</t>
+          <t>Is your crop insured?</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके घर को किसी सरकारी योजना से कुछ मिला? जवाब लेने से पहले सूची पढ़कर सुनाइए।</t>
+          <t>क्या आपकी फ़सल का बीमा है?</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -7437,10 +7437,14 @@
           <t>0 No | 1 Yes</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr"/>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if land_cultivable_acres &gt; 0</t>
+        </is>
+      </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>Project design; scheme names as administered in Uttarakhand</t>
+          <t>Standard household-survey item</t>
         </is>
       </c>
     </row>
@@ -7460,33 +7464,33 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>govt_schemes_detail</t>
+          <t>govt_any_benefit</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Which ones? Write down every scheme they name, in their own words.</t>
+          <t>In the last 12 months, did your household get anything from any government scheme? Read the list out before you take an answer.</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>कौन-कौन सी? वे जितनी योजनाएँ बताएँ, सब उन्हीं के शब्दों में लिख लीजिए।</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr"/>
-      <c r="I154" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if govt_any_benefit = 1</t>
-        </is>
-      </c>
+          <t>पिछले 12 महीनों में क्या आपके घर को किसी सरकारी योजना से कुछ मिला? जवाब लेने से पहले सूची पढ़कर सुनाइए।</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr"/>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>Project design; coded in the office against the Uttarakhand scheme list</t>
+          <t>Project design; scheme names as administered in Uttarakhand</t>
         </is>
       </c>
     </row>
@@ -7506,33 +7510,33 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>ration_portable_here</t>
+          <t>govt_schemes_detail</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Can you draw your ration here, or only at your home place?</t>
+          <t>Which ones? Write down every scheme they name, in their own words.</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>क्या आप अपना राशन यहाँ ले सकते हैं, या सिर्फ़ अपने घर वाली जगह पर?</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>1 Yes, can draw it here | 2 No, only at the home place | 3 Has never tried | 4 We have no ration card | 97 Does not know</t>
-        </is>
-      </c>
-      <c r="I155" s="2" t="inlineStr"/>
+          <t>कौन-कौन सी? वे जितनी योजनाएँ बताएँ, सब उन्हीं के शब्दों में लिख लीजिए।</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr"/>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if govt_any_benefit = 1</t>
+        </is>
+      </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>Lyons et al. 2023, Table 2 (legal residency), adapted; One Nation One Ration Card</t>
+          <t>Project design; coded in the office against the Uttarakhand scheme list</t>
         </is>
       </c>
     </row>
@@ -7552,33 +7556,33 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>smartphone_owned</t>
+          <t>ration_portable_here</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>Do you own a smartphone?</t>
+          <t>Can you draw your ration here, or only at your home place?</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके पास स्मार्टफ़ोन है?</t>
+          <t>क्या आप अपना राशन यहाँ ले सकते हैं, या सिर्फ़ अपने घर वाली जगह पर?</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 Yes, can draw it here | 2 No, only at the home place | 3 Has never tried | 4 We have no ration card | 97 Does not know</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr"/>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate; STEP digital items</t>
+          <t>Lyons et al. 2023, Table 2 (legal residency), adapted; One Nation One Ration Card</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7602,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>uses_digital_payment</t>
+          <t>smartphone_owned</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -7608,12 +7612,12 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Do you ever use UPI or another way of paying by phone?</t>
+          <t>Do you own a smartphone?</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>क्या आप कभी UPI या फ़ोन से पैसे का लेन-देन करते हैं?</t>
+          <t>क्या आपके पास स्मार्टफ़ोन है?</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -7644,29 +7648,33 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>n_can_transact_online</t>
+          <t>uses_digital_payment</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>How many people in your household can make a payment by phone themselves, without help? (0 if none)</t>
+          <t>Do you ever use UPI or another way of paying by phone?</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोग बिना किसी की मदद के फ़ोन से पैसे भेज सकते हैं? (कोई नहीं तो 0)</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr"/>
+          <t>क्या आप कभी UPI या फ़ोन से पैसे का लेन-देन करते हैं?</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
       <c r="I158" s="2" t="inlineStr"/>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>Project design (intra-household financial capability)</t>
+          <t>VEP adaptive-capacity covariate; STEP digital items</t>
         </is>
       </c>
     </row>
@@ -7676,43 +7684,39 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Finance, insurance and schemes</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>morbidity_15d</t>
+          <t>n_can_transact_online</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>In the last 15 days, was anyone in your household ill?</t>
+          <t>How many people in your household can make a payment by phone themselves, without help? (0 if none)</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>पिछले 15 दिनों में क्या आपके घर में कोई बीमार पड़ा?</t>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
+          <t>आपके घर में कितने लोग बिना किसी की मदद के फ़ोन से पैसे भेज सकते हैं? (कोई नहीं तो 0)</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr"/>
       <c r="I159" s="2" t="inlineStr"/>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>NSS health module (15-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
+          <t>Project design (intra-household financial capability)</t>
         </is>
       </c>
     </row>
@@ -7732,37 +7736,33 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>morbidity_coping_15d</t>
+          <t>morbidity_15d</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>How did the household mainly cope with the cost of this: used savings; borrowed money; sold or pawned assets; cut other consumption; got help from relatives or community; or something else?</t>
+          <t>In the last 15 days, was anyone in your household ill?</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>इसका ख़र्च आपके घर ने मुख्य रूप से कैसे उठाया: जमा पैसे से; उधार लेकर; कुछ बेचकर या गिरवी रखकर; बाकी ख़र्च घटाकर; रिश्तेदारों या गाँव वालों की मदद से; या किसी और तरह?</t>
+          <t>पिछले 15 दिनों में क्या आपके घर में कोई बीमार पड़ा?</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>1 Used savings | 2 Borrowed money | 3 Sold or pawned assets | 4 Cut consumption | 5 Help from relatives/community | 6 Paid it out of normal earnings, nothing given up | 7 Something else (say what)</t>
-        </is>
-      </c>
-      <c r="I160" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if morbidity_15d = 1</t>
-        </is>
-      </c>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr"/>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>Project design (a reported illness with no cost/coping follow-up said nothing about its burden)</t>
+          <t>NSS health module (15-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
         </is>
       </c>
     </row>
@@ -7782,25 +7782,29 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>morbidity_cost_15d</t>
+          <t>morbidity_coping_15d</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>About how much did the household spend on this in the last 15 days (medicine, doctor or clinic fees, travel for care)? (Rs)</t>
+          <t>How did the household mainly cope with the cost of this: used savings; borrowed money; sold or pawned assets; cut other consumption; got help from relatives or community; or something else?</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>पिछले 15 दिनों में इस पर घर का लगभग कितना ख़र्च हुआ (दवाई, डॉक्टर या क्लीनिक की फ़ीस, आने-जाने का ख़र्च)? (रुपये)</t>
-        </is>
-      </c>
-      <c r="H161" s="2" t="inlineStr"/>
+          <t>इसका ख़र्च आपके घर ने मुख्य रूप से कैसे उठाया: जमा पैसे से; उधार लेकर; कुछ बेचकर या गिरवी रखकर; बाकी ख़र्च घटाकर; रिश्तेदारों या गाँव वालों की मदद से; या किसी और तरह?</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>1 Used savings | 2 Borrowed money | 3 Sold or pawned assets | 4 Cut consumption | 5 Help from relatives/community | 6 Paid it out of normal earnings, nothing given up | 7 Something else (say what)</t>
+        </is>
+      </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
           <t>Ask only if morbidity_15d = 1</t>
@@ -7808,7 +7812,7 @@
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>Project design</t>
+          <t>Project design (a reported illness with no cost/coping follow-up said nothing about its burden)</t>
         </is>
       </c>
     </row>
@@ -7828,33 +7832,33 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>func_limitation</t>
+          <t>morbidity_cost_15d</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>Do you have difficulty walking or climbing steps?</t>
+          <t>About how much did the household spend on this in the last 15 days (medicine, doctor or clinic fees, travel for care)? (Rs)</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>क्या आपको चलने या सीढ़ियाँ चढ़ने में दिक़्क़त होती है?</t>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>1 No difficulty | 2 Some difficulty | 3 A lot of difficulty | 4 Cannot do it at all</t>
-        </is>
-      </c>
-      <c r="I162" s="2" t="inlineStr"/>
+          <t>पिछले 15 दिनों में इस पर घर का लगभग कितना ख़र्च हुआ (दवाई, डॉक्टर या क्लीनिक की फ़ीस, आने-जाने का ख़र्च)? (रुपये)</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr"/>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if morbidity_15d = 1</t>
+        </is>
+      </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>Washington Group on Disability Statistics, Short Set item 3 (mobility), verbatim; Lyons et al. 2023 health dimension</t>
+          <t>Project design</t>
         </is>
       </c>
     </row>
@@ -7874,33 +7878,33 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>hospitalization_365d</t>
+          <t>func_limitation</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, was anyone in your household admitted to hospital overnight?</t>
+          <t>Do you have difficulty walking or climbing steps?</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके घर का कोई रात भर के लिए अस्पताल में भर्ती हुआ?</t>
+          <t>क्या आपको चलने या सीढ़ियाँ चढ़ने में दिक़्क़त होती है?</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 No difficulty | 2 Some difficulty | 3 A lot of difficulty | 4 Cannot do it at all</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr"/>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>NSS health module (365-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
+          <t>Washington Group on Disability Statistics, Short Set item 3 (mobility), verbatim; Lyons et al. 2023 health dimension</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7924,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>health_access_barrier_3m</t>
+          <t>hospitalization_365d</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -7930,12 +7934,12 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>In the last 3 months, was there a time when someone in your household needed medical care but could not get it?</t>
+          <t>In the last 12 months, was anyone in your household admitted to hospital overnight?</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>पिछले 3 महीनों में क्या कभी ऐसा हुआ कि आपके घर में किसी को इलाज की ज़रूरत थी पर मिल नहीं पाया?</t>
+          <t>पिछले 12 महीनों में क्या आपके घर का कोई रात भर के लिए अस्पताल में भर्ती हुआ?</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -7946,7 +7950,7 @@
       <c r="I164" s="2" t="inlineStr"/>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 barriers_health_case_access_phc_m (primary-care access barriers); Lyons et al. 2023 Table 2 indicator 2 'healthcare access'</t>
+          <t>NSS health module (365-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
         </is>
       </c>
     </row>
@@ -7966,7 +7970,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>child_death_5y</t>
+          <t>health_access_barrier_3m</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -7976,12 +7980,12 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>In the last five years, has any child or young person under 18 in your household died?</t>
+          <t>In the last 3 months, was there a time when someone in your household needed medical care but could not get it?</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>पिछले पाँच साल में क्या आपके घर के 18 साल से छोटे किसी बच्चे या किशोर की मृत्यु हुई?</t>
+          <t>पिछले 3 महीनों में क्या कभी ऐसा हुआ कि आपके घर में किसी को इलाज की ज़रूरत थी पर मिल नहीं पाया?</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -7992,7 +7996,7 @@
       <c r="I165" s="2" t="inlineStr"/>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Child and Adolescent Mortality (weight 1/12)</t>
+          <t>VASyR 2025 barriers_health_case_access_phc_m (primary-care access barriers); Lyons et al. 2023 Table 2 indicator 2 'healthcare access'</t>
         </is>
       </c>
     </row>
@@ -8012,7 +8016,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>birth_last_5y</t>
+          <t>child_death_5y</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -8022,12 +8026,12 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>In the last five years, did any woman in your household give birth?</t>
+          <t>In the last five years, has any child or young person under 18 in your household died?</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>पिछले पाँच साल में क्या आपके घर की किसी महिला ने बच्चे को जन्म दिया?</t>
+          <t>पिछले पाँच साल में क्या आपके घर के 18 साल से छोटे किसी बच्चे या किशोर की मृत्यु हुई?</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -8038,7 +8042,7 @@
       <c r="I166" s="2" t="inlineStr"/>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (weight 1/12)</t>
+          <t>NITI Aayog National MPI, Child and Adolescent Mortality (weight 1/12)</t>
         </is>
       </c>
     </row>
@@ -8058,22 +8062,22 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>anc_4_visits</t>
+          <t>birth_last_5y</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>For the most recent birth, did she have at least four check-ups before the delivery?</t>
+          <t>In the last five years, did any woman in your household give birth?</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>सबसे हाल के जन्म के लिए, क्या डिलीवरी से पहले उनकी कम से कम चार बार जाँच हुई थी?</t>
+          <t>पिछले पाँच साल में क्या आपके घर की किसी महिला ने बच्चे को जन्म दिया?</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8081,14 +8085,10 @@
           <t>0 No | 1 Yes</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if birth_last_5y = 1</t>
-        </is>
-      </c>
+      <c r="I167" s="2" t="inlineStr"/>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (antenatal care limb)</t>
+          <t>NITI Aayog National MPI, Maternal Health (weight 1/12)</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>skilled_birth_attendant</t>
+          <t>anc_4_visits</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -8118,17 +8118,17 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>Who conducted that delivery — a doctor, a nurse or ANM, an ASHA or Anganwadi worker, a dai, or nobody trained?</t>
+          <t>For the most recent birth, did she have at least four check-ups before the delivery?</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>वह डिलीवरी किसने कराई — डॉक्टर, नर्स या एएनएम, आशा या आँगनवाड़ी कार्यकर्ता, दाई, या कोई प्रशिक्षित व्यक्ति नहीं?</t>
+          <t>सबसे हाल के जन्म के लिए, क्या डिलीवरी से पहले उनकी कम से कम चार बार जाँच हुई थी?</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>1 Doctor | 2 Nurse, ANM or LHV | 3 ASHA or Anganwadi worker only | 4 Dai (traditional birth attendant) | 5 Nobody trained; family only</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (assisted delivery limb); skilled-provider definition per NFHS</t>
+          <t>NITI Aayog National MPI, Maternal Health (antenatal care limb)</t>
         </is>
       </c>
     </row>
@@ -8148,43 +8148,47 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Food security, shocks and coping</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>distress_event_last365d</t>
+          <t>skilled_birth_attendant</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>select multiple</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did any of these happen — to your household, or to the Yatra route you work on? Check every one that applies.</t>
+          <t>Who conducted that delivery — a doctor, a nurse or ANM, an ASHA or Anganwadi worker, a dai, or nobody trained?</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में इनमें से क्या-क्या हुआ — आपके घर के साथ, या जिस यात्रा मार्ग पर आप काम करते हैं उस पर? जो-जो हुआ, सब चुनिए।</t>
+          <t>वह डिलीवरी किसने कराई — डॉक्टर, नर्स या एएनएम, आशा या आँगनवाड़ी कार्यकर्ता, दाई, या कोई प्रशिक्षित व्यक्ति नहीं?</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>9 Nothing of this kind happened | 1 Serious illness or death of an earning member | 2 Crop failure or livestock loss | 3 Damage from a natural disaster (flood, landslide, fire) | 4 Loss of business, goods or assets | 5 Road or bridge blocked, route closed | 6 Yatra stopped early or badly disrupted | 7 Sharp fall in customers or prices | 8 Lost the work or the work stopped</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr"/>
+          <t>1 Doctor | 2 Nurse, ANM or LHV | 3 ASHA or Anganwadi worker only | 4 Dai (traditional birth attendant) | 5 Nobody trained; family only</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if birth_last_5y = 1</t>
+        </is>
+      </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>VEP exposure covariate (Azeem et al. 2016); shock inventory following Gunther and Harttgen 2009, via Fujii 2016 section 4</t>
+          <t>NITI Aayog National MPI, Maternal Health (assisted delivery limb); skilled-provider definition per NFHS</t>
         </is>
       </c>
     </row>
@@ -8204,33 +8208,33 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>shock_work_lost_weeks</t>
+          <t>distress_event_last365d</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select multiple</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>Thinking of whichever of those hit you hardest — about how many weeks of work did you lose because of it? (0 if none)</t>
+          <t>In the last 12 months, did any of these happen — to your household, or to the Yatra route you work on? Check every one that applies.</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>इनमें से जो सबसे भारी पड़ा — उसके कारण लगभग कितने हफ़्ते का काम छूटा? (कुछ न छूटा हो तो 0)</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr"/>
-      <c r="I170" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if distress_event_last365d names a real shock (not code 9, nothing happened)</t>
-        </is>
-      </c>
+          <t>पिछले 12 महीनों में इनमें से क्या-क्या हुआ — आपके घर के साथ, या जिस यात्रा मार्ग पर आप काम करते हैं उस पर? जो-जो हुआ, सब चुनिए।</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>9 Nothing of this kind happened | 1 Serious illness or death of an earning member | 2 Crop failure or livestock loss | 3 Damage from a natural disaster (flood, landslide, fire) | 4 Loss of business, goods or assets | 5 Road or bridge blocked, route closed | 6 Yatra stopped early or badly disrupted | 7 Sharp fall in customers or prices | 8 Lost the work or the work stopped</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr"/>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>Ligon and Schechter 2003; Dercon and Krishnan 2000 (VER needs shock magnitude, not only incidence)</t>
+          <t>VEP exposure covariate (Azeem et al. 2016); shock inventory following Gunther and Harttgen 2009, via Fujii 2016 section 4</t>
         </is>
       </c>
     </row>
@@ -8250,22 +8254,22 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>shock_money_spent</t>
+          <t>shock_work_lost_weeks</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>And about how much money did your household have to spend because of it — treatment, repairs, replacing what was lost? (Rs, 0 if nothing)</t>
+          <t>Thinking of whichever of those hit you hardest — about how many weeks of work did you lose because of it? (0 if none)</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>और उसके कारण आपके घर को लगभग कितना पैसा ख़र्च करना पड़ा — इलाज, मरम्मत, जो नुक़सान हुआ उसे पूरा करना? (रुपये, कुछ नहीं तो 0)</t>
+          <t>इनमें से जो सबसे भारी पड़ा — उसके कारण लगभग कितने हफ़्ते का काम छूटा? (कुछ न छूटा हो तो 0)</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr"/>
@@ -8296,29 +8300,25 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>shock_month</t>
+          <t>shock_money_spent</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>And in which month did that one happen?</t>
+          <t>And about how much money did your household have to spend because of it — treatment, repairs, replacing what was lost? (Rs, 0 if nothing)</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>और वह किस महीने हुआ था?</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>1 January | 2 February | 3 March | 4 April | 5 May | 6 June | 7 July | 8 August | 9 September | 10 October | 11 November | 12 December</t>
-        </is>
-      </c>
+          <t>और उसके कारण आपके घर को लगभग कितना पैसा ख़र्च करना पड़ा — इलाज, मरम्मत, जो नुक़सान हुआ उसे पूरा करना? (रुपये, कुछ नहीं तो 0)</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr"/>
       <c r="I172" s="2" t="inlineStr">
         <is>
           <t>Ask only if distress_event_last365d names a real shock (not code 9, nothing happened)</t>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>Dercon and Krishnan 2000 (seasonal timing of shocks); project design</t>
+          <t>Ligon and Schechter 2003; Dercon and Krishnan 2000 (VER needs shock magnitude, not only incidence)</t>
         </is>
       </c>
     </row>
@@ -8346,37 +8346,37 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>shock_coping</t>
+          <t>shock_month</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>select multiple</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>How did your household manage? Check every one they used.</t>
+          <t>And in which month did that one happen?</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>आपके घर ने कैसे सँभाला? उन्होंने जो-जो किया, सब चुनिए।</t>
+          <t>और वह किस महीने हुआ था?</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>1 Used savings | 2 Borrowed money | 3 Sold or pawned assets | 4 Cut consumption | 5 Help from relatives/community | 6 Paid it out of normal earnings, nothing given up | 7 Something else (say what)</t>
+          <t>1 January | 2 February | 3 March | 4 April | 5 May | 6 June | 7 July | 8 August | 9 September | 10 October | 11 November | 12 December</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>Ask only if any shock was reported</t>
+          <t>Ask only if distress_event_last365d names a real shock (not code 9, nothing happened)</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
+          <t>Dercon and Krishnan 2000 (seasonal timing of shocks); project design</t>
         </is>
       </c>
     </row>
@@ -8396,29 +8396,37 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_yatra_wk</t>
+          <t>shock_coping</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select multiple</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
+          <t>How did your household manage? Check every one they used.</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
-        </is>
-      </c>
-      <c r="H174" s="2" t="inlineStr"/>
-      <c r="I174" s="2" t="inlineStr"/>
+          <t>आपके घर ने कैसे सँभाला? उन्होंने जो-जो किया, सब चुनिए।</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>1 Used savings | 2 Borrowed money | 3 Sold or pawned assets | 4 Cut consumption | 5 Help from relatives/community | 6 Paid it out of normal earnings, nothing given up | 7 Something else (say what)</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if any shock was reported</t>
+        </is>
+      </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, which is not included in this instrument. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking.</t>
+          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
         </is>
       </c>
     </row>
@@ -8438,7 +8446,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_offseason_wk</t>
+          <t>cope_less_pref_food_yatra_wk</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -8448,12 +8456,12 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr"/>
@@ -8480,7 +8488,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>cope_borrow_food_yatra_wk</t>
+          <t>cope_less_pref_food_offseason_wk</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -8490,12 +8498,12 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr"/>
@@ -8522,7 +8530,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>cope_borrow_food_offseason_wk</t>
+          <t>cope_borrow_food_yatra_wk</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -8532,12 +8540,12 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr"/>
@@ -8564,7 +8572,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_meals_yatra_wk</t>
+          <t>cope_borrow_food_offseason_wk</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -8574,12 +8582,12 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr"/>
@@ -8606,7 +8614,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_meals_offseason_wk</t>
+          <t>cope_reduce_meals_yatra_wk</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -8616,12 +8624,12 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr"/>
@@ -8648,7 +8656,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_portion_yatra_wk</t>
+          <t>cope_reduce_meals_offseason_wk</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -8658,12 +8666,12 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr"/>
@@ -8690,7 +8698,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_portion_offseason_wk</t>
+          <t>cope_reduce_portion_yatra_wk</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -8700,12 +8708,12 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr"/>
@@ -8732,7 +8740,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>cope_restrict_adult_yatra_wk</t>
+          <t>cope_reduce_portion_offseason_wk</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -8742,12 +8750,12 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr"/>
@@ -8774,7 +8782,7 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>cope_restrict_adult_offseason_wk</t>
+          <t>cope_restrict_adult_yatra_wk</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -8784,12 +8792,12 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr"/>
@@ -8806,43 +8814,39 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Ropeway</t>
+          <t>Food security, shocks and coping</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>ropeway_stance</t>
+          <t>cope_restrict_adult_offseason_wk</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>A ropeway is proposed between Gaurikund and Kedarnath. Are you in favour, neutral, or against?</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>गौरीकुंड से केदारनाथ तक रोपवे बनाने की बात चल रही है। आप इसके पक्ष में हैं, बीच में हैं, या ख़िलाफ़ हैं?</t>
-        </is>
-      </c>
-      <c r="H184" s="2" t="inlineStr">
-        <is>
-          <t>1 Support | 2 Neutral | 3 Oppose | 98 Prefer not to say</t>
-        </is>
-      </c>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr"/>
       <c r="I184" s="2" t="inlineStr"/>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>Project design</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, which is not included in this instrument. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking.</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8866,7 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>ropeway_expect_work</t>
+          <t>ropeway_stance</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -8872,27 +8876,23 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>If the ropeway is built, what do you think will happen to your own work? More work for you; less work; about the same; or don't know?</t>
+          <t>A ropeway is proposed between Gaurikund and Kedarnath. Are you in favour, neutral, or against?</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>अगर रोपवे बन गया, तो आपके अपने काम पर क्या असर होगा? मेरे लिए ज़्यादा काम; मेरे लिए कम काम; लगभग वैसा ही; या पता नहीं?</t>
+          <t>गौरीकुंड से केदारनाथ तक रोपवे बनाने की बात चल रही है। आप इसके पक्ष में हैं, बीच में हैं, या ख़िलाफ़ हैं?</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>1 More work for me | 2 Less work for me | 3 About the same | 97 Don't know</t>
-        </is>
-      </c>
-      <c r="I185" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if site = 1 (Kedarnath route)</t>
-        </is>
-      </c>
+          <t>1 Support | 2 Neutral | 3 Oppose | 98 Prefer not to say</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr"/>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>Pelz et al. 2024, Energy Policy 186:113973 (concept: perceived effect on livelihoods; wording ours)</t>
+          <t>Project design</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>ropeway_expect_jobs</t>
+          <t>ropeway_expect_work</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -8922,17 +8922,17 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>Who do you think will get most of the jobs the ropeway creates? People from these villages; people from outside the area; nobody will get jobs; or don't know?</t>
+          <t>If the ropeway is built, what do you think will happen to your own work? More work for you; less work; about the same; or don't know?</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>रोपवे में जो नौकरियाँ बनेंगी, वे ज़्यादातर किसे मिलेंगी? इन गाँवों के लोगों को; इलाके के बाहर के लोगों को; किसी को नहीं मिलेंगी; या पता नहीं?</t>
+          <t>अगर रोपवे बन गया, तो आपके अपने काम पर क्या असर होगा? मेरे लिए ज़्यादा काम; मेरे लिए कम काम; लगभग वैसा ही; या पता नहीं?</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>1 People from these villages | 2 People from outside the area | 3 Nobody will get jobs | 97 Don't know</t>
+          <t>1 More work for me | 2 Less work for me | 3 About the same | 97 Don't know</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>Pelz et al. 2024, Energy Policy 186:113973 (concept: local vs outside benefit; wording ours)</t>
+          <t>Pelz et al. 2024, Energy Policy 186:113973 (concept: perceived effect on livelihoods; wording ours)</t>
         </is>
       </c>
     </row>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>ropeway_trust</t>
+          <t>ropeway_expect_jobs</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -8972,17 +8972,17 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>Do you think the ropeway will improve the livelihoods of people here? Yes; no; or don't know?</t>
+          <t>Who do you think will get most of the jobs the ropeway creates? People from these villages; people from outside the area; nobody will get jobs; or don't know?</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>क्या आपको लगता है कि रोपवे से यहाँ के लोगों की रोज़ी-रोटी सुधरेगी? हाँ; नहीं; या पता नहीं?</t>
+          <t>रोपवे में जो नौकरियाँ बनेंगी, वे ज़्यादातर किसे मिलेंगी? इन गाँवों के लोगों को; इलाके के बाहर के लोगों को; किसी को नहीं मिलेंगी; या पता नहीं?</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
+          <t>1 People from these villages | 2 People from outside the area | 3 Nobody will get jobs | 97 Don't know</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>Pelz et al. 2024, Energy Policy 186:113973 (Fig. 4B, trust in the company; wording ours)</t>
+          <t>Pelz et al. 2024, Energy Policy 186:113973 (concept: local vs outside benefit; wording ours)</t>
         </is>
       </c>
     </row>
@@ -9012,33 +9012,37 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>trek_dependent</t>
+          <t>ropeway_trust</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>Is your main work carrying, transporting or guiding people or goods on foot along the pilgrimage trek?</t>
+          <t>Do you think the ropeway will improve the livelihoods of people here? Yes; no; or don't know?</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
+          <t>क्या आपको लगता है कि रोपवे से यहाँ के लोगों की रोज़ी-रोटी सुधरेगी? हाँ; नहीं; या पता नहीं?</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I188" s="2" t="inlineStr"/>
+          <t>0 No | 1 Yes | 97 Don't know</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if site = 1 (Kedarnath route)</t>
+        </is>
+      </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
+          <t>Pelz et al. 2024, Energy Policy 186:113973 (Fig. 4B, trust in the company; wording ours)</t>
         </is>
       </c>
     </row>
@@ -9048,43 +9052,43 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Ropeway</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>job_situation</t>
+          <t>trek_dependent</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>During the last month, what were you mainly doing? Ask it open and code the closest one; do not read the list out.</t>
+          <t>Is your main work carrying, transporting or guiding people or goods on foot along the pilgrimage trek?</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>पिछले महीने आप मुख्य रूप से क्या कर रहे थे? खुला पूछें और जो सबसे मिलता हो वह कोड करें; पूरी सूची पढ़कर न सुनाएँ।</t>
+          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>1 Works for pay full-time | 2 Works for pay part-time or occasional jobs | 3 Studies and works | 4 Only studies | 5 Being trained for work only | 6 Retired or pensioned | 7 Unpaid household tasks or caring for others | 8 Unemployed, actively seeking work | 9 Sick or disabled, cannot work | 10 Neither studying, working nor seeking work | 97 Does not know</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr"/>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
+          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
         </is>
       </c>
     </row>
@@ -9104,7 +9108,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>job_permanence</t>
+          <t>job_situation</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -9114,27 +9118,23 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
+          <t>During the last month, what were you mainly doing? Ask it open and code the closest one; do not read the list out.</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
+          <t>पिछले महीने आप मुख्य रूप से क्या कर रहे थे? खुला पूछें और जो सबसे मिलता हो वह कोड करें; पूरी सूची पढ़कर न सुनाएँ।</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>1 Permanent | 2 Seasonal or temporary | 3 Occasional or casual | 4 On probation | 5 Fixed-term</t>
-        </is>
-      </c>
-      <c r="I190" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
-        </is>
-      </c>
+          <t>1 Works for pay full-time | 2 Works for pay part-time or occasional jobs | 3 Studies and works | 4 Only studies | 5 Being trained for work only | 6 Retired or pensioned | 7 Unpaid household tasks or caring for others | 8 Unemployed, actively seeking work | 9 Sick or disabled, cannot work | 10 Neither studying, working nor seeking work | 97 Does not know</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr"/>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>contract_status</t>
+          <t>job_permanence</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -9164,27 +9164,27 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
+          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
+          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, signed | 2 Yes, but not yet signed | 3 No contract</t>
+          <t>1 Permanent | 2 Seasonal or temporary | 3 Occasional or casual | 4 On probation | 5 Fixed-term</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working); and employment_type is 3 or 4 (wage workers) — self-employed skip to the next question</t>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
         </is>
       </c>
     </row>
@@ -9204,37 +9204,37 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>workplace_registered</t>
+          <t>contract_status</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
+          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
+          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 Yes, signed | 2 Yes, but not yet signed | 3 No contract</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working); and employment_type is 3 or 4 (wage workers) — self-employed skip to the next question</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
         </is>
       </c>
     </row>
@@ -9254,27 +9254,27 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>pension_contrib</t>
+          <t>workplace_registered</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
+          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
+          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, employer deducts it | 2 Yes, contributes voluntarily | 3 No</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
         </is>
       </c>
     </row>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>work_health_ins</t>
+          <t>pension_contrib</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -9314,17 +9314,17 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
+          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
+          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, through work | 2 Only private or other insurance | 3 None | 4 Don't know</t>
+          <t>1 Yes, employer deducts it | 2 Yes, contributes voluntarily | 3 No</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
         </is>
       </c>
     </row>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>leave_rights</t>
+          <t>work_health_ins</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -9364,17 +9364,17 @@
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
+          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
+          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
+          <t>1 Yes, through work | 2 Only private or other insurance | 3 None | 4 Don't know</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
         </is>
       </c>
     </row>
@@ -9404,7 +9404,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>injured_ever</t>
+          <t>leave_rights</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -9414,12 +9414,12 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>Have you ever been physically injured at your workplace?</t>
+          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
+          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -9434,7 +9434,7 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
         </is>
       </c>
     </row>
@@ -9454,7 +9454,7 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>workplace_injury_12m</t>
+          <t>injured_ever</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -9464,12 +9464,12 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, was anyone physically injured at your workplace because of work?</t>
+          <t>Have you ever been physically injured at your workplace?</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी?</t>
+          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q20 (split into injury and death)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
         </is>
       </c>
     </row>
@@ -9504,7 +9504,7 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>workplace_death_12m</t>
+          <t>workplace_injury_12m</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -9514,12 +9514,12 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>And in the last 12 months, did anyone die at your workplace because of work?</t>
+          <t>In the last 12 months, was anyone physically injured at your workplace because of work?</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>और पिछले 12 महीनों में, क्या आपके काम की जगह पर काम की वजह से किसी की मौत हुई?</t>
+          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी?</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>wants_more_work</t>
+          <t>workplace_death_12m</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>Would you like to work more hours than you do?</t>
+          <t>And in the last 12 months, did anyone die at your workplace because of work?</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
+          <t>और पिछले 12 महीनों में, क्या आपके काम की जगह पर काम की वजह से किसी की मौत हुई?</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>Ask if job_situation is 1 to 7 (Apablaza routes codes 4-7 straight to this question)</t>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q20 (split into injury and death)</t>
         </is>
       </c>
     </row>
@@ -9604,33 +9604,37 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>more_hours_day</t>
+          <t>wants_more_work</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>On a working day, how many MORE hours would you like to work?</t>
+          <t>Would you like to work more hours than you do?</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
-        </is>
-      </c>
-      <c r="H200" s="2" t="inlineStr"/>
+          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes | 97 Don't know</t>
+        </is>
+      </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>Ask if wants_more_work = 1, or if job_situation = 8 (Apablaza routes the unemployed-and-seeking category here directly)</t>
+          <t>Ask if job_situation is 1 to 7 (Apablaza routes codes 4-7 straight to this question)</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9654,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>months_looked_for_work</t>
+          <t>more_hours_day</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -9660,23 +9664,23 @@
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
+          <t>On a working day, how many MORE hours would you like to work?</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
+          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr"/>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>Ask if any month in the calendar is 'No paid work', or if job_situation = 8</t>
+          <t>Ask if wants_more_work = 1, or if job_situation = 8 (Apablaza routes the unemployed-and-seeking category here directly)</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
         </is>
       </c>
     </row>
@@ -9696,33 +9700,33 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>first_job_ever</t>
+          <t>months_looked_for_work</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>Was your current work the first paid job you ever had?</t>
+          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
-        </is>
-      </c>
-      <c r="H202" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
-        </is>
-      </c>
-      <c r="I202" s="2" t="inlineStr"/>
+          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr"/>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>Ask if any month in the calendar is 'No paid work', or if job_situation = 8</t>
+        </is>
+      </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
         </is>
       </c>
     </row>
@@ -9742,7 +9746,7 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>higher_ed</t>
+          <t>first_job_ever</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -9752,12 +9756,12 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>Have you completed any college, diploma or university course?</t>
+          <t>Was your current work the first paid job you ever had?</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>क्या आपने कॉलेज, डिप्लोमा या यूनिवर्सिटी का कोई कोर्स पूरा किया है?</t>
+          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -9765,14 +9769,10 @@
           <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
-      <c r="I203" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
-        </is>
-      </c>
+      <c r="I203" s="2" t="inlineStr"/>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 employment table, occupational status (1/8)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
         </is>
       </c>
     </row>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>social_security_any</t>
+          <t>higher_ed</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>Are you enrolled in any pension, insurance or social-security scheme? For example, EPFO or PM-SYM pension, or Ayushman Bharat health cover.</t>
+          <t>Have you completed any college, diploma or university course?</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>क्या आप किसी पेंशन, बीमा या सरकारी सामाजिक सुरक्षा योजना में शामिल हैं? जैसे EPFO या PM-SYM पेंशन, या आयुष्मान भारत स्वास्थ्य कवर।</t>
+          <t>क्या आपने कॉलेज, डिप्लोमा या यूनिवर्सिटी का कोई कोर्स पूरा किया है?</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 employment table, employment security (1/8)</t>
+          <t>Apablaza et al. 2026, Appendix 2 employment table, occupational status (1/8)</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>intens_speed</t>
+          <t>social_security_any</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -9852,12 +9852,12 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you work at very high speed?</t>
+          <t>Are you enrolled in any pension, insurance or social-security scheme? For example, EPFO or PM-SYM pension, or Ayushman Bharat health cover.</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप बहुत तेज़ रफ़्तार से काम करते हैं?</t>
+          <t>क्या आप किसी पेंशन, बीमा या सरकारी सामाजिक सुरक्षा योजना में शामिल हैं? जैसे EPFO या PM-SYM पेंशन, या आयुष्मान भारत स्वास्थ्य कवर।</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 employment table, work intensity (1/16)</t>
+          <t>Apablaza et al. 2026, Appendix 2 employment table, employment security (1/8)</t>
         </is>
       </c>
     </row>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>intens_deadline</t>
+          <t>intens_speed</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you work to tight deadlines?</t>
+          <t>For more than half of your working day, do you work at very high speed?</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आपको कड़ी समय-सीमा में काम करना पड़ता है?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप बहुत तेज़ रफ़्तार से काम करते हैं?</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>intens_time</t>
+          <t>intens_deadline</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you not have enough time to finish your tasks?</t>
+          <t>For more than half of your working day, do you work to tight deadlines?</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आपके पास काम पूरा करने के लिए काफ़ी समय नहीं होता?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आपको कड़ी समय-सीमा में काम करना पड़ता है?</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>posture_position</t>
+          <t>intens_time</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -10002,12 +10002,12 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you work in a tiring or painful position?</t>
+          <t>For more than half of your working day, do you not have enough time to finish your tasks?</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप थकाने वाली या दर्द वाली स्थिति में काम करते हैं?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आपके पास काम पूरा करने के लिए काफ़ी समय नहीं होता?</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 employment table, posture risk (1/16)</t>
+          <t>Apablaza et al. 2026, Appendix 2 employment table, work intensity (1/16)</t>
         </is>
       </c>
     </row>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>posture_loads</t>
+          <t>posture_position</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you carry or move heavy loads?</t>
+          <t>For more than half of your working day, do you work in a tiring or painful position?</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप भारी बोझ उठाते या ढोते हैं?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप थकाने वाली या दर्द वाली स्थिति में काम करते हैं?</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>posture_repetitive</t>
+          <t>posture_loads</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -10102,12 +10102,12 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>For more than half of your working day, do you make the same movements again and again?</t>
+          <t>For more than half of your working day, do you carry or move heavy loads?</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप एक ही तरह की हरकत बार-बार करते हैं?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप भारी बोझ उठाते या ढोते हैं?</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>phys_noise</t>
+          <t>posture_repetitive</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>For more than half of your working day, are you exposed to loud noise?</t>
+          <t>For more than half of your working day, do you make the same movements again and again?</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप तेज़ शोर में रहते हैं?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप एक ही तरह की हरकत बार-बार करते हैं?</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 employment table, physical risk (1/16)</t>
+          <t>Apablaza et al. 2026, Appendix 2 employment table, posture risk (1/16)</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>phys_temperature</t>
+          <t>phys_noise</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>For more than half of your working day, are you exposed to extreme heat or cold?</t>
+          <t>For more than half of your working day, are you exposed to loud noise?</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप बहुत गर्मी या बहुत ठंड में रहते हैं?</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप तेज़ शोर में रहते हैं?</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -10232,17 +10232,17 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Tasks and skills (short block)</t>
+          <t>Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>tk_load</t>
+          <t>phys_temperature</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -10252,23 +10252,27 @@
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you load, unload, stack or count goods? </t>
+          <t>For more than half of your working day, are you exposed to extreme heat or cold?</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>काम के दिन के आधे से ज़्यादा समय, क्या आप बहुत गर्मी या बहुत ठंड में रहते हैं?</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
-        </is>
-      </c>
-      <c r="I213" s="2" t="inlineStr"/>
+          <t>0 No | 1 Yes | 97 Don't know</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+        </is>
+      </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
+          <t>Apablaza et al. 2026, Appendix 2 employment table, physical risk (1/16)</t>
         </is>
       </c>
     </row>
@@ -10288,7 +10292,7 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>tk_drive</t>
+          <t>tk_load</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -10298,12 +10302,12 @@
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you drive a motor vehicle? </t>
+          <t xml:space="preserve">Do you load, unload, stack or count goods? </t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
@@ -10314,7 +10318,7 @@
       <c r="I214" s="2" t="inlineStr"/>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
+          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
         </is>
       </c>
     </row>
@@ -10334,7 +10338,7 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>tk_engine</t>
+          <t>tk_drive</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -10344,12 +10348,12 @@
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you operate an engine or machine? </t>
+          <t xml:space="preserve">Do you drive a motor vehicle? </t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
@@ -10360,7 +10364,7 @@
       <c r="I215" s="2" t="inlineStr"/>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
+          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
         </is>
       </c>
     </row>
@@ -10380,7 +10384,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>tk_electric</t>
+          <t>tk_engine</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -10390,12 +10394,12 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you do electrical or wiring work? </t>
+          <t xml:space="preserve">Do you operate an engine or machine? </t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -10406,7 +10410,7 @@
       <c r="I216" s="2" t="inlineStr"/>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10430,7 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>tk_safety</t>
+          <t>tk_electric</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -10436,12 +10440,12 @@
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you check equipment or the route for safety? </t>
+          <t xml:space="preserve">Do you do electrical or wiring work? </t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -10452,7 +10456,7 @@
       <c r="I217" s="2" t="inlineStr"/>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
+          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
         </is>
       </c>
     </row>
@@ -10472,7 +10476,7 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>tk_sell</t>
+          <t>tk_safety</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -10482,12 +10486,12 @@
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you sell goods or services? </t>
+          <t xml:space="preserve">Do you check equipment or the route for safety? </t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -10498,7 +10502,7 @@
       <c r="I218" s="2" t="inlineStr"/>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
         </is>
       </c>
     </row>
@@ -10518,7 +10522,7 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>tk_cash</t>
+          <t>tk_sell</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -10528,12 +10532,12 @@
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you handle cash and payments? </t>
+          <t xml:space="preserve">Do you sell goods or services? </t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -10544,7 +10548,7 @@
       <c r="I219" s="2" t="inlineStr"/>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>Autor and Handel 2013; NCO 5131.0401</t>
+          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10568,7 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>tk_cook</t>
+          <t>tk_cash</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -10574,12 +10578,12 @@
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you cook or prepare food or drink? </t>
+          <t xml:space="preserve">Do you handle cash and payments? </t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -10590,7 +10594,7 @@
       <c r="I220" s="2" t="inlineStr"/>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>NCO 5120.0300 cook</t>
+          <t>Autor and Handel 2013; NCO 5131.0401</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10614,7 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>tk_serve</t>
+          <t>tk_cook</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -10620,12 +10624,12 @@
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you serve guests or customers? </t>
+          <t xml:space="preserve">Do you cook or prepare food or drink? </t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -10636,7 +10640,7 @@
       <c r="I221" s="2" t="inlineStr"/>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
+          <t>NCO 5120.0300 cook</t>
         </is>
       </c>
     </row>
@@ -10656,7 +10660,7 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>tk_clean</t>
+          <t>tk_serve</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -10666,12 +10670,12 @@
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you clean rooms or public areas? </t>
+          <t xml:space="preserve">Do you serve guests or customers? </t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -10682,7 +10686,7 @@
       <c r="I222" s="2" t="inlineStr"/>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
+          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10706,7 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>tk_guide</t>
+          <t>tk_clean</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -10712,12 +10716,12 @@
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you guide or explain things to visitors? </t>
+          <t xml:space="preserve">Do you clean rooms or public areas? </t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
@@ -10728,7 +10732,7 @@
       <c r="I223" s="2" t="inlineStr"/>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
+          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
         </is>
       </c>
     </row>
@@ -10748,7 +10752,7 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>tk_coord</t>
+          <t>tk_guide</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -10758,12 +10762,12 @@
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you coordinate work by phone, radio or signals? </t>
+          <t xml:space="preserve">Do you guide or explain things to visitors? </t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -10774,7 +10778,7 @@
       <c r="I224" s="2" t="inlineStr"/>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>NCO 8343.1700 ropeway operator</t>
+          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
         </is>
       </c>
     </row>
@@ -10794,37 +10798,33 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>drove_twowheeler</t>
+          <t>tk_coord</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
+          <t xml:space="preserve">Do you coordinate work by phone, radio or signals? </t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
+          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I225" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if tk_drive is 1 or 2</t>
-        </is>
-      </c>
+          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr"/>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>Level ladder without licences: people drive without holding a licence</t>
+          <t>NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>drove_car</t>
+          <t>drove_twowheeler</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -10854,12 +10854,12 @@
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>... a car or jeep?</t>
+          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>...कार या जीप?</t>
+          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>Level ladder without licences</t>
+          <t>Level ladder without licences: people drive without holding a licence</t>
         </is>
       </c>
     </row>
@@ -10894,7 +10894,7 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>drove_heavy</t>
+          <t>drove_car</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>... a truck or bus?</t>
+          <t>... a car or jeep?</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>...ट्रक या बस?</t>
+          <t>...कार या जीप?</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -10944,7 +10944,7 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>read_at_work</t>
+          <t>drove_heavy</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -10954,12 +10954,12 @@
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
+          <t>... a truck or bus?</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
+          <t>...ट्रक या बस?</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -10967,10 +10967,14 @@
           <t>0 No | 1 Yes</t>
         </is>
       </c>
-      <c r="I228" s="2" t="inlineStr"/>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if tk_drive is 1 or 2</t>
+        </is>
+      </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>STEP module 6A</t>
+          <t>Level ladder without licences</t>
         </is>
       </c>
     </row>
@@ -10990,7 +10994,7 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>calc_at_work</t>
+          <t>read_at_work</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -11000,12 +11004,12 @@
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>In your work, do you work out prices or costs?</t>
+          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
+          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11026,43 +11030,43 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Access to common resources (short block)</t>
+          <t>Tasks and skills (short block)</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>cpr_firewood</t>
+          <t>calc_at_work</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did anyone in your household collect firewood or dead wood from common land or forest near here?</t>
+          <t>In your work, do you work out prices or costs?</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने आस-पास की साझा ज़मीन या जंगल से लकड़ी या सूखी टहनियाँ इकट्ठी कीं?</t>
+          <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I230" s="2" t="inlineStr"/>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001, natural capital: resource stocks from which resource flows are derived (definitions list); item wording is ours</t>
+          <t>STEP module 6A</t>
         </is>
       </c>
     </row>
@@ -11082,7 +11086,7 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>cpr_fodder</t>
+          <t>cpr_firewood</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -11092,12 +11096,12 @@
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did anyone in your household cut grass or fodder from common land near here?</t>
+          <t>In the last 12 months, did anyone in your household collect firewood or dead wood from common land or forest near here?</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने साझा ज़मीन से घास या चारा काटा?</t>
+          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने आस-पास की साझा ज़मीन या जंगल से लकड़ी या सूखी टहनियाँ इकट्ठी कीं?</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11108,7 +11112,7 @@
       <c r="I231" s="2" t="inlineStr"/>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001, natural capital: resource stocks from which resource flows are derived; item wording is ours</t>
+          <t>Krantz 2001, natural capital: resource stocks from which resource flows are derived (definitions list); item wording is ours</t>
         </is>
       </c>
     </row>
@@ -11128,7 +11132,7 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>cpr_forest_produce</t>
+          <t>cpr_fodder</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -11138,12 +11142,12 @@
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did anyone in your household collect herbs, mushrooms or wild fruit from the forest?</t>
+          <t>In the last 12 months, did anyone in your household cut grass or fodder from common land near here?</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने जंगल से जड़ी-बूटी, मशरूम या जंगली फल इकट्ठे किए?</t>
+          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने साझा ज़मीन से घास या चारा काटा?</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11154,7 +11158,7 @@
       <c r="I232" s="2" t="inlineStr"/>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001, natural capital (resource flows from stocks); item wording is ours</t>
+          <t>Krantz 2001, natural capital: resource stocks from which resource flows are derived; item wording is ours</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11178,7 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>cpr_grazing</t>
+          <t>cpr_forest_produce</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -11184,12 +11188,12 @@
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did any animal of your household graze on common pasture?</t>
+          <t>In the last 12 months, did anyone in your household collect herbs, mushrooms or wild fruit from the forest?</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर का कोई जानवर साझा चरागाह में चरा?</t>
+          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने जंगल से जड़ी-बूटी, मशरूम या जंगली फल इकट्ठे किए?</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -11200,7 +11204,7 @@
       <c r="I233" s="2" t="inlineStr"/>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001, natural capital: resource stocks from which resource flows are derived; item wording is ours</t>
+          <t>Krantz 2001, natural capital (resource flows from stocks); item wording is ours</t>
         </is>
       </c>
     </row>
@@ -11220,7 +11224,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>cpr_restricted</t>
+          <t>cpr_grazing</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -11230,12 +11234,12 @@
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, has anyone in your household been stopped from using a common forest, pasture or path, or been asked to pay to use it?</t>
+          <t>In the last 12 months, did any animal of your household graze on common pasture?</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी को साझा जंगल, चरागाह या रास्ते के इस्तेमाल से रोका गया, या इसके लिए पैसे देने को कहा गया?</t>
+          <t>पिछले 12 महीनों में, क्या आपके घर का कोई जानवर साझा चरागाह में चरा?</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -11246,7 +11250,7 @@
       <c r="I234" s="2" t="inlineStr"/>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001, access ('the opportunity in practice to use a resource') and claims ('demands and appeals'); item wording is ours</t>
+          <t>Krantz 2001, natural capital: resource stocks from which resource flows are derived; item wording is ours</t>
         </is>
       </c>
     </row>
@@ -11266,7 +11270,7 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>cpr_lost_access</t>
+          <t>cpr_restricted</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -11276,12 +11280,12 @@
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, has a common place you used to collect from or graze on been closed because of building, road or ropeway work?</t>
+          <t>In the last 12 months, has anyone in your household been stopped from using a common forest, pasture or path, or been asked to pay to use it?</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या कोई साझा जगह, जहाँ आप पहले लकड़ी, घास या चारा लेते थे, निर्माण, सड़क या रोपवे के काम की वजह से बंद हो गई?</t>
+          <t>पिछले 12 महीनों में, क्या आपके घर के किसी को साझा जंगल, चरागाह या रास्ते के इस्तेमाल से रोका गया, या इसके लिए पैसे देने को कहा गया?</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11292,7 +11296,7 @@
       <c r="I235" s="2" t="inlineStr"/>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001, access (as above); the ropeway link is the project's own</t>
+          <t>Krantz 2001, access ('the opportunity in practice to use a resource') and claims ('demands and appeals'); item wording is ours</t>
         </is>
       </c>
     </row>
@@ -11312,7 +11316,7 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>cpr_water_route</t>
+          <t>cpr_lost_access</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -11322,23 +11326,23 @@
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>On your route or near your worksite, can you use a common water source (spring, tap or stream) without paying?</t>
+          <t>In the last 12 months, has a common place you used to collect from or graze on been closed because of building, road or ropeway work?</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>रास्ते पर या काम की जगह के पास, क्या आप कोई साझा पानी का स्रोत (झरना, नल या नदी-नाला) बिना पैसे दिए इस्तेमाल कर सकते हैं?</t>
+          <t>पिछले 12 महीनों में, क्या कोई साझा जगह, जहाँ आप पहले लकड़ी, घास या चारा लेते थे, निर्माण, सड़क या रोपवे के काम की वजह से बंद हो गई?</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, free to use | 2 A source exists but we must pay | 3 No source nearby | 97 Don't know</t>
+          <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
       <c r="I236" s="2" t="inlineStr"/>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001, natural capital (water) and access ('the opportunity in practice to use a resource'); item wording is ours</t>
+          <t>Krantz 2001, access (as above); the ropeway link is the project's own</t>
         </is>
       </c>
     </row>
@@ -11358,7 +11362,7 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>cpr_governance</t>
+          <t>cpr_water_route</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -11368,28 +11372,74 @@
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>In this area, who decides who may use the common land and forest? Ask and code what they name; do not read the list.</t>
+          <t>On your route or near your worksite, can you use a common water source (spring, tap or stream) without paying?</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>इस इलाके की साझा ज़मीन और जंगल का फ़ैसला कौन करता है, कि कौन उसका इस्तेमाल कर सकता है? जो नाम लें वही लिख लें; सूची न पढ़ें।</t>
+          <t>रास्ते पर या काम की जगह के पास, क्या आप कोई साझा पानी का स्रोत (झरना, नल या नदी-नाला) बिना पैसे दिए इस्तेमाल कर सकते हैं?</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>1 Village head or panchayat | 2 Forest department | 3 Local committee or community group | 4 Nobody decides; it is open to all | 97 Don't know</t>
+          <t>1 Yes, free to use | 2 A source exists but we must pay | 3 No source nearby | 97 Don't know</t>
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr"/>
       <c r="J237" s="2" t="inlineStr">
         <is>
+          <t>Krantz 2001, natural capital (water) and access ('the opportunity in practice to use a resource'); item wording is ours</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>Access to common resources (short block)</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>cpr_governance</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>select one</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>In this area, who decides who may use the common land and forest? Ask and code what they name; do not read the list.</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>इस इलाके की साझा ज़मीन और जंगल का फ़ैसला कौन करता है, कि कौन उसका इस्तेमाल कर सकता है? जो नाम लें वही लिख लें; सूची न पढ़ें।</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>1 Village head or panchayat | 2 Forest department | 3 Local committee or community group | 4 Nobody decides; it is open to all | 97 Don't know</t>
+        </is>
+      </c>
+      <c r="I238" s="2" t="inlineStr"/>
+      <c r="J238" s="2" t="inlineStr">
+        <is>
           <t>NO SOURCE ON DISK YET: Krantz does not address governance of common land. To be sourced from Agrawal 2001 or Ostrom 1990 once read on disk</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J237"/>
+  <autoFilter ref="A1:J238"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15625,7 +15675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C153"/>
+  <dimension ref="A1:C154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -16343,7 +16393,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Project design (multiple job-holding)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q8 (shortened to wage workers); categories ours</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -16351,14 +16401,14 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>other_activity_income_pm</t>
+          <t>wage_employer</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q10 (screen); Table 3 (stability)</t>
+          <t>Project design (multiple job-holding)</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
@@ -16366,14 +16416,14 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>tenure_under_1</t>
+          <t>other_activity_income_pm</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q10; Table 3 (stability)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q10 (screen); Table 3 (stability)</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -16381,14 +16431,14 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>years_current_job</t>
+          <t>tenure_under_1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Occupational mobility check; job-history item</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q10; Table 3 (stability)</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
@@ -16396,14 +16446,14 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>prev_occ_change</t>
+          <t>years_current_job</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010 (observed moves are systematically shorter than random moves — the validation test for a task-distance measure); coded to NCO-2015 in the office</t>
+          <t>Occupational mobility check; job-history item</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -16411,14 +16461,14 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>prev_occ</t>
+          <t>prev_occ_change</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Project design (stated destination, for the structural-displacement analysis); coded to NCO-2015 in the office</t>
+          <t>Gathmann and Schonberg 2010 (observed moves are systematically shorter than random moves — the validation test for a task-distance measure); coded to NCO-2015 in the office</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
@@ -16426,14 +16476,14 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>target_occ</t>
+          <t>prev_occ</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Job-history item</t>
+          <t>Project design (stated destination, for the structural-displacement analysis); coded to NCO-2015 in the office</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -16441,14 +16491,14 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>prev_occ_reason</t>
+          <t>target_occ</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>STEP module 2; Chaudhuri et al. 2002 adaptive-capacity covariate</t>
+          <t>Job-history item</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
@@ -16456,14 +16506,14 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>training_received</t>
+          <t>prev_occ_reason</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q14/Q15 (the 'does not know' route out of monthly earnings)</t>
+          <t>STEP module 2; Chaudhuri et al. 2002 adaptive-capacity covariate</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -16471,14 +16521,14 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>knows_monthly_income</t>
+          <t>training_received</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q15; bands to check</t>
+          <t>Apablaza et al. 2026 Q14/Q15 (the 'does not know' route out of monthly earnings)</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
@@ -16486,14 +16536,14 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>earnings_range</t>
+          <t>knows_monthly_income</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q15 (fallback when monthly earnings are not known), adapted to an annual total for a seasonal workforce</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q15; bands to check</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -16501,14 +16551,14 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>income_annual_total</t>
+          <t>earnings_range</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Project design (the Yatra / non-Yatra split needed to reweight an annual total onto the work calendar)</t>
+          <t>Apablaza et al. 2026 Q15 (fallback when monthly earnings are not known), adapted to an annual total for a seasonal workforce</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
@@ -16516,14 +16566,14 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>pct_income_yatra</t>
+          <t>income_annual_total</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season (decomposed as hours/day x days/week, as in the Yatra-season pair)</t>
+          <t>Project design (the Yatra / non-Yatra split needed to reweight an annual total onto the work calendar)</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -16531,14 +16581,14 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>hours_day_offseason</t>
+          <t>pct_income_yatra</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season</t>
+          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season (decomposed as hours/day x days/week, as in the Yatra-season pair)</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
@@ -16546,14 +16596,14 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>days_week_offseason</t>
+          <t>hours_day_offseason</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Project design (distance bucket); NOT an NSS classification — the earlier citation to one was withdrawn 2026-09-28, no NSS schedule is held by this project</t>
+          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -16561,14 +16611,14 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>origin</t>
+          <t>days_week_offseason</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Standard state/UT classification; needed to apply the right poverty line per respondent</t>
+          <t>Project design (distance bucket); NOT an NSS classification — the earlier citation to one was withdrawn 2026-09-28, no NSS schedule is held by this project</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
@@ -16576,14 +16626,14 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>home_state</t>
+          <t>origin</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Rural and urban poverty lines (Sethu et al. 2024)</t>
+          <t>Standard state/UT classification; needed to apply the right poverty line per respondent</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -16591,14 +16641,14 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>home_rural_urban</t>
+          <t>home_state</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Project design; categories from the pilot's own residency_pattern distribution (n=46)</t>
+          <t>Rural and urban poverty lines (Sethu et al. 2024)</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
@@ -16606,14 +16656,14 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>resp_returns_at_closure</t>
+          <t>home_rural_urban</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Project design (split-household measurement, underpinning Module E)</t>
+          <t>Project design; categories from the pilot's own residency_pattern distribution (n=46)</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -16621,14 +16671,14 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>hh_at_home_place</t>
+          <t>resp_returns_at_closure</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Project design (remittance channel as a financial-inclusion and cost measure)</t>
+          <t>Project design (split-household measurement, underpinning Module E)</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
@@ -16636,14 +16686,14 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>remit_mode</t>
+          <t>hh_at_home_place</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Project design (season-specific denominator for per-capita consumption)</t>
+          <t>Project design (remittance channel as a financial-inclusion and cost measure)</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -16651,14 +16701,14 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>n_here_season</t>
+          <t>remit_mode</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Project design (duration of the seasonal relationship)</t>
+          <t>Project design (season-specific denominator for per-capita consumption)</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
@@ -16666,14 +16716,14 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>years_coming_here</t>
+          <t>n_here_season</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Project design (push/pull as a vulnerability covariate)</t>
+          <t>Project design (duration of the seasonal relationship)</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -16681,14 +16731,14 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>came_here_reason</t>
+          <t>years_coming_here</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Project design (catch-all codes lose the case they catch)</t>
+          <t>Project design (push/pull as a vulnerability covariate)</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
@@ -16696,14 +16746,14 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>came_here_reason_other</t>
+          <t>came_here_reason</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Project design (off-season labour migration)</t>
+          <t>Project design (catch-all codes lose the case they catch)</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -16711,14 +16761,14 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>worked_away_in_closure</t>
+          <t>came_here_reason_other</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Project design; coded to NCO-2015 in the office</t>
+          <t>Project design (off-season labour migration)</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
@@ -16726,14 +16776,14 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>closure_work_detail</t>
+          <t>worked_away_in_closure</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Project design; horizoned intention item after VASyR 2025 (move_accom_yesno, asked over a stated 6-month horizon)</t>
+          <t>Project design; coded to NCO-2015 in the office</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -16741,14 +16791,14 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>would_move_for_work</t>
+          <t>closure_work_detail</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Project design (referral channel as a proxy for social capital and for placement debt)</t>
+          <t>Project design; horizoned intention item after VASyR 2025 (move_accom_yesno, asked over a stated 6-month horizon)</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
@@ -16756,14 +16806,14 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>migration_referral</t>
+          <t>would_move_for_work</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Project design (respondent-gated seasonal recall); the underlying two-season design follows Beegle et al. 2012 and Deaton and Grosh 2000 on usual-period recall</t>
+          <t>Project design (referral channel as a proxy for social capital and for placement debt)</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -16771,14 +16821,14 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>spend_differs_by_season</t>
+          <t>migration_referral</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 13.1-13.2 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.38-14.39 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses a 6-month recall for clothing (items 401-441); we follow the two India sources, since one of them (HCES) underlies our poverty line</t>
+          <t>Project design (respondent-gated seasonal recall); the underlying two-season design follows Beegle et al. 2012 and Deaton and Grosh 2000 on usual-period recall</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
@@ -16786,14 +16836,14 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>cons_clothing_12m</t>
+          <t>spend_differs_by_season</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 10.1 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.35-14.37 (365-day, same items). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 asks school fees inside its education/roster module, per child, not as a household total, so it is not directly comparable</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 13.1-13.2 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.38-14.39 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses a 6-month recall for clothing (items 401-441); we follow the two India sources, since one of them (HCES) underlies our poverty line</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -16801,14 +16851,14 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>cons_education_12m</t>
+          <t>cons_clothing_12m</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 10.2 (365-day, hospitalisation). IHDS-II Income and Social Capital Questionnaire, Q14 14.34 (365-day, in-patient). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses one combined 6-month medical item (less detail); we follow the matching HCES/IHDS split</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 10.1 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.35-14.37 (365-day, same items). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 asks school fees inside its education/roster module, per child, not as a household total, so it is not directly comparable</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
@@ -16816,14 +16866,14 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>cons_medical_hosp_12m</t>
+          <t>cons_education_12m</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 14 (365-day, 10 sub-groups). IHDS-II Income and Social Capital Questionnaire, Q14 14.40-14.48 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (12-month tier: durables, appliances, building materials). All three agree on the 12-month recall; insurance premiums, which IHDS (14.50) and the Nigeria survey (items 510-513) count here, are excluded, following HCES and standard national-accounts practice (insurance is a financial item, not consumption) — premiums are covered instead by the insurance items in Module G</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 10.2 (365-day, hospitalisation). IHDS-II Income and Social Capital Questionnaire, Q14 14.34 (365-day, in-patient). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses one combined 6-month medical item (less detail); we follow the matching HCES/IHDS split</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -16831,14 +16881,14 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>cons_durables_12m</t>
+          <t>cons_medical_hosp_12m</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI housing indicator (wall limb)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 14 (365-day, 10 sub-groups). IHDS-II Income and Social Capital Questionnaire, Q14 14.40-14.48 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (12-month tier: durables, appliances, building materials). All three agree on the 12-month recall; insurance premiums, which IHDS (14.50) and the Nigeria survey (items 510-513) count here, are excluded, following HCES and standard national-accounts practice (insurance is a financial item, not consumption) — premiums are covered instead by the insurance items in Module G</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
@@ -16846,14 +16896,14 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>wall_material</t>
+          <t>cons_durables_12m</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Lyons et al. 2023, Table 2 (area/settlement conditions), adapted to a labour-migrant setting</t>
+          <t>NITI Aayog National MPI housing indicator (wall limb)</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -16861,14 +16911,14 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>accom_type_here</t>
+          <t>wall_material</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI</t>
+          <t>Lyons et al. 2023, Table 2 (area/settlement conditions), adapted to a labour-migrant setting</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
@@ -16876,14 +16926,14 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>accom_type_here</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI sanitation indicator (improved/unimproved and shared/not)</t>
+          <t>NITI Aayog National MPI</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -16891,14 +16941,14 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>toilet_type</t>
+          <t>electricity</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI drinking-water indicator (JMP improved/unimproved taxonomy)</t>
+          <t>NITI Aayog National MPI sanitation indicator (improved/unimproved and shared/not)</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
@@ -16906,14 +16956,14 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>drinking_water</t>
+          <t>toilet_type</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI cooking-fuel indicator (its own list of dirty fuels)</t>
+          <t>NITI Aayog National MPI drinking-water indicator (JMP improved/unimproved taxonomy)</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -16921,14 +16971,14 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>cooking_fuel</t>
+          <t>drinking_water</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI assets indicator (car or truck limb)</t>
+          <t>NITI Aayog National MPI cooking-fuel indicator (its own list of dirty fuels)</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
@@ -16936,14 +16986,14 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>owns_car</t>
+          <t>cooking_fuel</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Project design (local land units, Uttarakhand)</t>
+          <t>NITI Aayog National MPI assets indicator (car or truck limb)</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -16951,14 +17001,14 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>land_unit</t>
+          <t>owns_car</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Project design (pilot livelihood survey)</t>
+          <t>Project design (local land units, Uttarakhand)</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
@@ -16966,14 +17016,14 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>owns_pony_mule</t>
+          <t>land_unit</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI bank-account indicator; VEP adaptive-capacity covariate</t>
+          <t>Project design (pilot livelihood survey)</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -16981,14 +17031,14 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>has_bank_account</t>
+          <t>owns_pony_mule</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate</t>
+          <t>NITI Aayog National MPI bank-account indicator; VEP adaptive-capacity covariate</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
@@ -16996,14 +17046,14 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>took_loan_12m</t>
+          <t>has_bank_account</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate (lender type)</t>
+          <t>VEP adaptive-capacity covariate</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -17011,14 +17061,14 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>credit_source</t>
+          <t>took_loan_12m</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Project design (investment against distress borrowing)</t>
+          <t>VEP adaptive-capacity covariate (lender type)</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
@@ -17026,14 +17076,14 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>loan_purpose</t>
+          <t>credit_source</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Project design (loan size, for the debt-burden measures)</t>
+          <t>Project design (investment against distress borrowing)</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -17041,14 +17091,14 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>loan_amount_borrowed</t>
+          <t>loan_purpose</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Islam and Chowdhury 2025 (financial distress and household vulnerability to poverty)</t>
+          <t>Project design (loan size, for the debt-burden measures)</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
@@ -17056,14 +17106,14 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>loan_amount</t>
+          <t>loan_amount_borrowed</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Project design (informal lending is often interest-free)</t>
+          <t>Islam and Chowdhury 2025 (financial distress and household vulnerability to poverty)</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -17071,14 +17121,14 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>pays_interest</t>
+          <t>loan_amount</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Project design (informal-credit pricing as locally quoted)</t>
+          <t>Project design (informal lending is often interest-free)</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
@@ -17086,14 +17136,14 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>loan_interest_per100_pm</t>
+          <t>pays_interest</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
+          <t>Project design (informal-credit pricing as locally quoted)</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -17101,14 +17151,14 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>loan_against_asset</t>
+          <t>loan_interest_per100_pm</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003 (asset-based coping)</t>
+          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
@@ -17116,14 +17166,14 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>loan_collateral</t>
+          <t>loan_against_asset</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI health-insurance indicator; Lyons et al. 2023</t>
+          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003 (asset-based coping)</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -17131,14 +17181,14 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>n_health_insured</t>
+          <t>loan_collateral</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Project design; scheme names as administered in Uttarakhand</t>
+          <t>NITI Aayog National MPI health-insurance indicator; Lyons et al. 2023</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
@@ -17146,14 +17196,14 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>govt_any_benefit</t>
+          <t>n_health_insured</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Project design; coded in the office against the Uttarakhand scheme list</t>
+          <t>Project design; scheme names as administered in Uttarakhand</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
@@ -17161,14 +17211,14 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>govt_schemes_detail</t>
+          <t>govt_any_benefit</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Lyons et al. 2023, Table 2 (legal residency), adapted; One Nation One Ration Card</t>
+          <t>Project design; coded in the office against the Uttarakhand scheme list</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
@@ -17176,14 +17226,14 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>ration_portable_here</t>
+          <t>govt_schemes_detail</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Project design (intra-household financial capability)</t>
+          <t>Lyons et al. 2023, Table 2 (legal residency), adapted; One Nation One Ration Card</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
@@ -17191,14 +17241,14 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>n_can_transact_online</t>
+          <t>ration_portable_here</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>NSS health module (15-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
+          <t>Project design (intra-household financial capability)</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
@@ -17206,14 +17256,14 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>morbidity_15d</t>
+          <t>n_can_transact_online</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Project design (a reported illness with no cost/coping follow-up said nothing about its burden)</t>
+          <t>NSS health module (15-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
@@ -17221,14 +17271,14 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>morbidity_coping_15d</t>
+          <t>morbidity_15d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Washington Group on Disability Statistics, Short Set item 3 (mobility), verbatim; Lyons et al. 2023 health dimension</t>
+          <t>Project design (a reported illness with no cost/coping follow-up said nothing about its burden)</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
@@ -17236,14 +17286,14 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>func_limitation</t>
+          <t>morbidity_coping_15d</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>NSS health module (365-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
+          <t>Washington Group on Disability Statistics, Short Set item 3 (mobility), verbatim; Lyons et al. 2023 health dimension</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
@@ -17251,14 +17301,14 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>hospitalization_365d</t>
+          <t>func_limitation</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 barriers_health_case_access_phc_m (primary-care access barriers); Lyons et al. 2023 Table 2 indicator 2 'healthcare access'</t>
+          <t>NSS health module (365-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
@@ -17266,14 +17316,14 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>health_access_barrier_3m</t>
+          <t>hospitalization_365d</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Child and Adolescent Mortality (weight 1/12)</t>
+          <t>VASyR 2025 barriers_health_case_access_phc_m (primary-care access barriers); Lyons et al. 2023 Table 2 indicator 2 'healthcare access'</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
@@ -17281,14 +17331,14 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>child_death_5y</t>
+          <t>health_access_barrier_3m</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (weight 1/12)</t>
+          <t>NITI Aayog National MPI, Child and Adolescent Mortality (weight 1/12)</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
@@ -17296,14 +17346,14 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>birth_last_5y</t>
+          <t>child_death_5y</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (antenatal care limb)</t>
+          <t>NITI Aayog National MPI, Maternal Health (weight 1/12)</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
@@ -17311,14 +17361,14 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>anc_4_visits</t>
+          <t>birth_last_5y</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (assisted delivery limb); skilled-provider definition per NFHS</t>
+          <t>NITI Aayog National MPI, Maternal Health (antenatal care limb)</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
@@ -17326,14 +17376,14 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>skilled_birth_attendant</t>
+          <t>anc_4_visits</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>VEP exposure covariate (Azeem et al. 2016); shock inventory following Gunther and Harttgen 2009, via Fujii 2016 section 4</t>
+          <t>NITI Aayog National MPI, Maternal Health (assisted delivery limb); skilled-provider definition per NFHS</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
@@ -17341,14 +17391,14 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>distress_event_last365d</t>
+          <t>skilled_birth_attendant</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Dercon and Krishnan 2000 (seasonal timing of shocks); project design</t>
+          <t>VEP exposure covariate (Azeem et al. 2016); shock inventory following Gunther and Harttgen 2009, via Fujii 2016 section 4</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
@@ -17356,14 +17406,14 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>shock_month</t>
+          <t>distress_event_last365d</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
+          <t>Dercon and Krishnan 2000 (seasonal timing of shocks); project design</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
@@ -17371,14 +17421,14 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>shock_coping</t>
+          <t>shock_month</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Pelz et al. 2024, Energy Policy 186:113973 (concept: perceived effect on livelihoods; wording ours)</t>
+          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
@@ -17386,14 +17436,14 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>ropeway_expect_work</t>
+          <t>shock_coping</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Pelz et al. 2024, Energy Policy 186:113973 (concept: local vs outside benefit; wording ours)</t>
+          <t>Pelz et al. 2024, Energy Policy 186:113973 (concept: perceived effect on livelihoods; wording ours)</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
@@ -17401,14 +17451,14 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>ropeway_expect_jobs</t>
+          <t>ropeway_expect_work</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Pelz et al. 2024, Energy Policy 186:113973 (Fig. 4B, trust in the company; wording ours)</t>
+          <t>Pelz et al. 2024, Energy Policy 186:113973 (concept: local vs outside benefit; wording ours)</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
@@ -17416,14 +17466,14 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>ropeway_trust</t>
+          <t>ropeway_expect_jobs</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
+          <t>Pelz et al. 2024, Energy Policy 186:113973 (Fig. 4B, trust in the company; wording ours)</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
@@ -17431,14 +17481,14 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>trek_dependent</t>
+          <t>ropeway_trust</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
+          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
@@ -17446,14 +17496,14 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>job_situation</t>
+          <t>trek_dependent</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
@@ -17461,14 +17511,14 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>job_permanence</t>
+          <t>job_situation</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
@@ -17476,14 +17526,14 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>contract_status</t>
+          <t>job_permanence</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
@@ -17491,14 +17541,14 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>workplace_registered</t>
+          <t>contract_status</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
@@ -17506,14 +17556,14 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>pension_contrib</t>
+          <t>workplace_registered</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
@@ -17521,14 +17571,14 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>work_health_ins</t>
+          <t>pension_contrib</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
@@ -17536,14 +17586,14 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>leave_rights</t>
+          <t>work_health_ins</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
@@ -17551,14 +17601,14 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>injured_ever</t>
+          <t>leave_rights</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
@@ -17566,14 +17616,14 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>wants_more_work</t>
+          <t>injured_ever</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
@@ -17581,14 +17631,14 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>more_hours_day</t>
+          <t>wants_more_work</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
@@ -17596,14 +17646,14 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>months_looked_for_work</t>
+          <t>more_hours_day</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
@@ -17611,14 +17661,14 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>first_job_ever</t>
+          <t>months_looked_for_work</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 employment table, occupational status (1/8)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
         </is>
       </c>
       <c r="B133" s="2" t="n">
@@ -17626,14 +17676,14 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>higher_ed</t>
+          <t>first_job_ever</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 employment table, employment security (1/8)</t>
+          <t>Apablaza et al. 2026, Appendix 2 employment table, occupational status (1/8)</t>
         </is>
       </c>
       <c r="B134" s="2" t="n">
@@ -17641,14 +17691,14 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>social_security_any</t>
+          <t>higher_ed</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
+          <t>Apablaza et al. 2026, Appendix 2 employment table, employment security (1/8)</t>
         </is>
       </c>
       <c r="B135" s="2" t="n">
@@ -17656,14 +17706,14 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>tk_load</t>
+          <t>social_security_any</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
+          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
@@ -17671,14 +17721,14 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>tk_drive</t>
+          <t>tk_load</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
+          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
@@ -17686,14 +17736,14 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>tk_engine</t>
+          <t>tk_drive</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
@@ -17701,14 +17751,14 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>tk_electric</t>
+          <t>tk_engine</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
+          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
         </is>
       </c>
       <c r="B139" s="2" t="n">
@@ -17716,14 +17766,14 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>tk_safety</t>
+          <t>tk_electric</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
         </is>
       </c>
       <c r="B140" s="2" t="n">
@@ -17731,14 +17781,14 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>tk_sell</t>
+          <t>tk_safety</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Autor and Handel 2013; NCO 5131.0401</t>
+          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
         </is>
       </c>
       <c r="B141" s="2" t="n">
@@ -17746,14 +17796,14 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>tk_cash</t>
+          <t>tk_sell</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>NCO 5120.0300 cook</t>
+          <t>Autor and Handel 2013; NCO 5131.0401</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
@@ -17761,14 +17811,14 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>tk_cook</t>
+          <t>tk_cash</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
+          <t>NCO 5120.0300 cook</t>
         </is>
       </c>
       <c r="B143" s="2" t="n">
@@ -17776,14 +17826,14 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>tk_serve</t>
+          <t>tk_cook</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
+          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="n">
@@ -17791,14 +17841,14 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>tk_clean</t>
+          <t>tk_serve</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
+          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
         </is>
       </c>
       <c r="B145" s="2" t="n">
@@ -17806,14 +17856,14 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>tk_guide</t>
+          <t>tk_clean</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>NCO 8343.1700 ropeway operator</t>
+          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
         </is>
       </c>
       <c r="B146" s="2" t="n">
@@ -17821,14 +17871,14 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>tk_coord</t>
+          <t>tk_guide</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Level ladder without licences: people drive without holding a licence</t>
+          <t>NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
       <c r="B147" s="2" t="n">
@@ -17836,14 +17886,14 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>drove_twowheeler</t>
+          <t>tk_coord</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001, natural capital: resource stocks from which resource flows are derived (definitions list); item wording is ours</t>
+          <t>Level ladder without licences: people drive without holding a licence</t>
         </is>
       </c>
       <c r="B148" s="2" t="n">
@@ -17851,14 +17901,14 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>cpr_firewood</t>
+          <t>drove_twowheeler</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001, natural capital (resource flows from stocks); item wording is ours</t>
+          <t>Krantz 2001, natural capital: resource stocks from which resource flows are derived (definitions list); item wording is ours</t>
         </is>
       </c>
       <c r="B149" s="2" t="n">
@@ -17866,14 +17916,14 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>cpr_forest_produce</t>
+          <t>cpr_firewood</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001, access ('the opportunity in practice to use a resource') and claims ('demands and appeals'); item wording is ours</t>
+          <t>Krantz 2001, natural capital (resource flows from stocks); item wording is ours</t>
         </is>
       </c>
       <c r="B150" s="2" t="n">
@@ -17881,14 +17931,14 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>cpr_restricted</t>
+          <t>cpr_forest_produce</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001, access (as above); the ropeway link is the project's own</t>
+          <t>Krantz 2001, access ('the opportunity in practice to use a resource') and claims ('demands and appeals'); item wording is ours</t>
         </is>
       </c>
       <c r="B151" s="2" t="n">
@@ -17896,14 +17946,14 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>cpr_lost_access</t>
+          <t>cpr_restricted</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Krantz 2001, natural capital (water) and access ('the opportunity in practice to use a resource'); item wording is ours</t>
+          <t>Krantz 2001, access (as above); the ropeway link is the project's own</t>
         </is>
       </c>
       <c r="B152" s="2" t="n">
@@ -17911,14 +17961,14 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>cpr_water_route</t>
+          <t>cpr_lost_access</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>NO SOURCE ON DISK YET: Krantz does not address governance of common land. To be sourced from Agrawal 2001 or Ostrom 1990 once read on disk</t>
+          <t>Krantz 2001, natural capital (water) and access ('the opportunity in practice to use a resource'); item wording is ours</t>
         </is>
       </c>
       <c r="B153" s="2" t="n">
@@ -17926,12 +17976,27 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
+          <t>cpr_water_route</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>NO SOURCE ON DISK YET: Krantz does not address governance of common land. To be sourced from Agrawal 2001 or Ostrom 1990 once read on disk</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
           <t>cpr_governance</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C153"/>
+  <autoFilter ref="A1:C154"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18009,7 +18074,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -18185,7 +18250,7 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>

--- a/Question_register.xlsx
+++ b/Question_register.xlsx
@@ -11096,12 +11096,12 @@
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did anyone in your household collect firewood or dead wood from common land or forest near here?</t>
+          <t>In this Yatra season or last Yatra season, did you or anyone staying with you here collect firewood or dead wood from common land or forest in the Yatra region or workplace region?</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने आस-पास की साझा ज़मीन या जंगल से लकड़ी या सूखी टहनियाँ इकट्ठी कीं?</t>
+          <t>इस यात्रा सीज़न या पिछले यात्रा सीज़न में, क्या आपने या आपके साथ यहाँ रहने वाले किसी ने यात्रा क्षेत्र या काम की जगह की साझा ज़मीन या जंगल से लकड़ी या सूखी टहनियाँ इकट्ठी कीं?</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11142,12 +11142,12 @@
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did anyone in your household cut grass or fodder from common land near here?</t>
+          <t>In this Yatra season or last Yatra season, did you or anyone staying with you here cut grass or fodder from common land in the Yatra region or workplace region?</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने साझा ज़मीन से घास या चारा काटा?</t>
+          <t>इस यात्रा सीज़न या पिछले यात्रा सीज़न में, क्या आपने या आपके साथ यहाँ रहने वाले किसी ने यात्रा क्षेत्र या काम की जगह की साझा ज़मीन से घास या चारा काटा?</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11188,12 +11188,12 @@
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did anyone in your household collect herbs, mushrooms or wild fruit from the forest?</t>
+          <t>In this Yatra season or last Yatra season, did you or anyone staying with you here collect herbs, mushrooms or wild fruit from the forest in the Yatra region or workplace region?</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी ने जंगल से जड़ी-बूटी, मशरूम या जंगली फल इकट्ठे किए?</t>
+          <t>इस यात्रा सीज़न या पिछले यात्रा सीज़न में, क्या आपने या आपके साथ यहाँ रहने वाले किसी ने यात्रा क्षेत्र या काम की जगह के जंगल से जड़ी-बूटी, मशरूम या जंगली फल इकट्ठे किए?</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -11234,12 +11234,12 @@
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did any animal of your household graze on common pasture?</t>
+          <t>In this Yatra season or last Yatra season, did any animal of yours or of anyone staying with you here graze on common pasture in the Yatra region or workplace region?</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर का कोई जानवर साझा चरागाह में चरा?</t>
+          <t>इस यात्रा सीज़न या पिछले यात्रा सीज़न में, क्या आपका या आपके साथ यहाँ रहने वाले किसी का कोई जानवर यात्रा क्षेत्र या काम की जगह की साझा चरागाह में चरा?</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -11280,12 +11280,12 @@
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, has anyone in your household been stopped from using a common forest, pasture or path, or been asked to pay to use it?</t>
+          <t>In this Yatra season or last Yatra season, has anyone you or someone staying with you here been stopped from using a common forest, pasture or path, or been asked to pay to use it, in the Yatra region or workplace region?</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या आपके घर के किसी को साझा जंगल, चरागाह या रास्ते के इस्तेमाल से रोका गया, या इसके लिए पैसे देने को कहा गया?</t>
+          <t>इस यात्रा सीज़न या पिछले यात्रा सीज़न में, क्या आपको या आपके साथ यहाँ रहने वाले किसी को यात्रा क्षेत्र या काम की जगह में साझा जंगल, चरागाह या रास्ते के इस्तेमाल से रोका गया, या इसके लिए पैसे देने को कहा गया?</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, has a common place you used to collect from or graze on been closed because of building, road or ropeway work?</t>
+          <t>In this Yatra season or last Yatra season, has a common place you used to collect from or graze on been closed, because of a landslide, flood, road or bridge damage, or construction work, in the Yatra region or workplace region?</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में, क्या कोई साझा जगह, जहाँ आप पहले लकड़ी, घास या चारा लेते थे, निर्माण, सड़क या रोपवे के काम की वजह से बंद हो गई?</t>
+          <t>इस यात्रा सीज़न या पिछले यात्रा सीज़न में, क्या कोई साझा जगह, जहाँ आप पहले लकड़ी, घास या चारा लेते थे, भूस्खलन, बाढ़, सड़क या पुल टूटने, या निर्माण कार्य की वजह से बंद हो गई?</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>In this area, who decides who may use the common land and forest? Ask and code what they name; do not read the list.</t>
+          <t>In the Yatra region or workplace region, who decides who may use the common land and forest? Ask and code what they name; do not read the list.</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>इस इलाके की साझा ज़मीन और जंगल का फ़ैसला कौन करता है, कि कौन उसका इस्तेमाल कर सकता है? जो नाम लें वही लिख लें; सूची न पढ़ें।</t>
+          <t>यात्रा क्षेत्र या काम की जगह की साझा ज़मीन और जंगल का फ़ैसला कौन करता है, कि कौन उसका इस्तेमाल कर सकता है? जो नाम लें वही लिख लें; सूची न पढ़ें।</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
